--- a/output/df_estudiantes_final.xlsx
+++ b/output/df_estudiantes_final.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Indice_Conocimiento</t>
+          <t>Indice_Conocimiento_Norm</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Indice_Prevencion</t>
+          <t>Indice_Prevencion_Norm</t>
         </is>
       </c>
     </row>
@@ -520,10 +520,10 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K2" t="n">
-        <v>36</v>
+        <v>76.59574468085107</v>
       </c>
     </row>
     <row r="3">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K3" t="n">
-        <v>46</v>
+        <v>97.87234042553192</v>
       </c>
     </row>
     <row r="4">
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>46</v>
+        <v>97.87234042553192</v>
       </c>
     </row>
     <row r="5">
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K5" t="n">
-        <v>36</v>
+        <v>76.59574468085107</v>
       </c>
     </row>
     <row r="6">
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>25</v>
+        <v>53.19148936170212</v>
       </c>
     </row>
     <row r="7">
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>65.95744680851064</v>
       </c>
     </row>
     <row r="8">
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K8" t="n">
-        <v>39</v>
+        <v>82.97872340425532</v>
       </c>
     </row>
     <row r="9">
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K9" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="10">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K10" t="n">
-        <v>44</v>
+        <v>93.61702127659575</v>
       </c>
     </row>
     <row r="11">
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K11" t="n">
-        <v>47</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K12" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="13">
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K13" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="14">
@@ -1156,10 +1156,10 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K14" t="n">
-        <v>47</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K15" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="16">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K16" t="n">
-        <v>31</v>
+        <v>65.95744680851064</v>
       </c>
     </row>
     <row r="17">
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K17" t="n">
-        <v>26</v>
+        <v>55.31914893617022</v>
       </c>
     </row>
     <row r="18">
@@ -1368,10 +1368,10 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K18" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="19">
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K19" t="n">
-        <v>26</v>
+        <v>55.31914893617022</v>
       </c>
     </row>
     <row r="20">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K20" t="n">
-        <v>41</v>
+        <v>87.2340425531915</v>
       </c>
     </row>
     <row r="21">
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K21" t="n">
-        <v>41</v>
+        <v>87.2340425531915</v>
       </c>
     </row>
     <row r="22">
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K22" t="n">
-        <v>14</v>
+        <v>29.78723404255319</v>
       </c>
     </row>
     <row r="23">
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K23" t="n">
-        <v>25</v>
+        <v>53.19148936170212</v>
       </c>
     </row>
     <row r="24">
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K24" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="25">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K25" t="n">
-        <v>41</v>
+        <v>87.2340425531915</v>
       </c>
     </row>
     <row r="26">
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K26" t="n">
-        <v>34</v>
+        <v>72.3404255319149</v>
       </c>
     </row>
     <row r="27">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K27" t="n">
-        <v>25</v>
+        <v>53.19148936170212</v>
       </c>
     </row>
     <row r="28">
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K28" t="n">
-        <v>37</v>
+        <v>78.72340425531915</v>
       </c>
     </row>
     <row r="29">
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K29" t="n">
-        <v>44</v>
+        <v>93.61702127659575</v>
       </c>
     </row>
     <row r="30">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K30" t="n">
-        <v>26</v>
+        <v>55.31914893617022</v>
       </c>
     </row>
     <row r="31">
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K31" t="n">
-        <v>43</v>
+        <v>91.48936170212765</v>
       </c>
     </row>
     <row r="32">
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K32" t="n">
-        <v>43</v>
+        <v>91.48936170212765</v>
       </c>
     </row>
     <row r="33">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K33" t="n">
-        <v>31</v>
+        <v>65.95744680851064</v>
       </c>
     </row>
     <row r="34">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K34" t="n">
-        <v>23</v>
+        <v>48.93617021276596</v>
       </c>
     </row>
     <row r="35">
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K35" t="n">
-        <v>39</v>
+        <v>82.97872340425532</v>
       </c>
     </row>
     <row r="36">
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K36" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="37">
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K37" t="n">
-        <v>36</v>
+        <v>76.59574468085107</v>
       </c>
     </row>
     <row r="38">
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K38" t="n">
-        <v>45</v>
+        <v>95.74468085106383</v>
       </c>
     </row>
     <row r="39">
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K39" t="n">
-        <v>43</v>
+        <v>91.48936170212765</v>
       </c>
     </row>
     <row r="40">
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K40" t="n">
-        <v>43</v>
+        <v>91.48936170212765</v>
       </c>
     </row>
     <row r="41">
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K41" t="n">
-        <v>32</v>
+        <v>68.08510638297872</v>
       </c>
     </row>
     <row r="42">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K42" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="43">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K43" t="n">
-        <v>40</v>
+        <v>85.1063829787234</v>
       </c>
     </row>
     <row r="44">
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K44" t="n">
-        <v>45</v>
+        <v>95.74468085106383</v>
       </c>
     </row>
     <row r="45">
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K45" t="n">
-        <v>34</v>
+        <v>72.3404255319149</v>
       </c>
     </row>
     <row r="46">
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K46" t="n">
-        <v>39</v>
+        <v>82.97872340425532</v>
       </c>
     </row>
     <row r="47">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K47" t="n">
-        <v>31</v>
+        <v>65.95744680851064</v>
       </c>
     </row>
     <row r="48">
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K48" t="n">
-        <v>40</v>
+        <v>85.1063829787234</v>
       </c>
     </row>
     <row r="49">
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K49" t="n">
-        <v>37</v>
+        <v>78.72340425531915</v>
       </c>
     </row>
     <row r="50">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K50" t="n">
-        <v>28</v>
+        <v>59.57446808510638</v>
       </c>
     </row>
     <row r="51">
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K51" t="n">
-        <v>42</v>
+        <v>89.36170212765957</v>
       </c>
     </row>
     <row r="52">
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K52" t="n">
-        <v>25</v>
+        <v>53.19148936170212</v>
       </c>
     </row>
     <row r="53">
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K53" t="n">
-        <v>39</v>
+        <v>82.97872340425532</v>
       </c>
     </row>
     <row r="54">
@@ -3276,10 +3276,10 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K54" t="n">
-        <v>45</v>
+        <v>95.74468085106383</v>
       </c>
     </row>
     <row r="55">
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K55" t="n">
-        <v>27</v>
+        <v>57.44680851063831</v>
       </c>
     </row>
     <row r="56">
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K56" t="n">
-        <v>20</v>
+        <v>42.5531914893617</v>
       </c>
     </row>
     <row r="57">
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K57" t="n">
-        <v>45</v>
+        <v>95.74468085106383</v>
       </c>
     </row>
     <row r="58">
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K58" t="n">
-        <v>45</v>
+        <v>95.74468085106383</v>
       </c>
     </row>
     <row r="59">
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K59" t="n">
-        <v>32</v>
+        <v>68.08510638297872</v>
       </c>
     </row>
     <row r="60">
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K60" t="n">
-        <v>42</v>
+        <v>89.36170212765957</v>
       </c>
     </row>
     <row r="61">
@@ -3647,10 +3647,10 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K61" t="n">
-        <v>36</v>
+        <v>76.59574468085107</v>
       </c>
     </row>
     <row r="62">
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K62" t="n">
-        <v>34</v>
+        <v>72.3404255319149</v>
       </c>
     </row>
     <row r="63">
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K63" t="n">
-        <v>42</v>
+        <v>89.36170212765957</v>
       </c>
     </row>
     <row r="64">
@@ -3806,10 +3806,10 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K64" t="n">
-        <v>36</v>
+        <v>76.59574468085107</v>
       </c>
     </row>
     <row r="65">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K65" t="n">
-        <v>39</v>
+        <v>82.97872340425532</v>
       </c>
     </row>
     <row r="66">
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K66" t="n">
-        <v>28</v>
+        <v>59.57446808510638</v>
       </c>
     </row>
     <row r="67">
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K67" t="n">
-        <v>30</v>
+        <v>63.82978723404256</v>
       </c>
     </row>
     <row r="68">
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K68" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="69">
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K69" t="n">
-        <v>32</v>
+        <v>68.08510638297872</v>
       </c>
     </row>
     <row r="70">
@@ -4124,10 +4124,10 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K70" t="n">
-        <v>22</v>
+        <v>46.80851063829788</v>
       </c>
     </row>
     <row r="71">
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K71" t="n">
-        <v>26</v>
+        <v>55.31914893617022</v>
       </c>
     </row>
     <row r="72">
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K72" t="n">
-        <v>25</v>
+        <v>53.19148936170212</v>
       </c>
     </row>
     <row r="73">
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K73" t="n">
-        <v>22</v>
+        <v>46.80851063829788</v>
       </c>
     </row>
     <row r="74">
@@ -4336,10 +4336,10 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K74" t="n">
-        <v>32</v>
+        <v>68.08510638297872</v>
       </c>
     </row>
     <row r="75">
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K75" t="n">
-        <v>34</v>
+        <v>72.3404255319149</v>
       </c>
     </row>
     <row r="76">
@@ -4442,10 +4442,10 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K76" t="n">
-        <v>33</v>
+        <v>70.21276595744681</v>
       </c>
     </row>
     <row r="77">
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K77" t="n">
-        <v>27</v>
+        <v>57.44680851063831</v>
       </c>
     </row>
     <row r="78">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K78" t="n">
-        <v>21</v>
+        <v>44.68085106382978</v>
       </c>
     </row>
     <row r="79">
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K79" t="n">
-        <v>18</v>
+        <v>38.29787234042553</v>
       </c>
     </row>
     <row r="80">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K80" t="n">
-        <v>21</v>
+        <v>44.68085106382978</v>
       </c>
     </row>
     <row r="81">
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K81" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="82">
@@ -4760,10 +4760,10 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K82" t="n">
-        <v>18</v>
+        <v>38.29787234042553</v>
       </c>
     </row>
     <row r="83">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K83" t="n">
-        <v>20</v>
+        <v>42.5531914893617</v>
       </c>
     </row>
     <row r="84">
@@ -4866,10 +4866,10 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K84" t="n">
-        <v>22</v>
+        <v>46.80851063829788</v>
       </c>
     </row>
     <row r="85">
@@ -4919,10 +4919,10 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K85" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="86">
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K86" t="n">
-        <v>20</v>
+        <v>42.5531914893617</v>
       </c>
     </row>
     <row r="87">
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K87" t="n">
-        <v>22</v>
+        <v>46.80851063829788</v>
       </c>
     </row>
     <row r="88">
@@ -5078,10 +5078,10 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K88" t="n">
-        <v>21</v>
+        <v>44.68085106382978</v>
       </c>
     </row>
     <row r="89">
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K89" t="n">
-        <v>33</v>
+        <v>70.21276595744681</v>
       </c>
     </row>
     <row r="90">
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K90" t="n">
-        <v>27</v>
+        <v>57.44680851063831</v>
       </c>
     </row>
     <row r="91">
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K91" t="n">
-        <v>27</v>
+        <v>57.44680851063831</v>
       </c>
     </row>
     <row r="92">
@@ -5290,10 +5290,10 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K92" t="n">
-        <v>39</v>
+        <v>82.97872340425532</v>
       </c>
     </row>
     <row r="93">
@@ -5343,10 +5343,10 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K93" t="n">
-        <v>22</v>
+        <v>46.80851063829788</v>
       </c>
     </row>
     <row r="94">
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K94" t="n">
-        <v>18</v>
+        <v>38.29787234042553</v>
       </c>
     </row>
     <row r="95">
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K95" t="n">
-        <v>31</v>
+        <v>65.95744680851064</v>
       </c>
     </row>
     <row r="96">
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K96" t="n">
-        <v>30</v>
+        <v>63.82978723404256</v>
       </c>
     </row>
     <row r="97">
@@ -5555,10 +5555,10 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K97" t="n">
-        <v>28</v>
+        <v>59.57446808510638</v>
       </c>
     </row>
     <row r="98">
@@ -5608,10 +5608,10 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K98" t="n">
-        <v>22</v>
+        <v>46.80851063829788</v>
       </c>
     </row>
     <row r="99">
@@ -5661,10 +5661,10 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K99" t="n">
-        <v>19</v>
+        <v>40.42553191489361</v>
       </c>
     </row>
     <row r="100">
@@ -5717,7 +5717,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>23</v>
+        <v>48.93617021276596</v>
       </c>
     </row>
     <row r="101">
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K101" t="n">
-        <v>33</v>
+        <v>70.21276595744681</v>
       </c>
     </row>
     <row r="102">
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K102" t="n">
-        <v>29</v>
+        <v>61.70212765957447</v>
       </c>
     </row>
     <row r="103">
@@ -5873,10 +5873,10 @@
         </is>
       </c>
       <c r="J103" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K103" t="n">
-        <v>34</v>
+        <v>72.3404255319149</v>
       </c>
     </row>
     <row r="104">
@@ -5929,7 +5929,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="105">
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K105" t="n">
-        <v>19</v>
+        <v>40.42553191489361</v>
       </c>
     </row>
     <row r="106">
@@ -6032,10 +6032,10 @@
         </is>
       </c>
       <c r="J106" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K106" t="n">
-        <v>34</v>
+        <v>72.3404255319149</v>
       </c>
     </row>
     <row r="107">
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K107" t="n">
-        <v>20</v>
+        <v>42.5531914893617</v>
       </c>
     </row>
     <row r="108">
@@ -6138,10 +6138,10 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K108" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="109">
@@ -6191,10 +6191,10 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K109" t="n">
-        <v>44</v>
+        <v>93.61702127659575</v>
       </c>
     </row>
     <row r="110">
@@ -6244,10 +6244,10 @@
         </is>
       </c>
       <c r="J110" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K110" t="n">
-        <v>41</v>
+        <v>87.2340425531915</v>
       </c>
     </row>
     <row r="111">
@@ -6297,10 +6297,10 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K111" t="n">
-        <v>40</v>
+        <v>85.1063829787234</v>
       </c>
     </row>
     <row r="112">
@@ -6350,10 +6350,10 @@
         </is>
       </c>
       <c r="J112" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K112" t="n">
-        <v>40</v>
+        <v>85.1063829787234</v>
       </c>
     </row>
     <row r="113">
@@ -6403,10 +6403,10 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K113" t="n">
-        <v>34</v>
+        <v>72.3404255319149</v>
       </c>
     </row>
     <row r="114">
@@ -6456,10 +6456,10 @@
         </is>
       </c>
       <c r="J114" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K114" t="n">
-        <v>30</v>
+        <v>63.82978723404256</v>
       </c>
     </row>
     <row r="115">
@@ -6509,10 +6509,10 @@
         </is>
       </c>
       <c r="J115" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K115" t="n">
-        <v>22</v>
+        <v>46.80851063829788</v>
       </c>
     </row>
     <row r="116">
@@ -6562,10 +6562,10 @@
         </is>
       </c>
       <c r="J116" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K116" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="117">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K117" t="n">
-        <v>28</v>
+        <v>59.57446808510638</v>
       </c>
     </row>
     <row r="118">
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="J118" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K118" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="119">
@@ -6721,10 +6721,10 @@
         </is>
       </c>
       <c r="J119" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K119" t="n">
-        <v>26</v>
+        <v>55.31914893617022</v>
       </c>
     </row>
     <row r="120">
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="J120" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K120" t="n">
-        <v>22</v>
+        <v>46.80851063829788</v>
       </c>
     </row>
     <row r="121">
@@ -6827,10 +6827,10 @@
         </is>
       </c>
       <c r="J121" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K121" t="n">
-        <v>37</v>
+        <v>78.72340425531915</v>
       </c>
     </row>
     <row r="122">
@@ -6880,10 +6880,10 @@
         </is>
       </c>
       <c r="J122" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K122" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="123">
@@ -6933,10 +6933,10 @@
         </is>
       </c>
       <c r="J123" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K123" t="n">
-        <v>32</v>
+        <v>68.08510638297872</v>
       </c>
     </row>
     <row r="124">
@@ -6986,10 +6986,10 @@
         </is>
       </c>
       <c r="J124" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K124" t="n">
-        <v>32</v>
+        <v>68.08510638297872</v>
       </c>
     </row>
     <row r="125">
@@ -7039,10 +7039,10 @@
         </is>
       </c>
       <c r="J125" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K125" t="n">
-        <v>27</v>
+        <v>57.44680851063831</v>
       </c>
     </row>
     <row r="126">
@@ -7092,10 +7092,10 @@
         </is>
       </c>
       <c r="J126" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K126" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="127">
@@ -7145,10 +7145,10 @@
         </is>
       </c>
       <c r="J127" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K127" t="n">
-        <v>37</v>
+        <v>78.72340425531915</v>
       </c>
     </row>
     <row r="128">
@@ -7198,10 +7198,10 @@
         </is>
       </c>
       <c r="J128" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K128" t="n">
-        <v>31</v>
+        <v>65.95744680851064</v>
       </c>
     </row>
     <row r="129">
@@ -7251,10 +7251,10 @@
         </is>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K129" t="n">
-        <v>25</v>
+        <v>53.19148936170212</v>
       </c>
     </row>
     <row r="130">
@@ -7304,10 +7304,10 @@
         </is>
       </c>
       <c r="J130" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K130" t="n">
-        <v>26</v>
+        <v>55.31914893617022</v>
       </c>
     </row>
     <row r="131">
@@ -7357,10 +7357,10 @@
         </is>
       </c>
       <c r="J131" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K131" t="n">
-        <v>29</v>
+        <v>61.70212765957447</v>
       </c>
     </row>
     <row r="132">
@@ -7410,10 +7410,10 @@
         </is>
       </c>
       <c r="J132" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K132" t="n">
-        <v>21</v>
+        <v>44.68085106382978</v>
       </c>
     </row>
     <row r="133">
@@ -7463,10 +7463,10 @@
         </is>
       </c>
       <c r="J133" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K133" t="n">
-        <v>30</v>
+        <v>63.82978723404256</v>
       </c>
     </row>
     <row r="134">
@@ -7516,10 +7516,10 @@
         </is>
       </c>
       <c r="J134" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K134" t="n">
-        <v>34</v>
+        <v>72.3404255319149</v>
       </c>
     </row>
     <row r="135">
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="J135" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K135" t="n">
-        <v>41</v>
+        <v>87.2340425531915</v>
       </c>
     </row>
     <row r="136">
@@ -7622,10 +7622,10 @@
         </is>
       </c>
       <c r="J136" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K136" t="n">
-        <v>29</v>
+        <v>61.70212765957447</v>
       </c>
     </row>
     <row r="137">
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="J137" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K137" t="n">
-        <v>45</v>
+        <v>95.74468085106383</v>
       </c>
     </row>
     <row r="138">
@@ -7728,10 +7728,10 @@
         </is>
       </c>
       <c r="J138" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K138" t="n">
-        <v>44</v>
+        <v>93.61702127659575</v>
       </c>
     </row>
     <row r="139">
@@ -7781,10 +7781,10 @@
         </is>
       </c>
       <c r="J139" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K139" t="n">
-        <v>41</v>
+        <v>87.2340425531915</v>
       </c>
     </row>
     <row r="140">
@@ -7834,10 +7834,10 @@
         </is>
       </c>
       <c r="J140" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K140" t="n">
-        <v>36</v>
+        <v>76.59574468085107</v>
       </c>
     </row>
     <row r="141">
@@ -7887,10 +7887,10 @@
         </is>
       </c>
       <c r="J141" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K141" t="n">
-        <v>32</v>
+        <v>68.08510638297872</v>
       </c>
     </row>
     <row r="142">
@@ -7940,10 +7940,10 @@
         </is>
       </c>
       <c r="J142" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K142" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="143">
@@ -7993,10 +7993,10 @@
         </is>
       </c>
       <c r="J143" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K143" t="n">
-        <v>26</v>
+        <v>55.31914893617022</v>
       </c>
     </row>
     <row r="144">
@@ -8046,10 +8046,10 @@
         </is>
       </c>
       <c r="J144" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K144" t="n">
-        <v>34</v>
+        <v>72.3404255319149</v>
       </c>
     </row>
     <row r="145">
@@ -8102,7 +8102,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>34</v>
+        <v>72.3404255319149</v>
       </c>
     </row>
     <row r="146">
@@ -8152,10 +8152,10 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K146" t="n">
-        <v>37</v>
+        <v>78.72340425531915</v>
       </c>
     </row>
     <row r="147">
@@ -8205,10 +8205,10 @@
         </is>
       </c>
       <c r="J147" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K147" t="n">
-        <v>22</v>
+        <v>46.80851063829788</v>
       </c>
     </row>
     <row r="148">
@@ -8258,10 +8258,10 @@
         </is>
       </c>
       <c r="J148" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K148" t="n">
-        <v>32</v>
+        <v>68.08510638297872</v>
       </c>
     </row>
     <row r="149">
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="J149" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K149" t="n">
-        <v>33</v>
+        <v>70.21276595744681</v>
       </c>
     </row>
     <row r="150">
@@ -8364,10 +8364,10 @@
         </is>
       </c>
       <c r="J150" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K150" t="n">
-        <v>47</v>
+        <v>100</v>
       </c>
     </row>
     <row r="151">
@@ -8417,10 +8417,10 @@
         </is>
       </c>
       <c r="J151" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K151" t="n">
-        <v>25</v>
+        <v>53.19148936170212</v>
       </c>
     </row>
     <row r="152">
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="J152" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K152" t="n">
-        <v>29</v>
+        <v>61.70212765957447</v>
       </c>
     </row>
     <row r="153">
@@ -8523,10 +8523,10 @@
         </is>
       </c>
       <c r="J153" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K153" t="n">
-        <v>23</v>
+        <v>48.93617021276596</v>
       </c>
     </row>
     <row r="154">
@@ -8576,10 +8576,10 @@
         </is>
       </c>
       <c r="J154" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K154" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="155">
@@ -8629,10 +8629,10 @@
         </is>
       </c>
       <c r="J155" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K155" t="n">
-        <v>28</v>
+        <v>59.57446808510638</v>
       </c>
     </row>
     <row r="156">
@@ -8682,10 +8682,10 @@
         </is>
       </c>
       <c r="J156" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K156" t="n">
-        <v>28</v>
+        <v>59.57446808510638</v>
       </c>
     </row>
     <row r="157">
@@ -8735,10 +8735,10 @@
         </is>
       </c>
       <c r="J157" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K157" t="n">
-        <v>33</v>
+        <v>70.21276595744681</v>
       </c>
     </row>
     <row r="158">
@@ -8788,10 +8788,10 @@
         </is>
       </c>
       <c r="J158" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K158" t="n">
-        <v>33</v>
+        <v>70.21276595744681</v>
       </c>
     </row>
     <row r="159">
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K159" t="n">
-        <v>20</v>
+        <v>42.5531914893617</v>
       </c>
     </row>
     <row r="160">
@@ -8894,10 +8894,10 @@
         </is>
       </c>
       <c r="J160" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K160" t="n">
-        <v>22</v>
+        <v>46.80851063829788</v>
       </c>
     </row>
     <row r="161">
@@ -8947,10 +8947,10 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K161" t="n">
-        <v>25</v>
+        <v>53.19148936170212</v>
       </c>
     </row>
     <row r="162">
@@ -9000,10 +9000,10 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K162" t="n">
-        <v>23</v>
+        <v>48.93617021276596</v>
       </c>
     </row>
     <row r="163">
@@ -9053,10 +9053,10 @@
         </is>
       </c>
       <c r="J163" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K163" t="n">
-        <v>41</v>
+        <v>87.2340425531915</v>
       </c>
     </row>
     <row r="164">
@@ -9106,10 +9106,10 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K164" t="n">
-        <v>23</v>
+        <v>48.93617021276596</v>
       </c>
     </row>
     <row r="165">
@@ -9159,10 +9159,10 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K165" t="n">
-        <v>47</v>
+        <v>100</v>
       </c>
     </row>
     <row r="166">
@@ -9212,10 +9212,10 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K166" t="n">
-        <v>27</v>
+        <v>57.44680851063831</v>
       </c>
     </row>
     <row r="167">
@@ -9265,10 +9265,10 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K167" t="n">
-        <v>37</v>
+        <v>78.72340425531915</v>
       </c>
     </row>
     <row r="168">
@@ -9318,10 +9318,10 @@
         </is>
       </c>
       <c r="J168" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K168" t="n">
-        <v>25</v>
+        <v>53.19148936170212</v>
       </c>
     </row>
     <row r="169">
@@ -9374,7 +9374,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="n">
-        <v>27</v>
+        <v>57.44680851063831</v>
       </c>
     </row>
     <row r="170">
@@ -9424,10 +9424,10 @@
         </is>
       </c>
       <c r="J170" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K170" t="n">
-        <v>29</v>
+        <v>61.70212765957447</v>
       </c>
     </row>
     <row r="171">
@@ -9477,10 +9477,10 @@
         </is>
       </c>
       <c r="J171" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K171" t="n">
-        <v>33</v>
+        <v>70.21276595744681</v>
       </c>
     </row>
     <row r="172">
@@ -9530,10 +9530,10 @@
         </is>
       </c>
       <c r="J172" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K172" t="n">
-        <v>36</v>
+        <v>76.59574468085107</v>
       </c>
     </row>
     <row r="173">
@@ -9583,10 +9583,10 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K173" t="n">
-        <v>30</v>
+        <v>63.82978723404256</v>
       </c>
     </row>
     <row r="174">
@@ -9636,10 +9636,10 @@
         </is>
       </c>
       <c r="J174" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K174" t="n">
-        <v>29</v>
+        <v>61.70212765957447</v>
       </c>
     </row>
     <row r="175">
@@ -9689,10 +9689,10 @@
         </is>
       </c>
       <c r="J175" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K175" t="n">
-        <v>31</v>
+        <v>65.95744680851064</v>
       </c>
     </row>
     <row r="176">
@@ -9742,10 +9742,10 @@
         </is>
       </c>
       <c r="J176" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K176" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="177">
@@ -9795,10 +9795,10 @@
         </is>
       </c>
       <c r="J177" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K177" t="n">
-        <v>41</v>
+        <v>87.2340425531915</v>
       </c>
     </row>
     <row r="178">
@@ -9848,10 +9848,10 @@
         </is>
       </c>
       <c r="J178" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K178" t="n">
-        <v>26</v>
+        <v>55.31914893617022</v>
       </c>
     </row>
     <row r="179">
@@ -9901,10 +9901,10 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K179" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="180">
@@ -9954,10 +9954,10 @@
         </is>
       </c>
       <c r="J180" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K180" t="n">
-        <v>33</v>
+        <v>70.21276595744681</v>
       </c>
     </row>
     <row r="181">
@@ -10007,10 +10007,10 @@
         </is>
       </c>
       <c r="J181" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K181" t="n">
-        <v>30</v>
+        <v>63.82978723404256</v>
       </c>
     </row>
     <row r="182">
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K182" t="n">
-        <v>42</v>
+        <v>89.36170212765957</v>
       </c>
     </row>
     <row r="183">
@@ -10113,10 +10113,10 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K183" t="n">
-        <v>14</v>
+        <v>29.78723404255319</v>
       </c>
     </row>
     <row r="184">
@@ -10166,10 +10166,10 @@
         </is>
       </c>
       <c r="J184" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K184" t="n">
-        <v>21</v>
+        <v>44.68085106382978</v>
       </c>
     </row>
     <row r="185">
@@ -10219,10 +10219,10 @@
         </is>
       </c>
       <c r="J185" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K185" t="n">
-        <v>23</v>
+        <v>48.93617021276596</v>
       </c>
     </row>
     <row r="186">
@@ -10272,10 +10272,10 @@
         </is>
       </c>
       <c r="J186" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K186" t="n">
-        <v>27</v>
+        <v>57.44680851063831</v>
       </c>
     </row>
     <row r="187">
@@ -10325,10 +10325,10 @@
         </is>
       </c>
       <c r="J187" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K187" t="n">
-        <v>27</v>
+        <v>57.44680851063831</v>
       </c>
     </row>
     <row r="188">
@@ -10378,10 +10378,10 @@
         </is>
       </c>
       <c r="J188" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K188" t="n">
-        <v>19</v>
+        <v>40.42553191489361</v>
       </c>
     </row>
     <row r="189">
@@ -10431,10 +10431,10 @@
         </is>
       </c>
       <c r="J189" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K189" t="n">
-        <v>22</v>
+        <v>46.80851063829788</v>
       </c>
     </row>
     <row r="190">
@@ -10484,10 +10484,10 @@
         </is>
       </c>
       <c r="J190" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K190" t="n">
-        <v>22</v>
+        <v>46.80851063829788</v>
       </c>
     </row>
     <row r="191">
@@ -10537,10 +10537,10 @@
         </is>
       </c>
       <c r="J191" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K191" t="n">
-        <v>16</v>
+        <v>34.04255319148936</v>
       </c>
     </row>
     <row r="192">
@@ -10590,10 +10590,10 @@
         </is>
       </c>
       <c r="J192" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K192" t="n">
-        <v>23</v>
+        <v>48.93617021276596</v>
       </c>
     </row>
     <row r="193">
@@ -10643,10 +10643,10 @@
         </is>
       </c>
       <c r="J193" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K193" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="194">
@@ -10696,10 +10696,10 @@
         </is>
       </c>
       <c r="J194" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K194" t="n">
-        <v>32</v>
+        <v>68.08510638297872</v>
       </c>
     </row>
     <row r="195">
@@ -10749,10 +10749,10 @@
         </is>
       </c>
       <c r="J195" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K195" t="n">
-        <v>22</v>
+        <v>46.80851063829788</v>
       </c>
     </row>
     <row r="196">
@@ -10802,10 +10802,10 @@
         </is>
       </c>
       <c r="J196" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K196" t="n">
-        <v>23</v>
+        <v>48.93617021276596</v>
       </c>
     </row>
     <row r="197">
@@ -10855,10 +10855,10 @@
         </is>
       </c>
       <c r="J197" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K197" t="n">
-        <v>42</v>
+        <v>89.36170212765957</v>
       </c>
     </row>
     <row r="198">
@@ -10908,10 +10908,10 @@
         </is>
       </c>
       <c r="J198" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K198" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="199">
@@ -10961,10 +10961,10 @@
         </is>
       </c>
       <c r="J199" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K199" t="n">
-        <v>23</v>
+        <v>48.93617021276596</v>
       </c>
     </row>
     <row r="200">
@@ -11014,10 +11014,10 @@
         </is>
       </c>
       <c r="J200" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K200" t="n">
-        <v>25</v>
+        <v>53.19148936170212</v>
       </c>
     </row>
     <row r="201">
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="J201" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K201" t="n">
-        <v>27</v>
+        <v>57.44680851063831</v>
       </c>
     </row>
     <row r="202">
@@ -11120,10 +11120,10 @@
         </is>
       </c>
       <c r="J202" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K202" t="n">
-        <v>29</v>
+        <v>61.70212765957447</v>
       </c>
     </row>
     <row r="203">
@@ -11173,10 +11173,10 @@
         </is>
       </c>
       <c r="J203" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K203" t="n">
-        <v>32</v>
+        <v>68.08510638297872</v>
       </c>
     </row>
     <row r="204">
@@ -11226,10 +11226,10 @@
         </is>
       </c>
       <c r="J204" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K204" t="n">
-        <v>21</v>
+        <v>44.68085106382978</v>
       </c>
     </row>
     <row r="205">
@@ -11282,7 +11282,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="n">
-        <v>18</v>
+        <v>38.29787234042553</v>
       </c>
     </row>
     <row r="206">
@@ -11332,10 +11332,10 @@
         </is>
       </c>
       <c r="J206" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K206" t="n">
-        <v>29</v>
+        <v>61.70212765957447</v>
       </c>
     </row>
     <row r="207">
@@ -11385,10 +11385,10 @@
         </is>
       </c>
       <c r="J207" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K207" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="208">
@@ -11441,7 +11441,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="n">
-        <v>27</v>
+        <v>57.44680851063831</v>
       </c>
     </row>
     <row r="209">
@@ -11491,10 +11491,10 @@
         </is>
       </c>
       <c r="J209" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K209" t="n">
-        <v>23</v>
+        <v>48.93617021276596</v>
       </c>
     </row>
     <row r="210">
@@ -11544,10 +11544,10 @@
         </is>
       </c>
       <c r="J210" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K210" t="n">
-        <v>26</v>
+        <v>55.31914893617022</v>
       </c>
     </row>
     <row r="211">
@@ -11597,10 +11597,10 @@
         </is>
       </c>
       <c r="J211" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K211" t="n">
-        <v>23</v>
+        <v>48.93617021276596</v>
       </c>
     </row>
     <row r="212">
@@ -11650,10 +11650,10 @@
         </is>
       </c>
       <c r="J212" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K212" t="n">
-        <v>36</v>
+        <v>76.59574468085107</v>
       </c>
     </row>
     <row r="213">
@@ -11703,10 +11703,10 @@
         </is>
       </c>
       <c r="J213" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K213" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="214">
@@ -11756,10 +11756,10 @@
         </is>
       </c>
       <c r="J214" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K214" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="215">
@@ -11809,10 +11809,10 @@
         </is>
       </c>
       <c r="J215" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K215" t="n">
-        <v>20</v>
+        <v>42.5531914893617</v>
       </c>
     </row>
     <row r="216">
@@ -11862,10 +11862,10 @@
         </is>
       </c>
       <c r="J216" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K216" t="n">
-        <v>37</v>
+        <v>78.72340425531915</v>
       </c>
     </row>
     <row r="217">
@@ -11915,10 +11915,10 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K217" t="n">
-        <v>38</v>
+        <v>80.85106382978722</v>
       </c>
     </row>
     <row r="218">
@@ -11968,10 +11968,10 @@
         </is>
       </c>
       <c r="J218" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K218" t="n">
-        <v>22</v>
+        <v>46.80851063829788</v>
       </c>
     </row>
     <row r="219">
@@ -12021,10 +12021,10 @@
         </is>
       </c>
       <c r="J219" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K219" t="n">
-        <v>15</v>
+        <v>31.91489361702128</v>
       </c>
     </row>
     <row r="220">
@@ -12074,10 +12074,10 @@
         </is>
       </c>
       <c r="J220" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K220" t="n">
-        <v>45</v>
+        <v>95.74468085106383</v>
       </c>
     </row>
     <row r="221">
@@ -12127,10 +12127,10 @@
         </is>
       </c>
       <c r="J221" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K221" t="n">
-        <v>32</v>
+        <v>68.08510638297872</v>
       </c>
     </row>
     <row r="222">
@@ -12180,10 +12180,10 @@
         </is>
       </c>
       <c r="J222" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K222" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="223">
@@ -12236,7 +12236,7 @@
         <v>0</v>
       </c>
       <c r="K223" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="224">
@@ -12286,10 +12286,10 @@
         </is>
       </c>
       <c r="J224" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K224" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="225">
@@ -12339,10 +12339,10 @@
         </is>
       </c>
       <c r="J225" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K225" t="n">
-        <v>33</v>
+        <v>70.21276595744681</v>
       </c>
     </row>
     <row r="226">
@@ -12392,10 +12392,10 @@
         </is>
       </c>
       <c r="J226" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K226" t="n">
-        <v>23</v>
+        <v>48.93617021276596</v>
       </c>
     </row>
     <row r="227">
@@ -12445,10 +12445,10 @@
         </is>
       </c>
       <c r="J227" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K227" t="n">
-        <v>33</v>
+        <v>70.21276595744681</v>
       </c>
     </row>
     <row r="228">
@@ -12498,10 +12498,10 @@
         </is>
       </c>
       <c r="J228" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K228" t="n">
-        <v>38</v>
+        <v>80.85106382978722</v>
       </c>
     </row>
     <row r="229">
@@ -12551,10 +12551,10 @@
         </is>
       </c>
       <c r="J229" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K229" t="n">
-        <v>39</v>
+        <v>82.97872340425532</v>
       </c>
     </row>
     <row r="230">
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="J230" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K230" t="n">
-        <v>26</v>
+        <v>55.31914893617022</v>
       </c>
     </row>
     <row r="231">
@@ -12657,10 +12657,10 @@
         </is>
       </c>
       <c r="J231" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K231" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="232">
@@ -12710,10 +12710,10 @@
         </is>
       </c>
       <c r="J232" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K232" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="233">
@@ -12763,10 +12763,10 @@
         </is>
       </c>
       <c r="J233" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K233" t="n">
-        <v>33</v>
+        <v>70.21276595744681</v>
       </c>
     </row>
     <row r="234">
@@ -12816,10 +12816,10 @@
         </is>
       </c>
       <c r="J234" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K234" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="235">
@@ -12869,10 +12869,10 @@
         </is>
       </c>
       <c r="J235" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K235" t="n">
-        <v>42</v>
+        <v>89.36170212765957</v>
       </c>
     </row>
     <row r="236">
@@ -12922,10 +12922,10 @@
         </is>
       </c>
       <c r="J236" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K236" t="n">
-        <v>37</v>
+        <v>78.72340425531915</v>
       </c>
     </row>
     <row r="237">
@@ -12975,10 +12975,10 @@
         </is>
       </c>
       <c r="J237" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K237" t="n">
-        <v>15</v>
+        <v>31.91489361702128</v>
       </c>
     </row>
     <row r="238">
@@ -13028,10 +13028,10 @@
         </is>
       </c>
       <c r="J238" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K238" t="n">
-        <v>22</v>
+        <v>46.80851063829788</v>
       </c>
     </row>
     <row r="239">
@@ -13081,10 +13081,10 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K239" t="n">
-        <v>44</v>
+        <v>93.61702127659575</v>
       </c>
     </row>
     <row r="240">
@@ -13134,10 +13134,10 @@
         </is>
       </c>
       <c r="J240" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K240" t="n">
-        <v>23</v>
+        <v>48.93617021276596</v>
       </c>
     </row>
     <row r="241">
@@ -13187,10 +13187,10 @@
         </is>
       </c>
       <c r="J241" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K241" t="n">
-        <v>20</v>
+        <v>42.5531914893617</v>
       </c>
     </row>
     <row r="242">
@@ -13240,10 +13240,10 @@
         </is>
       </c>
       <c r="J242" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K242" t="n">
-        <v>36</v>
+        <v>76.59574468085107</v>
       </c>
     </row>
     <row r="243">
@@ -13293,10 +13293,10 @@
         </is>
       </c>
       <c r="J243" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K243" t="n">
-        <v>42</v>
+        <v>89.36170212765957</v>
       </c>
     </row>
     <row r="244">
@@ -13346,10 +13346,10 @@
         </is>
       </c>
       <c r="J244" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K244" t="n">
-        <v>30</v>
+        <v>63.82978723404256</v>
       </c>
     </row>
     <row r="245">
@@ -13399,10 +13399,10 @@
         </is>
       </c>
       <c r="J245" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K245" t="n">
-        <v>29</v>
+        <v>61.70212765957447</v>
       </c>
     </row>
     <row r="246">
@@ -13452,10 +13452,10 @@
         </is>
       </c>
       <c r="J246" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K246" t="n">
-        <v>22</v>
+        <v>46.80851063829788</v>
       </c>
     </row>
     <row r="247">
@@ -13505,10 +13505,10 @@
         </is>
       </c>
       <c r="J247" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K247" t="n">
-        <v>37</v>
+        <v>78.72340425531915</v>
       </c>
     </row>
     <row r="248">
@@ -13558,10 +13558,10 @@
         </is>
       </c>
       <c r="J248" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K248" t="n">
-        <v>18</v>
+        <v>38.29787234042553</v>
       </c>
     </row>
     <row r="249">
@@ -13611,10 +13611,10 @@
         </is>
       </c>
       <c r="J249" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K249" t="n">
-        <v>38</v>
+        <v>80.85106382978722</v>
       </c>
     </row>
     <row r="250">
@@ -13664,10 +13664,10 @@
         </is>
       </c>
       <c r="J250" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K250" t="n">
-        <v>26</v>
+        <v>55.31914893617022</v>
       </c>
     </row>
     <row r="251">
@@ -13717,10 +13717,10 @@
         </is>
       </c>
       <c r="J251" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K251" t="n">
-        <v>40</v>
+        <v>85.1063829787234</v>
       </c>
     </row>
     <row r="252">
@@ -13770,10 +13770,10 @@
         </is>
       </c>
       <c r="J252" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K252" t="n">
-        <v>36</v>
+        <v>76.59574468085107</v>
       </c>
     </row>
     <row r="253">
@@ -13823,10 +13823,10 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K253" t="n">
-        <v>25</v>
+        <v>53.19148936170212</v>
       </c>
     </row>
     <row r="254">
@@ -13876,10 +13876,10 @@
         </is>
       </c>
       <c r="J254" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K254" t="n">
-        <v>29</v>
+        <v>61.70212765957447</v>
       </c>
     </row>
     <row r="255">
@@ -13929,10 +13929,10 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K255" t="n">
-        <v>41</v>
+        <v>87.2340425531915</v>
       </c>
     </row>
     <row r="256">
@@ -13982,10 +13982,10 @@
         </is>
       </c>
       <c r="J256" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K256" t="n">
-        <v>31</v>
+        <v>65.95744680851064</v>
       </c>
     </row>
     <row r="257">
@@ -14035,10 +14035,10 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K257" t="n">
-        <v>45</v>
+        <v>95.74468085106383</v>
       </c>
     </row>
     <row r="258">
@@ -14088,10 +14088,10 @@
         </is>
       </c>
       <c r="J258" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K258" t="n">
-        <v>34</v>
+        <v>72.3404255319149</v>
       </c>
     </row>
     <row r="259">
@@ -14141,10 +14141,10 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K259" t="n">
-        <v>27</v>
+        <v>57.44680851063831</v>
       </c>
     </row>
     <row r="260">
@@ -14194,10 +14194,10 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K260" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="261">
@@ -14247,10 +14247,10 @@
         </is>
       </c>
       <c r="J261" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K261" t="n">
-        <v>44</v>
+        <v>93.61702127659575</v>
       </c>
     </row>
     <row r="262">
@@ -14300,10 +14300,10 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K262" t="n">
-        <v>30</v>
+        <v>63.82978723404256</v>
       </c>
     </row>
     <row r="263">
@@ -14353,10 +14353,10 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K263" t="n">
-        <v>17</v>
+        <v>36.17021276595745</v>
       </c>
     </row>
     <row r="264">
@@ -14406,10 +14406,10 @@
         </is>
       </c>
       <c r="J264" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K264" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="265">
@@ -14459,10 +14459,10 @@
         </is>
       </c>
       <c r="J265" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K265" t="n">
-        <v>28</v>
+        <v>59.57446808510638</v>
       </c>
     </row>
     <row r="266">
@@ -14512,10 +14512,10 @@
         </is>
       </c>
       <c r="J266" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K266" t="n">
-        <v>18</v>
+        <v>38.29787234042553</v>
       </c>
     </row>
     <row r="267">
@@ -14565,10 +14565,10 @@
         </is>
       </c>
       <c r="J267" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K267" t="n">
-        <v>23</v>
+        <v>48.93617021276596</v>
       </c>
     </row>
     <row r="268">
@@ -14618,10 +14618,10 @@
         </is>
       </c>
       <c r="J268" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K268" t="n">
-        <v>34</v>
+        <v>72.3404255319149</v>
       </c>
     </row>
     <row r="269">
@@ -14671,10 +14671,10 @@
         </is>
       </c>
       <c r="J269" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K269" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="270">
@@ -14724,10 +14724,10 @@
         </is>
       </c>
       <c r="J270" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K270" t="n">
-        <v>33</v>
+        <v>70.21276595744681</v>
       </c>
     </row>
     <row r="271">
@@ -14777,10 +14777,10 @@
         </is>
       </c>
       <c r="J271" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K271" t="n">
-        <v>36</v>
+        <v>76.59574468085107</v>
       </c>
     </row>
     <row r="272">
@@ -14830,10 +14830,10 @@
         </is>
       </c>
       <c r="J272" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K272" t="n">
-        <v>44</v>
+        <v>93.61702127659575</v>
       </c>
     </row>
     <row r="273">
@@ -14883,10 +14883,10 @@
         </is>
       </c>
       <c r="J273" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K273" t="n">
-        <v>31</v>
+        <v>65.95744680851064</v>
       </c>
     </row>
     <row r="274">
@@ -14936,10 +14936,10 @@
         </is>
       </c>
       <c r="J274" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K274" t="n">
-        <v>36</v>
+        <v>76.59574468085107</v>
       </c>
     </row>
     <row r="275">
@@ -14989,10 +14989,10 @@
         </is>
       </c>
       <c r="J275" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K275" t="n">
-        <v>30</v>
+        <v>63.82978723404256</v>
       </c>
     </row>
     <row r="276">
@@ -15042,10 +15042,10 @@
         </is>
       </c>
       <c r="J276" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K276" t="n">
-        <v>33</v>
+        <v>70.21276595744681</v>
       </c>
     </row>
     <row r="277">
@@ -15095,10 +15095,10 @@
         </is>
       </c>
       <c r="J277" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K277" t="n">
-        <v>31</v>
+        <v>65.95744680851064</v>
       </c>
     </row>
     <row r="278">
@@ -15148,10 +15148,10 @@
         </is>
       </c>
       <c r="J278" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K278" t="n">
-        <v>29</v>
+        <v>61.70212765957447</v>
       </c>
     </row>
     <row r="279">
@@ -15201,10 +15201,10 @@
         </is>
       </c>
       <c r="J279" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K279" t="n">
-        <v>39</v>
+        <v>82.97872340425532</v>
       </c>
     </row>
     <row r="280">
@@ -15254,10 +15254,10 @@
         </is>
       </c>
       <c r="J280" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K280" t="n">
-        <v>33</v>
+        <v>70.21276595744681</v>
       </c>
     </row>
     <row r="281">
@@ -15307,10 +15307,10 @@
         </is>
       </c>
       <c r="J281" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K281" t="n">
-        <v>33</v>
+        <v>70.21276595744681</v>
       </c>
     </row>
     <row r="282">
@@ -15360,10 +15360,10 @@
         </is>
       </c>
       <c r="J282" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K282" t="n">
-        <v>32</v>
+        <v>68.08510638297872</v>
       </c>
     </row>
     <row r="283">
@@ -15413,10 +15413,10 @@
         </is>
       </c>
       <c r="J283" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K283" t="n">
-        <v>26</v>
+        <v>55.31914893617022</v>
       </c>
     </row>
     <row r="284">
@@ -15466,10 +15466,10 @@
         </is>
       </c>
       <c r="J284" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K284" t="n">
-        <v>38</v>
+        <v>80.85106382978722</v>
       </c>
     </row>
     <row r="285">
@@ -15519,10 +15519,10 @@
         </is>
       </c>
       <c r="J285" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K285" t="n">
-        <v>15</v>
+        <v>31.91489361702128</v>
       </c>
     </row>
     <row r="286">
@@ -15572,10 +15572,10 @@
         </is>
       </c>
       <c r="J286" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K286" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="287">
@@ -15625,10 +15625,10 @@
         </is>
       </c>
       <c r="J287" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K287" t="n">
-        <v>44</v>
+        <v>93.61702127659575</v>
       </c>
     </row>
     <row r="288">
@@ -15678,10 +15678,10 @@
         </is>
       </c>
       <c r="J288" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K288" t="n">
-        <v>31</v>
+        <v>65.95744680851064</v>
       </c>
     </row>
     <row r="289">
@@ -15731,10 +15731,10 @@
         </is>
       </c>
       <c r="J289" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K289" t="n">
-        <v>32</v>
+        <v>68.08510638297872</v>
       </c>
     </row>
     <row r="290">
@@ -15784,10 +15784,10 @@
         </is>
       </c>
       <c r="J290" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K290" t="n">
-        <v>33</v>
+        <v>70.21276595744681</v>
       </c>
     </row>
     <row r="291">
@@ -15837,10 +15837,10 @@
         </is>
       </c>
       <c r="J291" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K291" t="n">
-        <v>27</v>
+        <v>57.44680851063831</v>
       </c>
     </row>
     <row r="292">
@@ -15890,10 +15890,10 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K292" t="n">
-        <v>20</v>
+        <v>42.5531914893617</v>
       </c>
     </row>
     <row r="293">
@@ -15943,10 +15943,10 @@
         </is>
       </c>
       <c r="J293" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K293" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="294">
@@ -15996,10 +15996,10 @@
         </is>
       </c>
       <c r="J294" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K294" t="n">
-        <v>20</v>
+        <v>42.5531914893617</v>
       </c>
     </row>
     <row r="295">
@@ -16049,10 +16049,10 @@
         </is>
       </c>
       <c r="J295" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K295" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="296">
@@ -16102,10 +16102,10 @@
         </is>
       </c>
       <c r="J296" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K296" t="n">
-        <v>30</v>
+        <v>63.82978723404256</v>
       </c>
     </row>
     <row r="297">
@@ -16155,10 +16155,10 @@
         </is>
       </c>
       <c r="J297" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K297" t="n">
-        <v>30</v>
+        <v>63.82978723404256</v>
       </c>
     </row>
     <row r="298">
@@ -16208,10 +16208,10 @@
         </is>
       </c>
       <c r="J298" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K298" t="n">
-        <v>29</v>
+        <v>61.70212765957447</v>
       </c>
     </row>
     <row r="299">
@@ -16261,10 +16261,10 @@
         </is>
       </c>
       <c r="J299" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K299" t="n">
-        <v>36</v>
+        <v>76.59574468085107</v>
       </c>
     </row>
     <row r="300">
@@ -16314,10 +16314,10 @@
         </is>
       </c>
       <c r="J300" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K300" t="n">
-        <v>25</v>
+        <v>53.19148936170212</v>
       </c>
     </row>
     <row r="301">
@@ -16367,10 +16367,10 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K301" t="n">
-        <v>41</v>
+        <v>87.2340425531915</v>
       </c>
     </row>
     <row r="302">
@@ -16420,10 +16420,10 @@
         </is>
       </c>
       <c r="J302" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K302" t="n">
-        <v>28</v>
+        <v>59.57446808510638</v>
       </c>
     </row>
     <row r="303">
@@ -16473,10 +16473,10 @@
         </is>
       </c>
       <c r="J303" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K303" t="n">
-        <v>29</v>
+        <v>61.70212765957447</v>
       </c>
     </row>
     <row r="304">
@@ -16526,10 +16526,10 @@
         </is>
       </c>
       <c r="J304" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K304" t="n">
-        <v>22</v>
+        <v>46.80851063829788</v>
       </c>
     </row>
     <row r="305">
@@ -16579,10 +16579,10 @@
         </is>
       </c>
       <c r="J305" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K305" t="n">
-        <v>31</v>
+        <v>65.95744680851064</v>
       </c>
     </row>
     <row r="306">
@@ -16632,10 +16632,10 @@
         </is>
       </c>
       <c r="J306" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K306" t="n">
-        <v>26</v>
+        <v>55.31914893617022</v>
       </c>
     </row>
     <row r="307">
@@ -16685,10 +16685,10 @@
         </is>
       </c>
       <c r="J307" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K307" t="n">
-        <v>38</v>
+        <v>80.85106382978722</v>
       </c>
     </row>
     <row r="308">
@@ -16738,10 +16738,10 @@
         </is>
       </c>
       <c r="J308" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K308" t="n">
-        <v>19</v>
+        <v>40.42553191489361</v>
       </c>
     </row>
     <row r="309">
@@ -16791,10 +16791,10 @@
         </is>
       </c>
       <c r="J309" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K309" t="n">
-        <v>44</v>
+        <v>93.61702127659575</v>
       </c>
     </row>
     <row r="310">
@@ -16844,10 +16844,10 @@
         </is>
       </c>
       <c r="J310" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K310" t="n">
-        <v>38</v>
+        <v>80.85106382978722</v>
       </c>
     </row>
     <row r="311">
@@ -16897,10 +16897,10 @@
         </is>
       </c>
       <c r="J311" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K311" t="n">
-        <v>26</v>
+        <v>55.31914893617022</v>
       </c>
     </row>
     <row r="312">
@@ -16950,10 +16950,10 @@
         </is>
       </c>
       <c r="J312" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K312" t="n">
-        <v>45</v>
+        <v>95.74468085106383</v>
       </c>
     </row>
     <row r="313">
@@ -17003,10 +17003,10 @@
         </is>
       </c>
       <c r="J313" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K313" t="n">
-        <v>22</v>
+        <v>46.80851063829788</v>
       </c>
     </row>
     <row r="314">
@@ -17056,10 +17056,10 @@
         </is>
       </c>
       <c r="J314" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K314" t="n">
-        <v>43</v>
+        <v>91.48936170212765</v>
       </c>
     </row>
     <row r="315">
@@ -17109,10 +17109,10 @@
         </is>
       </c>
       <c r="J315" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K315" t="n">
-        <v>21</v>
+        <v>44.68085106382978</v>
       </c>
     </row>
     <row r="316">
@@ -17162,10 +17162,10 @@
         </is>
       </c>
       <c r="J316" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K316" t="n">
-        <v>28</v>
+        <v>59.57446808510638</v>
       </c>
     </row>
     <row r="317">
@@ -17215,10 +17215,10 @@
         </is>
       </c>
       <c r="J317" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K317" t="n">
-        <v>17</v>
+        <v>36.17021276595745</v>
       </c>
     </row>
     <row r="318">
@@ -17268,10 +17268,10 @@
         </is>
       </c>
       <c r="J318" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K318" t="n">
-        <v>28</v>
+        <v>59.57446808510638</v>
       </c>
     </row>
     <row r="319">
@@ -17321,10 +17321,10 @@
         </is>
       </c>
       <c r="J319" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K319" t="n">
-        <v>27</v>
+        <v>57.44680851063831</v>
       </c>
     </row>
     <row r="320">
@@ -17374,10 +17374,10 @@
         </is>
       </c>
       <c r="J320" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K320" t="n">
-        <v>20</v>
+        <v>42.5531914893617</v>
       </c>
     </row>
     <row r="321">
@@ -17427,10 +17427,10 @@
         </is>
       </c>
       <c r="J321" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K321" t="n">
-        <v>41</v>
+        <v>87.2340425531915</v>
       </c>
     </row>
     <row r="322">
@@ -17480,10 +17480,10 @@
         </is>
       </c>
       <c r="J322" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K322" t="n">
-        <v>26</v>
+        <v>55.31914893617022</v>
       </c>
     </row>
     <row r="323">
@@ -17533,10 +17533,10 @@
         </is>
       </c>
       <c r="J323" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K323" t="n">
-        <v>34</v>
+        <v>72.3404255319149</v>
       </c>
     </row>
     <row r="324">
@@ -17586,10 +17586,10 @@
         </is>
       </c>
       <c r="J324" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K324" t="n">
-        <v>36</v>
+        <v>76.59574468085107</v>
       </c>
     </row>
     <row r="325">
@@ -17639,10 +17639,10 @@
         </is>
       </c>
       <c r="J325" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K325" t="n">
-        <v>38</v>
+        <v>80.85106382978722</v>
       </c>
     </row>
     <row r="326">
@@ -17692,10 +17692,10 @@
         </is>
       </c>
       <c r="J326" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K326" t="n">
-        <v>43</v>
+        <v>91.48936170212765</v>
       </c>
     </row>
     <row r="327">
@@ -17745,10 +17745,10 @@
         </is>
       </c>
       <c r="J327" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K327" t="n">
-        <v>26</v>
+        <v>55.31914893617022</v>
       </c>
     </row>
     <row r="328">
@@ -17798,10 +17798,10 @@
         </is>
       </c>
       <c r="J328" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K328" t="n">
-        <v>26</v>
+        <v>55.31914893617022</v>
       </c>
     </row>
     <row r="329">
@@ -17851,10 +17851,10 @@
         </is>
       </c>
       <c r="J329" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K329" t="n">
-        <v>43</v>
+        <v>91.48936170212765</v>
       </c>
     </row>
     <row r="330">
@@ -17904,10 +17904,10 @@
         </is>
       </c>
       <c r="J330" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K330" t="n">
-        <v>21</v>
+        <v>44.68085106382978</v>
       </c>
     </row>
     <row r="331">
@@ -17957,10 +17957,10 @@
         </is>
       </c>
       <c r="J331" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K331" t="n">
-        <v>32</v>
+        <v>68.08510638297872</v>
       </c>
     </row>
     <row r="332">
@@ -18010,10 +18010,10 @@
         </is>
       </c>
       <c r="J332" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K332" t="n">
-        <v>25</v>
+        <v>53.19148936170212</v>
       </c>
     </row>
     <row r="333">
@@ -18063,10 +18063,10 @@
         </is>
       </c>
       <c r="J333" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K333" t="n">
-        <v>23</v>
+        <v>48.93617021276596</v>
       </c>
     </row>
     <row r="334">
@@ -18116,10 +18116,10 @@
         </is>
       </c>
       <c r="J334" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K334" t="n">
-        <v>25</v>
+        <v>53.19148936170212</v>
       </c>
     </row>
     <row r="335">
@@ -18169,10 +18169,10 @@
         </is>
       </c>
       <c r="J335" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K335" t="n">
-        <v>33</v>
+        <v>70.21276595744681</v>
       </c>
     </row>
     <row r="336">
@@ -18222,10 +18222,10 @@
         </is>
       </c>
       <c r="J336" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K336" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="337">
@@ -18275,10 +18275,10 @@
         </is>
       </c>
       <c r="J337" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K337" t="n">
-        <v>20</v>
+        <v>42.5531914893617</v>
       </c>
     </row>
     <row r="338">
@@ -18328,10 +18328,10 @@
         </is>
       </c>
       <c r="J338" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K338" t="n">
-        <v>40</v>
+        <v>85.1063829787234</v>
       </c>
     </row>
     <row r="339">
@@ -18381,10 +18381,10 @@
         </is>
       </c>
       <c r="J339" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K339" t="n">
-        <v>21</v>
+        <v>44.68085106382978</v>
       </c>
     </row>
     <row r="340">
@@ -18434,10 +18434,10 @@
         </is>
       </c>
       <c r="J340" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K340" t="n">
-        <v>31</v>
+        <v>65.95744680851064</v>
       </c>
     </row>
     <row r="341">
@@ -18487,10 +18487,10 @@
         </is>
       </c>
       <c r="J341" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K341" t="n">
-        <v>28</v>
+        <v>59.57446808510638</v>
       </c>
     </row>
     <row r="342">
@@ -18540,10 +18540,10 @@
         </is>
       </c>
       <c r="J342" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K342" t="n">
-        <v>14</v>
+        <v>29.78723404255319</v>
       </c>
     </row>
     <row r="343">
@@ -18593,10 +18593,10 @@
         </is>
       </c>
       <c r="J343" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K343" t="n">
-        <v>26</v>
+        <v>55.31914893617022</v>
       </c>
     </row>
     <row r="344">
@@ -18646,10 +18646,10 @@
         </is>
       </c>
       <c r="J344" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K344" t="n">
-        <v>20</v>
+        <v>42.5531914893617</v>
       </c>
     </row>
     <row r="345">
@@ -18699,10 +18699,10 @@
         </is>
       </c>
       <c r="J345" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K345" t="n">
-        <v>37</v>
+        <v>78.72340425531915</v>
       </c>
     </row>
     <row r="346">
@@ -18752,10 +18752,10 @@
         </is>
       </c>
       <c r="J346" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K346" t="n">
-        <v>37</v>
+        <v>78.72340425531915</v>
       </c>
     </row>
     <row r="347">
@@ -18805,10 +18805,10 @@
         </is>
       </c>
       <c r="J347" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K347" t="n">
-        <v>36</v>
+        <v>76.59574468085107</v>
       </c>
     </row>
     <row r="348">
@@ -18858,10 +18858,10 @@
         </is>
       </c>
       <c r="J348" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K348" t="n">
-        <v>20</v>
+        <v>42.5531914893617</v>
       </c>
     </row>
     <row r="349">
@@ -18911,10 +18911,10 @@
         </is>
       </c>
       <c r="J349" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K349" t="n">
-        <v>23</v>
+        <v>48.93617021276596</v>
       </c>
     </row>
     <row r="350">
@@ -18964,10 +18964,10 @@
         </is>
       </c>
       <c r="J350" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K350" t="n">
-        <v>37</v>
+        <v>78.72340425531915</v>
       </c>
     </row>
     <row r="351">
@@ -19017,10 +19017,10 @@
         </is>
       </c>
       <c r="J351" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K351" t="n">
-        <v>30</v>
+        <v>63.82978723404256</v>
       </c>
     </row>
     <row r="352">
@@ -19070,10 +19070,10 @@
         </is>
       </c>
       <c r="J352" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K352" t="n">
-        <v>21</v>
+        <v>44.68085106382978</v>
       </c>
     </row>
     <row r="353">
@@ -19123,10 +19123,10 @@
         </is>
       </c>
       <c r="J353" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K353" t="n">
-        <v>25</v>
+        <v>53.19148936170212</v>
       </c>
     </row>
     <row r="354">
@@ -19176,10 +19176,10 @@
         </is>
       </c>
       <c r="J354" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K354" t="n">
-        <v>25</v>
+        <v>53.19148936170212</v>
       </c>
     </row>
     <row r="355">
@@ -19229,10 +19229,10 @@
         </is>
       </c>
       <c r="J355" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K355" t="n">
-        <v>26</v>
+        <v>55.31914893617022</v>
       </c>
     </row>
     <row r="356">
@@ -19282,10 +19282,10 @@
         </is>
       </c>
       <c r="J356" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K356" t="n">
-        <v>37</v>
+        <v>78.72340425531915</v>
       </c>
     </row>
     <row r="357">
@@ -19335,10 +19335,10 @@
         </is>
       </c>
       <c r="J357" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K357" t="n">
-        <v>45</v>
+        <v>95.74468085106383</v>
       </c>
     </row>
     <row r="358">
@@ -19388,10 +19388,10 @@
         </is>
       </c>
       <c r="J358" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K358" t="n">
-        <v>27</v>
+        <v>57.44680851063831</v>
       </c>
     </row>
     <row r="359">
@@ -19441,10 +19441,10 @@
         </is>
       </c>
       <c r="J359" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K359" t="n">
-        <v>22</v>
+        <v>46.80851063829788</v>
       </c>
     </row>
     <row r="360">
@@ -19494,10 +19494,10 @@
         </is>
       </c>
       <c r="J360" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K360" t="n">
-        <v>26</v>
+        <v>55.31914893617022</v>
       </c>
     </row>
     <row r="361">
@@ -19547,10 +19547,10 @@
         </is>
       </c>
       <c r="J361" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K361" t="n">
-        <v>31</v>
+        <v>65.95744680851064</v>
       </c>
     </row>
     <row r="362">
@@ -19600,10 +19600,10 @@
         </is>
       </c>
       <c r="J362" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K362" t="n">
-        <v>33</v>
+        <v>70.21276595744681</v>
       </c>
     </row>
     <row r="363">
@@ -19653,10 +19653,10 @@
         </is>
       </c>
       <c r="J363" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K363" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="364">
@@ -19706,10 +19706,10 @@
         </is>
       </c>
       <c r="J364" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K364" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="365">
@@ -19759,10 +19759,10 @@
         </is>
       </c>
       <c r="J365" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K365" t="n">
-        <v>34</v>
+        <v>72.3404255319149</v>
       </c>
     </row>
     <row r="366">
@@ -19812,10 +19812,10 @@
         </is>
       </c>
       <c r="J366" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K366" t="n">
-        <v>21</v>
+        <v>44.68085106382978</v>
       </c>
     </row>
     <row r="367">
@@ -19865,10 +19865,10 @@
         </is>
       </c>
       <c r="J367" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K367" t="n">
-        <v>29</v>
+        <v>61.70212765957447</v>
       </c>
     </row>
     <row r="368">
@@ -19918,10 +19918,10 @@
         </is>
       </c>
       <c r="J368" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K368" t="n">
-        <v>25</v>
+        <v>53.19148936170212</v>
       </c>
     </row>
     <row r="369">
@@ -19971,10 +19971,10 @@
         </is>
       </c>
       <c r="J369" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K369" t="n">
-        <v>37</v>
+        <v>78.72340425531915</v>
       </c>
     </row>
     <row r="370">
@@ -20024,10 +20024,10 @@
         </is>
       </c>
       <c r="J370" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K370" t="n">
-        <v>26</v>
+        <v>55.31914893617022</v>
       </c>
     </row>
     <row r="371">
@@ -20077,10 +20077,10 @@
         </is>
       </c>
       <c r="J371" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K371" t="n">
-        <v>45</v>
+        <v>95.74468085106383</v>
       </c>
     </row>
     <row r="372">
@@ -20130,10 +20130,10 @@
         </is>
       </c>
       <c r="J372" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K372" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="373">
@@ -20183,10 +20183,10 @@
         </is>
       </c>
       <c r="J373" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K373" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="374">
@@ -20236,10 +20236,10 @@
         </is>
       </c>
       <c r="J374" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K374" t="n">
-        <v>30</v>
+        <v>63.82978723404256</v>
       </c>
     </row>
     <row r="375">
@@ -20289,10 +20289,10 @@
         </is>
       </c>
       <c r="J375" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K375" t="n">
-        <v>41</v>
+        <v>87.2340425531915</v>
       </c>
     </row>
     <row r="376">
@@ -20342,10 +20342,10 @@
         </is>
       </c>
       <c r="J376" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K376" t="n">
-        <v>17</v>
+        <v>36.17021276595745</v>
       </c>
     </row>
     <row r="377">
@@ -20395,10 +20395,10 @@
         </is>
       </c>
       <c r="J377" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K377" t="n">
-        <v>34</v>
+        <v>72.3404255319149</v>
       </c>
     </row>
     <row r="378">
@@ -20448,10 +20448,10 @@
         </is>
       </c>
       <c r="J378" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K378" t="n">
-        <v>13</v>
+        <v>27.65957446808511</v>
       </c>
     </row>
     <row r="379">
@@ -20501,10 +20501,10 @@
         </is>
       </c>
       <c r="J379" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K379" t="n">
-        <v>18</v>
+        <v>38.29787234042553</v>
       </c>
     </row>
     <row r="380">
@@ -20554,10 +20554,10 @@
         </is>
       </c>
       <c r="J380" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K380" t="n">
-        <v>40</v>
+        <v>85.1063829787234</v>
       </c>
     </row>
     <row r="381">
@@ -20607,10 +20607,10 @@
         </is>
       </c>
       <c r="J381" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K381" t="n">
-        <v>21</v>
+        <v>44.68085106382978</v>
       </c>
     </row>
     <row r="382">
@@ -20660,10 +20660,10 @@
         </is>
       </c>
       <c r="J382" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K382" t="n">
-        <v>37</v>
+        <v>78.72340425531915</v>
       </c>
     </row>
     <row r="383">
@@ -20713,10 +20713,10 @@
         </is>
       </c>
       <c r="J383" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K383" t="n">
-        <v>32</v>
+        <v>68.08510638297872</v>
       </c>
     </row>
     <row r="384">
@@ -20766,10 +20766,10 @@
         </is>
       </c>
       <c r="J384" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K384" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="385">
@@ -20819,10 +20819,10 @@
         </is>
       </c>
       <c r="J385" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K385" t="n">
-        <v>37</v>
+        <v>78.72340425531915</v>
       </c>
     </row>
     <row r="386">
@@ -20872,10 +20872,10 @@
         </is>
       </c>
       <c r="J386" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K386" t="n">
-        <v>23</v>
+        <v>48.93617021276596</v>
       </c>
     </row>
     <row r="387">
@@ -20925,10 +20925,10 @@
         </is>
       </c>
       <c r="J387" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K387" t="n">
-        <v>32</v>
+        <v>68.08510638297872</v>
       </c>
     </row>
     <row r="388">
@@ -20978,10 +20978,10 @@
         </is>
       </c>
       <c r="J388" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K388" t="n">
-        <v>19</v>
+        <v>40.42553191489361</v>
       </c>
     </row>
     <row r="389">
@@ -21031,10 +21031,10 @@
         </is>
       </c>
       <c r="J389" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K389" t="n">
-        <v>25</v>
+        <v>53.19148936170212</v>
       </c>
     </row>
     <row r="390">
@@ -21084,10 +21084,10 @@
         </is>
       </c>
       <c r="J390" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K390" t="n">
-        <v>37</v>
+        <v>78.72340425531915</v>
       </c>
     </row>
     <row r="391">
@@ -21137,10 +21137,10 @@
         </is>
       </c>
       <c r="J391" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K391" t="n">
-        <v>46</v>
+        <v>97.87234042553192</v>
       </c>
     </row>
     <row r="392">
@@ -21190,10 +21190,10 @@
         </is>
       </c>
       <c r="J392" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K392" t="n">
-        <v>22</v>
+        <v>46.80851063829788</v>
       </c>
     </row>
     <row r="393">
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="J393" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K393" t="n">
-        <v>27</v>
+        <v>57.44680851063831</v>
       </c>
     </row>
     <row r="394">
@@ -21296,10 +21296,10 @@
         </is>
       </c>
       <c r="J394" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K394" t="n">
-        <v>37</v>
+        <v>78.72340425531915</v>
       </c>
     </row>
     <row r="395">
@@ -21349,10 +21349,10 @@
         </is>
       </c>
       <c r="J395" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K395" t="n">
-        <v>29</v>
+        <v>61.70212765957447</v>
       </c>
     </row>
     <row r="396">
@@ -21402,10 +21402,10 @@
         </is>
       </c>
       <c r="J396" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K396" t="n">
-        <v>43</v>
+        <v>91.48936170212765</v>
       </c>
     </row>
     <row r="397">
@@ -21455,10 +21455,10 @@
         </is>
       </c>
       <c r="J397" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K397" t="n">
-        <v>23</v>
+        <v>48.93617021276596</v>
       </c>
     </row>
     <row r="398">
@@ -21508,10 +21508,10 @@
         </is>
       </c>
       <c r="J398" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K398" t="n">
-        <v>32</v>
+        <v>68.08510638297872</v>
       </c>
     </row>
     <row r="399">
@@ -21561,10 +21561,10 @@
         </is>
       </c>
       <c r="J399" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K399" t="n">
-        <v>40</v>
+        <v>85.1063829787234</v>
       </c>
     </row>
     <row r="400">
@@ -21614,10 +21614,10 @@
         </is>
       </c>
       <c r="J400" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K400" t="n">
-        <v>27</v>
+        <v>57.44680851063831</v>
       </c>
     </row>
     <row r="401">
@@ -21667,10 +21667,10 @@
         </is>
       </c>
       <c r="J401" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K401" t="n">
-        <v>46</v>
+        <v>97.87234042553192</v>
       </c>
     </row>
     <row r="402">
@@ -21720,10 +21720,10 @@
         </is>
       </c>
       <c r="J402" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K402" t="n">
-        <v>20</v>
+        <v>42.5531914893617</v>
       </c>
     </row>
     <row r="403">
@@ -21773,10 +21773,10 @@
         </is>
       </c>
       <c r="J403" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K403" t="n">
-        <v>29</v>
+        <v>61.70212765957447</v>
       </c>
     </row>
     <row r="404">
@@ -21826,10 +21826,10 @@
         </is>
       </c>
       <c r="J404" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K404" t="n">
-        <v>44</v>
+        <v>93.61702127659575</v>
       </c>
     </row>
     <row r="405">
@@ -21879,10 +21879,10 @@
         </is>
       </c>
       <c r="J405" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K405" t="n">
-        <v>37</v>
+        <v>78.72340425531915</v>
       </c>
     </row>
     <row r="406">
@@ -21932,10 +21932,10 @@
         </is>
       </c>
       <c r="J406" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K406" t="n">
-        <v>20</v>
+        <v>42.5531914893617</v>
       </c>
     </row>
     <row r="407">
@@ -21985,10 +21985,10 @@
         </is>
       </c>
       <c r="J407" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K407" t="n">
-        <v>23</v>
+        <v>48.93617021276596</v>
       </c>
     </row>
     <row r="408">
@@ -22038,10 +22038,10 @@
         </is>
       </c>
       <c r="J408" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K408" t="n">
-        <v>31</v>
+        <v>65.95744680851064</v>
       </c>
     </row>
     <row r="409">
@@ -22091,10 +22091,10 @@
         </is>
       </c>
       <c r="J409" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K409" t="n">
-        <v>45</v>
+        <v>95.74468085106383</v>
       </c>
     </row>
     <row r="410">
@@ -22144,10 +22144,10 @@
         </is>
       </c>
       <c r="J410" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K410" t="n">
-        <v>42</v>
+        <v>89.36170212765957</v>
       </c>
     </row>
     <row r="411">
@@ -22197,10 +22197,10 @@
         </is>
       </c>
       <c r="J411" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K411" t="n">
-        <v>21</v>
+        <v>44.68085106382978</v>
       </c>
     </row>
     <row r="412">
@@ -22250,10 +22250,10 @@
         </is>
       </c>
       <c r="J412" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K412" t="n">
-        <v>13</v>
+        <v>27.65957446808511</v>
       </c>
     </row>
     <row r="413">
@@ -22303,10 +22303,10 @@
         </is>
       </c>
       <c r="J413" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K413" t="n">
-        <v>37</v>
+        <v>78.72340425531915</v>
       </c>
     </row>
     <row r="414">
@@ -22356,10 +22356,10 @@
         </is>
       </c>
       <c r="J414" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K414" t="n">
-        <v>20</v>
+        <v>42.5531914893617</v>
       </c>
     </row>
     <row r="415">
@@ -22409,10 +22409,10 @@
         </is>
       </c>
       <c r="J415" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K415" t="n">
-        <v>20</v>
+        <v>42.5531914893617</v>
       </c>
     </row>
     <row r="416">
@@ -22462,10 +22462,10 @@
         </is>
       </c>
       <c r="J416" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K416" t="n">
-        <v>41</v>
+        <v>87.2340425531915</v>
       </c>
     </row>
     <row r="417">
@@ -22515,10 +22515,10 @@
         </is>
       </c>
       <c r="J417" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K417" t="n">
-        <v>23</v>
+        <v>48.93617021276596</v>
       </c>
     </row>
     <row r="418">
@@ -22568,10 +22568,10 @@
         </is>
       </c>
       <c r="J418" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K418" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="419">
@@ -22621,10 +22621,10 @@
         </is>
       </c>
       <c r="J419" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K419" t="n">
-        <v>27</v>
+        <v>57.44680851063831</v>
       </c>
     </row>
     <row r="420">
@@ -22674,10 +22674,10 @@
         </is>
       </c>
       <c r="J420" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K420" t="n">
-        <v>36</v>
+        <v>76.59574468085107</v>
       </c>
     </row>
     <row r="421">
@@ -22727,10 +22727,10 @@
         </is>
       </c>
       <c r="J421" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K421" t="n">
-        <v>44</v>
+        <v>93.61702127659575</v>
       </c>
     </row>
     <row r="422">
@@ -22780,10 +22780,10 @@
         </is>
       </c>
       <c r="J422" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K422" t="n">
-        <v>29</v>
+        <v>61.70212765957447</v>
       </c>
     </row>
     <row r="423">
@@ -22833,10 +22833,10 @@
         </is>
       </c>
       <c r="J423" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K423" t="n">
-        <v>19</v>
+        <v>40.42553191489361</v>
       </c>
     </row>
     <row r="424">
@@ -22886,10 +22886,10 @@
         </is>
       </c>
       <c r="J424" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K424" t="n">
-        <v>38</v>
+        <v>80.85106382978722</v>
       </c>
     </row>
     <row r="425">
@@ -22939,10 +22939,10 @@
         </is>
       </c>
       <c r="J425" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K425" t="n">
-        <v>28</v>
+        <v>59.57446808510638</v>
       </c>
     </row>
     <row r="426">
@@ -22992,10 +22992,10 @@
         </is>
       </c>
       <c r="J426" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K426" t="n">
-        <v>34</v>
+        <v>72.3404255319149</v>
       </c>
     </row>
     <row r="427">
@@ -23045,10 +23045,10 @@
         </is>
       </c>
       <c r="J427" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K427" t="n">
-        <v>39</v>
+        <v>82.97872340425532</v>
       </c>
     </row>
     <row r="428">
@@ -23098,10 +23098,10 @@
         </is>
       </c>
       <c r="J428" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K428" t="n">
-        <v>25</v>
+        <v>53.19148936170212</v>
       </c>
     </row>
     <row r="429">
@@ -23154,7 +23154,7 @@
         <v>0</v>
       </c>
       <c r="K429" t="n">
-        <v>29</v>
+        <v>61.70212765957447</v>
       </c>
     </row>
     <row r="430">
@@ -23204,10 +23204,10 @@
         </is>
       </c>
       <c r="J430" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K430" t="n">
-        <v>38</v>
+        <v>80.85106382978722</v>
       </c>
     </row>
     <row r="431">
@@ -23257,10 +23257,10 @@
         </is>
       </c>
       <c r="J431" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K431" t="n">
-        <v>21</v>
+        <v>44.68085106382978</v>
       </c>
     </row>
     <row r="432">
@@ -23310,10 +23310,10 @@
         </is>
       </c>
       <c r="J432" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K432" t="n">
-        <v>29</v>
+        <v>61.70212765957447</v>
       </c>
     </row>
     <row r="433">
@@ -23363,10 +23363,10 @@
         </is>
       </c>
       <c r="J433" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K433" t="n">
-        <v>16</v>
+        <v>34.04255319148936</v>
       </c>
     </row>
     <row r="434">
@@ -23416,10 +23416,10 @@
         </is>
       </c>
       <c r="J434" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K434" t="n">
-        <v>40</v>
+        <v>85.1063829787234</v>
       </c>
     </row>
     <row r="435">
@@ -23469,10 +23469,10 @@
         </is>
       </c>
       <c r="J435" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K435" t="n">
-        <v>29</v>
+        <v>61.70212765957447</v>
       </c>
     </row>
     <row r="436">
@@ -23522,10 +23522,10 @@
         </is>
       </c>
       <c r="J436" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K436" t="n">
-        <v>39</v>
+        <v>82.97872340425532</v>
       </c>
     </row>
     <row r="437">
@@ -23575,10 +23575,10 @@
         </is>
       </c>
       <c r="J437" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K437" t="n">
-        <v>31</v>
+        <v>65.95744680851064</v>
       </c>
     </row>
     <row r="438">
@@ -23628,10 +23628,10 @@
         </is>
       </c>
       <c r="J438" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K438" t="n">
-        <v>35</v>
+        <v>74.46808510638297</v>
       </c>
     </row>
     <row r="439">
@@ -23681,10 +23681,10 @@
         </is>
       </c>
       <c r="J439" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K439" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="440">
@@ -23734,10 +23734,10 @@
         </is>
       </c>
       <c r="J440" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K440" t="n">
-        <v>24</v>
+        <v>51.06382978723404</v>
       </c>
     </row>
     <row r="441">
@@ -23787,10 +23787,10 @@
         </is>
       </c>
       <c r="J441" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K441" t="n">
-        <v>19</v>
+        <v>40.42553191489361</v>
       </c>
     </row>
     <row r="442">
@@ -23840,10 +23840,10 @@
         </is>
       </c>
       <c r="J442" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K442" t="n">
-        <v>27</v>
+        <v>57.44680851063831</v>
       </c>
     </row>
     <row r="443">
@@ -23893,10 +23893,10 @@
         </is>
       </c>
       <c r="J443" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K443" t="n">
-        <v>38</v>
+        <v>80.85106382978722</v>
       </c>
     </row>
     <row r="444">
@@ -23946,10 +23946,10 @@
         </is>
       </c>
       <c r="J444" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="K444" t="n">
-        <v>28</v>
+        <v>59.57446808510638</v>
       </c>
     </row>
   </sheetData>

--- a/output/df_estudiantes_final.xlsx
+++ b/output/df_estudiantes_final.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K444"/>
+  <dimension ref="A1:M444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,10 +464,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>Indice_Conocimiento</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Indice_Conocimiento_Norm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Indice_Prevencion</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>Indice_Prevencion_Norm</t>
         </is>
@@ -520,9 +530,15 @@
         </is>
       </c>
       <c r="J2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2" t="n">
         <v>80</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
+        <v>36</v>
+      </c>
+      <c r="M2" t="n">
         <v>76.59574468085107</v>
       </c>
     </row>
@@ -573,9 +589,15 @@
         </is>
       </c>
       <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
         <v>80</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
+        <v>46</v>
+      </c>
+      <c r="M3" t="n">
         <v>97.87234042553192</v>
       </c>
     </row>
@@ -626,9 +648,15 @@
         </is>
       </c>
       <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
         <v>100</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
+        <v>46</v>
+      </c>
+      <c r="M4" t="n">
         <v>97.87234042553192</v>
       </c>
     </row>
@@ -679,9 +707,15 @@
         </is>
       </c>
       <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
         <v>100</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
+        <v>36</v>
+      </c>
+      <c r="M5" t="n">
         <v>76.59574468085107</v>
       </c>
     </row>
@@ -732,9 +766,15 @@
         </is>
       </c>
       <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="n">
         <v>100</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
+        <v>25</v>
+      </c>
+      <c r="M6" t="n">
         <v>53.19148936170212</v>
       </c>
     </row>
@@ -785,9 +825,15 @@
         </is>
       </c>
       <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
         <v>60</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
+        <v>31</v>
+      </c>
+      <c r="M7" t="n">
         <v>65.95744680851064</v>
       </c>
     </row>
@@ -838,9 +884,15 @@
         </is>
       </c>
       <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
         <v>100</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
+        <v>39</v>
+      </c>
+      <c r="M8" t="n">
         <v>82.97872340425532</v>
       </c>
     </row>
@@ -891,9 +943,15 @@
         </is>
       </c>
       <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
         <v>40</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
+        <v>35</v>
+      </c>
+      <c r="M9" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -944,9 +1002,15 @@
         </is>
       </c>
       <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
         <v>100</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
+        <v>44</v>
+      </c>
+      <c r="M10" t="n">
         <v>93.61702127659575</v>
       </c>
     </row>
@@ -997,11 +1061,17 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
         <v>100</v>
       </c>
+      <c r="L11" t="n">
+        <v>47</v>
+      </c>
+      <c r="M11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1050,9 +1120,15 @@
         </is>
       </c>
       <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
         <v>80</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
+        <v>35</v>
+      </c>
+      <c r="M12" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -1103,9 +1179,15 @@
         </is>
       </c>
       <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
         <v>40</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
+        <v>24</v>
+      </c>
+      <c r="M13" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -1156,9 +1238,15 @@
         </is>
       </c>
       <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
         <v>40</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
+        <v>47</v>
+      </c>
+      <c r="M14" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1209,9 +1297,15 @@
         </is>
       </c>
       <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
         <v>80</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
+        <v>35</v>
+      </c>
+      <c r="M15" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -1262,9 +1356,15 @@
         </is>
       </c>
       <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
         <v>80</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
+        <v>31</v>
+      </c>
+      <c r="M16" t="n">
         <v>65.95744680851064</v>
       </c>
     </row>
@@ -1315,9 +1415,15 @@
         </is>
       </c>
       <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
         <v>80</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
+        <v>26</v>
+      </c>
+      <c r="M17" t="n">
         <v>55.31914893617022</v>
       </c>
     </row>
@@ -1368,9 +1474,15 @@
         </is>
       </c>
       <c r="J18" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" t="n">
         <v>80</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
+        <v>35</v>
+      </c>
+      <c r="M18" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -1421,9 +1533,15 @@
         </is>
       </c>
       <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
         <v>40</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
+        <v>26</v>
+      </c>
+      <c r="M19" t="n">
         <v>55.31914893617022</v>
       </c>
     </row>
@@ -1474,9 +1592,15 @@
         </is>
       </c>
       <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="n">
         <v>100</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
+        <v>41</v>
+      </c>
+      <c r="M20" t="n">
         <v>87.2340425531915</v>
       </c>
     </row>
@@ -1527,9 +1651,15 @@
         </is>
       </c>
       <c r="J21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" t="n">
         <v>80</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
+        <v>41</v>
+      </c>
+      <c r="M21" t="n">
         <v>87.2340425531915</v>
       </c>
     </row>
@@ -1580,9 +1710,15 @@
         </is>
       </c>
       <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
         <v>20</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
+        <v>14</v>
+      </c>
+      <c r="M22" t="n">
         <v>29.78723404255319</v>
       </c>
     </row>
@@ -1633,9 +1769,15 @@
         </is>
       </c>
       <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
         <v>60</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
+        <v>25</v>
+      </c>
+      <c r="M23" t="n">
         <v>53.19148936170212</v>
       </c>
     </row>
@@ -1686,9 +1828,15 @@
         </is>
       </c>
       <c r="J24" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" t="n">
         <v>80</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
+        <v>24</v>
+      </c>
+      <c r="M24" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -1739,9 +1887,15 @@
         </is>
       </c>
       <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
         <v>60</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
+        <v>41</v>
+      </c>
+      <c r="M25" t="n">
         <v>87.2340425531915</v>
       </c>
     </row>
@@ -1792,9 +1946,15 @@
         </is>
       </c>
       <c r="J26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" t="n">
         <v>100</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
+        <v>34</v>
+      </c>
+      <c r="M26" t="n">
         <v>72.3404255319149</v>
       </c>
     </row>
@@ -1845,9 +2005,15 @@
         </is>
       </c>
       <c r="J27" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" t="n">
         <v>60</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
+        <v>25</v>
+      </c>
+      <c r="M27" t="n">
         <v>53.19148936170212</v>
       </c>
     </row>
@@ -1898,9 +2064,15 @@
         </is>
       </c>
       <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
         <v>40</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
+        <v>37</v>
+      </c>
+      <c r="M28" t="n">
         <v>78.72340425531915</v>
       </c>
     </row>
@@ -1951,9 +2123,15 @@
         </is>
       </c>
       <c r="J29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" t="n">
         <v>100</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
+        <v>44</v>
+      </c>
+      <c r="M29" t="n">
         <v>93.61702127659575</v>
       </c>
     </row>
@@ -2004,9 +2182,15 @@
         </is>
       </c>
       <c r="J30" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" t="n">
         <v>100</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
+        <v>26</v>
+      </c>
+      <c r="M30" t="n">
         <v>55.31914893617022</v>
       </c>
     </row>
@@ -2057,9 +2241,15 @@
         </is>
       </c>
       <c r="J31" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" t="n">
         <v>80</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
+        <v>43</v>
+      </c>
+      <c r="M31" t="n">
         <v>91.48936170212765</v>
       </c>
     </row>
@@ -2110,9 +2300,15 @@
         </is>
       </c>
       <c r="J32" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" t="n">
         <v>80</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
+        <v>43</v>
+      </c>
+      <c r="M32" t="n">
         <v>91.48936170212765</v>
       </c>
     </row>
@@ -2163,9 +2359,15 @@
         </is>
       </c>
       <c r="J33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" t="n">
         <v>40</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
+        <v>31</v>
+      </c>
+      <c r="M33" t="n">
         <v>65.95744680851064</v>
       </c>
     </row>
@@ -2216,9 +2418,15 @@
         </is>
       </c>
       <c r="J34" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" t="n">
         <v>60</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
+        <v>23</v>
+      </c>
+      <c r="M34" t="n">
         <v>48.93617021276596</v>
       </c>
     </row>
@@ -2269,9 +2477,15 @@
         </is>
       </c>
       <c r="J35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" t="n">
         <v>100</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
+        <v>39</v>
+      </c>
+      <c r="M35" t="n">
         <v>82.97872340425532</v>
       </c>
     </row>
@@ -2322,9 +2536,15 @@
         </is>
       </c>
       <c r="J36" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" t="n">
         <v>60</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
+        <v>24</v>
+      </c>
+      <c r="M36" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -2375,9 +2595,15 @@
         </is>
       </c>
       <c r="J37" t="n">
+        <v>4</v>
+      </c>
+      <c r="K37" t="n">
         <v>80</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
+        <v>36</v>
+      </c>
+      <c r="M37" t="n">
         <v>76.59574468085107</v>
       </c>
     </row>
@@ -2428,9 +2654,15 @@
         </is>
       </c>
       <c r="J38" t="n">
+        <v>5</v>
+      </c>
+      <c r="K38" t="n">
         <v>100</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
+        <v>45</v>
+      </c>
+      <c r="M38" t="n">
         <v>95.74468085106383</v>
       </c>
     </row>
@@ -2481,9 +2713,15 @@
         </is>
       </c>
       <c r="J39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K39" t="n">
         <v>100</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
+        <v>43</v>
+      </c>
+      <c r="M39" t="n">
         <v>91.48936170212765</v>
       </c>
     </row>
@@ -2534,9 +2772,15 @@
         </is>
       </c>
       <c r="J40" t="n">
+        <v>4</v>
+      </c>
+      <c r="K40" t="n">
         <v>80</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
+        <v>43</v>
+      </c>
+      <c r="M40" t="n">
         <v>91.48936170212765</v>
       </c>
     </row>
@@ -2587,9 +2831,15 @@
         </is>
       </c>
       <c r="J41" t="n">
+        <v>4</v>
+      </c>
+      <c r="K41" t="n">
         <v>80</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
+        <v>32</v>
+      </c>
+      <c r="M41" t="n">
         <v>68.08510638297872</v>
       </c>
     </row>
@@ -2640,9 +2890,15 @@
         </is>
       </c>
       <c r="J42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" t="n">
         <v>100</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
+        <v>35</v>
+      </c>
+      <c r="M42" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -2693,9 +2949,15 @@
         </is>
       </c>
       <c r="J43" t="n">
+        <v>5</v>
+      </c>
+      <c r="K43" t="n">
         <v>100</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
+        <v>40</v>
+      </c>
+      <c r="M43" t="n">
         <v>85.1063829787234</v>
       </c>
     </row>
@@ -2746,9 +3008,15 @@
         </is>
       </c>
       <c r="J44" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" t="n">
         <v>100</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
+        <v>45</v>
+      </c>
+      <c r="M44" t="n">
         <v>95.74468085106383</v>
       </c>
     </row>
@@ -2799,9 +3067,15 @@
         </is>
       </c>
       <c r="J45" t="n">
+        <v>4</v>
+      </c>
+      <c r="K45" t="n">
         <v>80</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
+        <v>34</v>
+      </c>
+      <c r="M45" t="n">
         <v>72.3404255319149</v>
       </c>
     </row>
@@ -2852,9 +3126,15 @@
         </is>
       </c>
       <c r="J46" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" t="n">
         <v>100</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
+        <v>39</v>
+      </c>
+      <c r="M46" t="n">
         <v>82.97872340425532</v>
       </c>
     </row>
@@ -2905,9 +3185,15 @@
         </is>
       </c>
       <c r="J47" t="n">
+        <v>5</v>
+      </c>
+      <c r="K47" t="n">
         <v>100</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
+        <v>31</v>
+      </c>
+      <c r="M47" t="n">
         <v>65.95744680851064</v>
       </c>
     </row>
@@ -2958,9 +3244,15 @@
         </is>
       </c>
       <c r="J48" t="n">
+        <v>5</v>
+      </c>
+      <c r="K48" t="n">
         <v>100</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
+        <v>40</v>
+      </c>
+      <c r="M48" t="n">
         <v>85.1063829787234</v>
       </c>
     </row>
@@ -3011,9 +3303,15 @@
         </is>
       </c>
       <c r="J49" t="n">
+        <v>4</v>
+      </c>
+      <c r="K49" t="n">
         <v>80</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
+        <v>37</v>
+      </c>
+      <c r="M49" t="n">
         <v>78.72340425531915</v>
       </c>
     </row>
@@ -3064,9 +3362,15 @@
         </is>
       </c>
       <c r="J50" t="n">
+        <v>3</v>
+      </c>
+      <c r="K50" t="n">
         <v>60</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
+        <v>28</v>
+      </c>
+      <c r="M50" t="n">
         <v>59.57446808510638</v>
       </c>
     </row>
@@ -3117,9 +3421,15 @@
         </is>
       </c>
       <c r="J51" t="n">
+        <v>3</v>
+      </c>
+      <c r="K51" t="n">
         <v>60</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
+        <v>42</v>
+      </c>
+      <c r="M51" t="n">
         <v>89.36170212765957</v>
       </c>
     </row>
@@ -3170,9 +3480,15 @@
         </is>
       </c>
       <c r="J52" t="n">
+        <v>3</v>
+      </c>
+      <c r="K52" t="n">
         <v>60</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
+        <v>25</v>
+      </c>
+      <c r="M52" t="n">
         <v>53.19148936170212</v>
       </c>
     </row>
@@ -3223,9 +3539,15 @@
         </is>
       </c>
       <c r="J53" t="n">
+        <v>4</v>
+      </c>
+      <c r="K53" t="n">
         <v>80</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
+        <v>39</v>
+      </c>
+      <c r="M53" t="n">
         <v>82.97872340425532</v>
       </c>
     </row>
@@ -3276,9 +3598,15 @@
         </is>
       </c>
       <c r="J54" t="n">
+        <v>4</v>
+      </c>
+      <c r="K54" t="n">
         <v>80</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
+        <v>45</v>
+      </c>
+      <c r="M54" t="n">
         <v>95.74468085106383</v>
       </c>
     </row>
@@ -3329,9 +3657,15 @@
         </is>
       </c>
       <c r="J55" t="n">
+        <v>4</v>
+      </c>
+      <c r="K55" t="n">
         <v>80</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
+        <v>27</v>
+      </c>
+      <c r="M55" t="n">
         <v>57.44680851063831</v>
       </c>
     </row>
@@ -3382,9 +3716,15 @@
         </is>
       </c>
       <c r="J56" t="n">
+        <v>2</v>
+      </c>
+      <c r="K56" t="n">
         <v>40</v>
       </c>
-      <c r="K56" t="n">
+      <c r="L56" t="n">
+        <v>20</v>
+      </c>
+      <c r="M56" t="n">
         <v>42.5531914893617</v>
       </c>
     </row>
@@ -3435,9 +3775,15 @@
         </is>
       </c>
       <c r="J57" t="n">
+        <v>3</v>
+      </c>
+      <c r="K57" t="n">
         <v>60</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
+        <v>45</v>
+      </c>
+      <c r="M57" t="n">
         <v>95.74468085106383</v>
       </c>
     </row>
@@ -3488,9 +3834,15 @@
         </is>
       </c>
       <c r="J58" t="n">
+        <v>3</v>
+      </c>
+      <c r="K58" t="n">
         <v>60</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
+        <v>45</v>
+      </c>
+      <c r="M58" t="n">
         <v>95.74468085106383</v>
       </c>
     </row>
@@ -3541,9 +3893,15 @@
         </is>
       </c>
       <c r="J59" t="n">
+        <v>4</v>
+      </c>
+      <c r="K59" t="n">
         <v>80</v>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
+        <v>32</v>
+      </c>
+      <c r="M59" t="n">
         <v>68.08510638297872</v>
       </c>
     </row>
@@ -3594,9 +3952,15 @@
         </is>
       </c>
       <c r="J60" t="n">
+        <v>2</v>
+      </c>
+      <c r="K60" t="n">
         <v>40</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
+        <v>42</v>
+      </c>
+      <c r="M60" t="n">
         <v>89.36170212765957</v>
       </c>
     </row>
@@ -3647,9 +4011,15 @@
         </is>
       </c>
       <c r="J61" t="n">
+        <v>5</v>
+      </c>
+      <c r="K61" t="n">
         <v>100</v>
       </c>
-      <c r="K61" t="n">
+      <c r="L61" t="n">
+        <v>36</v>
+      </c>
+      <c r="M61" t="n">
         <v>76.59574468085107</v>
       </c>
     </row>
@@ -3700,9 +4070,15 @@
         </is>
       </c>
       <c r="J62" t="n">
+        <v>4</v>
+      </c>
+      <c r="K62" t="n">
         <v>80</v>
       </c>
-      <c r="K62" t="n">
+      <c r="L62" t="n">
+        <v>34</v>
+      </c>
+      <c r="M62" t="n">
         <v>72.3404255319149</v>
       </c>
     </row>
@@ -3753,9 +4129,15 @@
         </is>
       </c>
       <c r="J63" t="n">
+        <v>5</v>
+      </c>
+      <c r="K63" t="n">
         <v>100</v>
       </c>
-      <c r="K63" t="n">
+      <c r="L63" t="n">
+        <v>42</v>
+      </c>
+      <c r="M63" t="n">
         <v>89.36170212765957</v>
       </c>
     </row>
@@ -3806,9 +4188,15 @@
         </is>
       </c>
       <c r="J64" t="n">
+        <v>5</v>
+      </c>
+      <c r="K64" t="n">
         <v>100</v>
       </c>
-      <c r="K64" t="n">
+      <c r="L64" t="n">
+        <v>36</v>
+      </c>
+      <c r="M64" t="n">
         <v>76.59574468085107</v>
       </c>
     </row>
@@ -3859,9 +4247,15 @@
         </is>
       </c>
       <c r="J65" t="n">
+        <v>5</v>
+      </c>
+      <c r="K65" t="n">
         <v>100</v>
       </c>
-      <c r="K65" t="n">
+      <c r="L65" t="n">
+        <v>39</v>
+      </c>
+      <c r="M65" t="n">
         <v>82.97872340425532</v>
       </c>
     </row>
@@ -3912,9 +4306,15 @@
         </is>
       </c>
       <c r="J66" t="n">
+        <v>5</v>
+      </c>
+      <c r="K66" t="n">
         <v>100</v>
       </c>
-      <c r="K66" t="n">
+      <c r="L66" t="n">
+        <v>28</v>
+      </c>
+      <c r="M66" t="n">
         <v>59.57446808510638</v>
       </c>
     </row>
@@ -3965,9 +4365,15 @@
         </is>
       </c>
       <c r="J67" t="n">
+        <v>4</v>
+      </c>
+      <c r="K67" t="n">
         <v>80</v>
       </c>
-      <c r="K67" t="n">
+      <c r="L67" t="n">
+        <v>30</v>
+      </c>
+      <c r="M67" t="n">
         <v>63.82978723404256</v>
       </c>
     </row>
@@ -4018,9 +4424,15 @@
         </is>
       </c>
       <c r="J68" t="n">
+        <v>4</v>
+      </c>
+      <c r="K68" t="n">
         <v>80</v>
       </c>
-      <c r="K68" t="n">
+      <c r="L68" t="n">
+        <v>24</v>
+      </c>
+      <c r="M68" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -4071,9 +4483,15 @@
         </is>
       </c>
       <c r="J69" t="n">
+        <v>5</v>
+      </c>
+      <c r="K69" t="n">
         <v>100</v>
       </c>
-      <c r="K69" t="n">
+      <c r="L69" t="n">
+        <v>32</v>
+      </c>
+      <c r="M69" t="n">
         <v>68.08510638297872</v>
       </c>
     </row>
@@ -4124,9 +4542,15 @@
         </is>
       </c>
       <c r="J70" t="n">
+        <v>2</v>
+      </c>
+      <c r="K70" t="n">
         <v>40</v>
       </c>
-      <c r="K70" t="n">
+      <c r="L70" t="n">
+        <v>22</v>
+      </c>
+      <c r="M70" t="n">
         <v>46.80851063829788</v>
       </c>
     </row>
@@ -4177,9 +4601,15 @@
         </is>
       </c>
       <c r="J71" t="n">
+        <v>4</v>
+      </c>
+      <c r="K71" t="n">
         <v>80</v>
       </c>
-      <c r="K71" t="n">
+      <c r="L71" t="n">
+        <v>26</v>
+      </c>
+      <c r="M71" t="n">
         <v>55.31914893617022</v>
       </c>
     </row>
@@ -4230,9 +4660,15 @@
         </is>
       </c>
       <c r="J72" t="n">
+        <v>4</v>
+      </c>
+      <c r="K72" t="n">
         <v>80</v>
       </c>
-      <c r="K72" t="n">
+      <c r="L72" t="n">
+        <v>25</v>
+      </c>
+      <c r="M72" t="n">
         <v>53.19148936170212</v>
       </c>
     </row>
@@ -4283,9 +4719,15 @@
         </is>
       </c>
       <c r="J73" t="n">
+        <v>3</v>
+      </c>
+      <c r="K73" t="n">
         <v>60</v>
       </c>
-      <c r="K73" t="n">
+      <c r="L73" t="n">
+        <v>22</v>
+      </c>
+      <c r="M73" t="n">
         <v>46.80851063829788</v>
       </c>
     </row>
@@ -4336,9 +4778,15 @@
         </is>
       </c>
       <c r="J74" t="n">
+        <v>3</v>
+      </c>
+      <c r="K74" t="n">
         <v>60</v>
       </c>
-      <c r="K74" t="n">
+      <c r="L74" t="n">
+        <v>32</v>
+      </c>
+      <c r="M74" t="n">
         <v>68.08510638297872</v>
       </c>
     </row>
@@ -4389,9 +4837,15 @@
         </is>
       </c>
       <c r="J75" t="n">
+        <v>3</v>
+      </c>
+      <c r="K75" t="n">
         <v>60</v>
       </c>
-      <c r="K75" t="n">
+      <c r="L75" t="n">
+        <v>34</v>
+      </c>
+      <c r="M75" t="n">
         <v>72.3404255319149</v>
       </c>
     </row>
@@ -4442,9 +4896,15 @@
         </is>
       </c>
       <c r="J76" t="n">
+        <v>5</v>
+      </c>
+      <c r="K76" t="n">
         <v>100</v>
       </c>
-      <c r="K76" t="n">
+      <c r="L76" t="n">
+        <v>33</v>
+      </c>
+      <c r="M76" t="n">
         <v>70.21276595744681</v>
       </c>
     </row>
@@ -4495,9 +4955,15 @@
         </is>
       </c>
       <c r="J77" t="n">
+        <v>3</v>
+      </c>
+      <c r="K77" t="n">
         <v>60</v>
       </c>
-      <c r="K77" t="n">
+      <c r="L77" t="n">
+        <v>27</v>
+      </c>
+      <c r="M77" t="n">
         <v>57.44680851063831</v>
       </c>
     </row>
@@ -4548,9 +5014,15 @@
         </is>
       </c>
       <c r="J78" t="n">
+        <v>3</v>
+      </c>
+      <c r="K78" t="n">
         <v>60</v>
       </c>
-      <c r="K78" t="n">
+      <c r="L78" t="n">
+        <v>21</v>
+      </c>
+      <c r="M78" t="n">
         <v>44.68085106382978</v>
       </c>
     </row>
@@ -4601,9 +5073,15 @@
         </is>
       </c>
       <c r="J79" t="n">
+        <v>3</v>
+      </c>
+      <c r="K79" t="n">
         <v>60</v>
       </c>
-      <c r="K79" t="n">
+      <c r="L79" t="n">
+        <v>18</v>
+      </c>
+      <c r="M79" t="n">
         <v>38.29787234042553</v>
       </c>
     </row>
@@ -4654,9 +5132,15 @@
         </is>
       </c>
       <c r="J80" t="n">
+        <v>4</v>
+      </c>
+      <c r="K80" t="n">
         <v>80</v>
       </c>
-      <c r="K80" t="n">
+      <c r="L80" t="n">
+        <v>21</v>
+      </c>
+      <c r="M80" t="n">
         <v>44.68085106382978</v>
       </c>
     </row>
@@ -4707,9 +5191,15 @@
         </is>
       </c>
       <c r="J81" t="n">
+        <v>3</v>
+      </c>
+      <c r="K81" t="n">
         <v>60</v>
       </c>
-      <c r="K81" t="n">
+      <c r="L81" t="n">
+        <v>24</v>
+      </c>
+      <c r="M81" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -4760,9 +5250,15 @@
         </is>
       </c>
       <c r="J82" t="n">
+        <v>4</v>
+      </c>
+      <c r="K82" t="n">
         <v>80</v>
       </c>
-      <c r="K82" t="n">
+      <c r="L82" t="n">
+        <v>18</v>
+      </c>
+      <c r="M82" t="n">
         <v>38.29787234042553</v>
       </c>
     </row>
@@ -4813,9 +5309,15 @@
         </is>
       </c>
       <c r="J83" t="n">
+        <v>4</v>
+      </c>
+      <c r="K83" t="n">
         <v>80</v>
       </c>
-      <c r="K83" t="n">
+      <c r="L83" t="n">
+        <v>20</v>
+      </c>
+      <c r="M83" t="n">
         <v>42.5531914893617</v>
       </c>
     </row>
@@ -4866,9 +5368,15 @@
         </is>
       </c>
       <c r="J84" t="n">
+        <v>4</v>
+      </c>
+      <c r="K84" t="n">
         <v>80</v>
       </c>
-      <c r="K84" t="n">
+      <c r="L84" t="n">
+        <v>22</v>
+      </c>
+      <c r="M84" t="n">
         <v>46.80851063829788</v>
       </c>
     </row>
@@ -4919,9 +5427,15 @@
         </is>
       </c>
       <c r="J85" t="n">
+        <v>4</v>
+      </c>
+      <c r="K85" t="n">
         <v>80</v>
       </c>
-      <c r="K85" t="n">
+      <c r="L85" t="n">
+        <v>24</v>
+      </c>
+      <c r="M85" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -4972,9 +5486,15 @@
         </is>
       </c>
       <c r="J86" t="n">
+        <v>4</v>
+      </c>
+      <c r="K86" t="n">
         <v>80</v>
       </c>
-      <c r="K86" t="n">
+      <c r="L86" t="n">
+        <v>20</v>
+      </c>
+      <c r="M86" t="n">
         <v>42.5531914893617</v>
       </c>
     </row>
@@ -5025,9 +5545,15 @@
         </is>
       </c>
       <c r="J87" t="n">
+        <v>3</v>
+      </c>
+      <c r="K87" t="n">
         <v>60</v>
       </c>
-      <c r="K87" t="n">
+      <c r="L87" t="n">
+        <v>22</v>
+      </c>
+      <c r="M87" t="n">
         <v>46.80851063829788</v>
       </c>
     </row>
@@ -5078,9 +5604,15 @@
         </is>
       </c>
       <c r="J88" t="n">
+        <v>3</v>
+      </c>
+      <c r="K88" t="n">
         <v>60</v>
       </c>
-      <c r="K88" t="n">
+      <c r="L88" t="n">
+        <v>21</v>
+      </c>
+      <c r="M88" t="n">
         <v>44.68085106382978</v>
       </c>
     </row>
@@ -5131,9 +5663,15 @@
         </is>
       </c>
       <c r="J89" t="n">
+        <v>4</v>
+      </c>
+      <c r="K89" t="n">
         <v>80</v>
       </c>
-      <c r="K89" t="n">
+      <c r="L89" t="n">
+        <v>33</v>
+      </c>
+      <c r="M89" t="n">
         <v>70.21276595744681</v>
       </c>
     </row>
@@ -5184,9 +5722,15 @@
         </is>
       </c>
       <c r="J90" t="n">
+        <v>4</v>
+      </c>
+      <c r="K90" t="n">
         <v>80</v>
       </c>
-      <c r="K90" t="n">
+      <c r="L90" t="n">
+        <v>27</v>
+      </c>
+      <c r="M90" t="n">
         <v>57.44680851063831</v>
       </c>
     </row>
@@ -5237,9 +5781,15 @@
         </is>
       </c>
       <c r="J91" t="n">
+        <v>3</v>
+      </c>
+      <c r="K91" t="n">
         <v>60</v>
       </c>
-      <c r="K91" t="n">
+      <c r="L91" t="n">
+        <v>27</v>
+      </c>
+      <c r="M91" t="n">
         <v>57.44680851063831</v>
       </c>
     </row>
@@ -5290,9 +5840,15 @@
         </is>
       </c>
       <c r="J92" t="n">
+        <v>4</v>
+      </c>
+      <c r="K92" t="n">
         <v>80</v>
       </c>
-      <c r="K92" t="n">
+      <c r="L92" t="n">
+        <v>39</v>
+      </c>
+      <c r="M92" t="n">
         <v>82.97872340425532</v>
       </c>
     </row>
@@ -5343,9 +5899,15 @@
         </is>
       </c>
       <c r="J93" t="n">
+        <v>5</v>
+      </c>
+      <c r="K93" t="n">
         <v>100</v>
       </c>
-      <c r="K93" t="n">
+      <c r="L93" t="n">
+        <v>22</v>
+      </c>
+      <c r="M93" t="n">
         <v>46.80851063829788</v>
       </c>
     </row>
@@ -5396,9 +5958,15 @@
         </is>
       </c>
       <c r="J94" t="n">
+        <v>4</v>
+      </c>
+      <c r="K94" t="n">
         <v>80</v>
       </c>
-      <c r="K94" t="n">
+      <c r="L94" t="n">
+        <v>18</v>
+      </c>
+      <c r="M94" t="n">
         <v>38.29787234042553</v>
       </c>
     </row>
@@ -5449,9 +6017,15 @@
         </is>
       </c>
       <c r="J95" t="n">
+        <v>2</v>
+      </c>
+      <c r="K95" t="n">
         <v>40</v>
       </c>
-      <c r="K95" t="n">
+      <c r="L95" t="n">
+        <v>31</v>
+      </c>
+      <c r="M95" t="n">
         <v>65.95744680851064</v>
       </c>
     </row>
@@ -5502,9 +6076,15 @@
         </is>
       </c>
       <c r="J96" t="n">
+        <v>3</v>
+      </c>
+      <c r="K96" t="n">
         <v>60</v>
       </c>
-      <c r="K96" t="n">
+      <c r="L96" t="n">
+        <v>30</v>
+      </c>
+      <c r="M96" t="n">
         <v>63.82978723404256</v>
       </c>
     </row>
@@ -5555,9 +6135,15 @@
         </is>
       </c>
       <c r="J97" t="n">
+        <v>2</v>
+      </c>
+      <c r="K97" t="n">
         <v>40</v>
       </c>
-      <c r="K97" t="n">
+      <c r="L97" t="n">
+        <v>28</v>
+      </c>
+      <c r="M97" t="n">
         <v>59.57446808510638</v>
       </c>
     </row>
@@ -5608,9 +6194,15 @@
         </is>
       </c>
       <c r="J98" t="n">
+        <v>3</v>
+      </c>
+      <c r="K98" t="n">
         <v>60</v>
       </c>
-      <c r="K98" t="n">
+      <c r="L98" t="n">
+        <v>22</v>
+      </c>
+      <c r="M98" t="n">
         <v>46.80851063829788</v>
       </c>
     </row>
@@ -5661,9 +6253,15 @@
         </is>
       </c>
       <c r="J99" t="n">
+        <v>3</v>
+      </c>
+      <c r="K99" t="n">
         <v>60</v>
       </c>
-      <c r="K99" t="n">
+      <c r="L99" t="n">
+        <v>19</v>
+      </c>
+      <c r="M99" t="n">
         <v>40.42553191489361</v>
       </c>
     </row>
@@ -5717,6 +6315,12 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>23</v>
+      </c>
+      <c r="M100" t="n">
         <v>48.93617021276596</v>
       </c>
     </row>
@@ -5767,9 +6371,15 @@
         </is>
       </c>
       <c r="J101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K101" t="n">
         <v>20</v>
       </c>
-      <c r="K101" t="n">
+      <c r="L101" t="n">
+        <v>33</v>
+      </c>
+      <c r="M101" t="n">
         <v>70.21276595744681</v>
       </c>
     </row>
@@ -5820,9 +6430,15 @@
         </is>
       </c>
       <c r="J102" t="n">
+        <v>1</v>
+      </c>
+      <c r="K102" t="n">
         <v>20</v>
       </c>
-      <c r="K102" t="n">
+      <c r="L102" t="n">
+        <v>29</v>
+      </c>
+      <c r="M102" t="n">
         <v>61.70212765957447</v>
       </c>
     </row>
@@ -5873,9 +6489,15 @@
         </is>
       </c>
       <c r="J103" t="n">
+        <v>1</v>
+      </c>
+      <c r="K103" t="n">
         <v>20</v>
       </c>
-      <c r="K103" t="n">
+      <c r="L103" t="n">
+        <v>34</v>
+      </c>
+      <c r="M103" t="n">
         <v>72.3404255319149</v>
       </c>
     </row>
@@ -5929,6 +6551,12 @@
         <v>0</v>
       </c>
       <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>35</v>
+      </c>
+      <c r="M104" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -5979,9 +6607,15 @@
         </is>
       </c>
       <c r="J105" t="n">
+        <v>2</v>
+      </c>
+      <c r="K105" t="n">
         <v>40</v>
       </c>
-      <c r="K105" t="n">
+      <c r="L105" t="n">
+        <v>19</v>
+      </c>
+      <c r="M105" t="n">
         <v>40.42553191489361</v>
       </c>
     </row>
@@ -6032,9 +6666,15 @@
         </is>
       </c>
       <c r="J106" t="n">
+        <v>3</v>
+      </c>
+      <c r="K106" t="n">
         <v>60</v>
       </c>
-      <c r="K106" t="n">
+      <c r="L106" t="n">
+        <v>34</v>
+      </c>
+      <c r="M106" t="n">
         <v>72.3404255319149</v>
       </c>
     </row>
@@ -6085,9 +6725,15 @@
         </is>
       </c>
       <c r="J107" t="n">
+        <v>2</v>
+      </c>
+      <c r="K107" t="n">
         <v>40</v>
       </c>
-      <c r="K107" t="n">
+      <c r="L107" t="n">
+        <v>20</v>
+      </c>
+      <c r="M107" t="n">
         <v>42.5531914893617</v>
       </c>
     </row>
@@ -6138,9 +6784,15 @@
         </is>
       </c>
       <c r="J108" t="n">
+        <v>2</v>
+      </c>
+      <c r="K108" t="n">
         <v>40</v>
       </c>
-      <c r="K108" t="n">
+      <c r="L108" t="n">
+        <v>24</v>
+      </c>
+      <c r="M108" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -6191,9 +6843,15 @@
         </is>
       </c>
       <c r="J109" t="n">
+        <v>1</v>
+      </c>
+      <c r="K109" t="n">
         <v>20</v>
       </c>
-      <c r="K109" t="n">
+      <c r="L109" t="n">
+        <v>44</v>
+      </c>
+      <c r="M109" t="n">
         <v>93.61702127659575</v>
       </c>
     </row>
@@ -6244,9 +6902,15 @@
         </is>
       </c>
       <c r="J110" t="n">
+        <v>2</v>
+      </c>
+      <c r="K110" t="n">
         <v>40</v>
       </c>
-      <c r="K110" t="n">
+      <c r="L110" t="n">
+        <v>41</v>
+      </c>
+      <c r="M110" t="n">
         <v>87.2340425531915</v>
       </c>
     </row>
@@ -6297,9 +6961,15 @@
         </is>
       </c>
       <c r="J111" t="n">
+        <v>2</v>
+      </c>
+      <c r="K111" t="n">
         <v>40</v>
       </c>
-      <c r="K111" t="n">
+      <c r="L111" t="n">
+        <v>40</v>
+      </c>
+      <c r="M111" t="n">
         <v>85.1063829787234</v>
       </c>
     </row>
@@ -6350,9 +7020,15 @@
         </is>
       </c>
       <c r="J112" t="n">
+        <v>2</v>
+      </c>
+      <c r="K112" t="n">
         <v>40</v>
       </c>
-      <c r="K112" t="n">
+      <c r="L112" t="n">
+        <v>40</v>
+      </c>
+      <c r="M112" t="n">
         <v>85.1063829787234</v>
       </c>
     </row>
@@ -6403,9 +7079,15 @@
         </is>
       </c>
       <c r="J113" t="n">
+        <v>2</v>
+      </c>
+      <c r="K113" t="n">
         <v>40</v>
       </c>
-      <c r="K113" t="n">
+      <c r="L113" t="n">
+        <v>34</v>
+      </c>
+      <c r="M113" t="n">
         <v>72.3404255319149</v>
       </c>
     </row>
@@ -6456,9 +7138,15 @@
         </is>
       </c>
       <c r="J114" t="n">
+        <v>1</v>
+      </c>
+      <c r="K114" t="n">
         <v>20</v>
       </c>
-      <c r="K114" t="n">
+      <c r="L114" t="n">
+        <v>30</v>
+      </c>
+      <c r="M114" t="n">
         <v>63.82978723404256</v>
       </c>
     </row>
@@ -6509,9 +7197,15 @@
         </is>
       </c>
       <c r="J115" t="n">
+        <v>2</v>
+      </c>
+      <c r="K115" t="n">
         <v>40</v>
       </c>
-      <c r="K115" t="n">
+      <c r="L115" t="n">
+        <v>22</v>
+      </c>
+      <c r="M115" t="n">
         <v>46.80851063829788</v>
       </c>
     </row>
@@ -6562,9 +7256,15 @@
         </is>
       </c>
       <c r="J116" t="n">
+        <v>1</v>
+      </c>
+      <c r="K116" t="n">
         <v>20</v>
       </c>
-      <c r="K116" t="n">
+      <c r="L116" t="n">
+        <v>24</v>
+      </c>
+      <c r="M116" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -6615,9 +7315,15 @@
         </is>
       </c>
       <c r="J117" t="n">
+        <v>2</v>
+      </c>
+      <c r="K117" t="n">
         <v>40</v>
       </c>
-      <c r="K117" t="n">
+      <c r="L117" t="n">
+        <v>28</v>
+      </c>
+      <c r="M117" t="n">
         <v>59.57446808510638</v>
       </c>
     </row>
@@ -6668,9 +7374,15 @@
         </is>
       </c>
       <c r="J118" t="n">
+        <v>1</v>
+      </c>
+      <c r="K118" t="n">
         <v>20</v>
       </c>
-      <c r="K118" t="n">
+      <c r="L118" t="n">
+        <v>35</v>
+      </c>
+      <c r="M118" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -6721,9 +7433,15 @@
         </is>
       </c>
       <c r="J119" t="n">
+        <v>2</v>
+      </c>
+      <c r="K119" t="n">
         <v>40</v>
       </c>
-      <c r="K119" t="n">
+      <c r="L119" t="n">
+        <v>26</v>
+      </c>
+      <c r="M119" t="n">
         <v>55.31914893617022</v>
       </c>
     </row>
@@ -6774,9 +7492,15 @@
         </is>
       </c>
       <c r="J120" t="n">
+        <v>2</v>
+      </c>
+      <c r="K120" t="n">
         <v>40</v>
       </c>
-      <c r="K120" t="n">
+      <c r="L120" t="n">
+        <v>22</v>
+      </c>
+      <c r="M120" t="n">
         <v>46.80851063829788</v>
       </c>
     </row>
@@ -6827,9 +7551,15 @@
         </is>
       </c>
       <c r="J121" t="n">
+        <v>3</v>
+      </c>
+      <c r="K121" t="n">
         <v>60</v>
       </c>
-      <c r="K121" t="n">
+      <c r="L121" t="n">
+        <v>37</v>
+      </c>
+      <c r="M121" t="n">
         <v>78.72340425531915</v>
       </c>
     </row>
@@ -6880,9 +7610,15 @@
         </is>
       </c>
       <c r="J122" t="n">
+        <v>5</v>
+      </c>
+      <c r="K122" t="n">
         <v>100</v>
       </c>
-      <c r="K122" t="n">
+      <c r="L122" t="n">
+        <v>35</v>
+      </c>
+      <c r="M122" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -6933,9 +7669,15 @@
         </is>
       </c>
       <c r="J123" t="n">
+        <v>2</v>
+      </c>
+      <c r="K123" t="n">
         <v>40</v>
       </c>
-      <c r="K123" t="n">
+      <c r="L123" t="n">
+        <v>32</v>
+      </c>
+      <c r="M123" t="n">
         <v>68.08510638297872</v>
       </c>
     </row>
@@ -6986,9 +7728,15 @@
         </is>
       </c>
       <c r="J124" t="n">
+        <v>4</v>
+      </c>
+      <c r="K124" t="n">
         <v>80</v>
       </c>
-      <c r="K124" t="n">
+      <c r="L124" t="n">
+        <v>32</v>
+      </c>
+      <c r="M124" t="n">
         <v>68.08510638297872</v>
       </c>
     </row>
@@ -7039,9 +7787,15 @@
         </is>
       </c>
       <c r="J125" t="n">
+        <v>2</v>
+      </c>
+      <c r="K125" t="n">
         <v>40</v>
       </c>
-      <c r="K125" t="n">
+      <c r="L125" t="n">
+        <v>27</v>
+      </c>
+      <c r="M125" t="n">
         <v>57.44680851063831</v>
       </c>
     </row>
@@ -7092,9 +7846,15 @@
         </is>
       </c>
       <c r="J126" t="n">
+        <v>4</v>
+      </c>
+      <c r="K126" t="n">
         <v>80</v>
       </c>
-      <c r="K126" t="n">
+      <c r="L126" t="n">
+        <v>24</v>
+      </c>
+      <c r="M126" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -7145,9 +7905,15 @@
         </is>
       </c>
       <c r="J127" t="n">
+        <v>2</v>
+      </c>
+      <c r="K127" t="n">
         <v>40</v>
       </c>
-      <c r="K127" t="n">
+      <c r="L127" t="n">
+        <v>37</v>
+      </c>
+      <c r="M127" t="n">
         <v>78.72340425531915</v>
       </c>
     </row>
@@ -7198,9 +7964,15 @@
         </is>
       </c>
       <c r="J128" t="n">
+        <v>4</v>
+      </c>
+      <c r="K128" t="n">
         <v>80</v>
       </c>
-      <c r="K128" t="n">
+      <c r="L128" t="n">
+        <v>31</v>
+      </c>
+      <c r="M128" t="n">
         <v>65.95744680851064</v>
       </c>
     </row>
@@ -7251,9 +8023,15 @@
         </is>
       </c>
       <c r="J129" t="n">
+        <v>1</v>
+      </c>
+      <c r="K129" t="n">
         <v>20</v>
       </c>
-      <c r="K129" t="n">
+      <c r="L129" t="n">
+        <v>25</v>
+      </c>
+      <c r="M129" t="n">
         <v>53.19148936170212</v>
       </c>
     </row>
@@ -7304,9 +8082,15 @@
         </is>
       </c>
       <c r="J130" t="n">
+        <v>5</v>
+      </c>
+      <c r="K130" t="n">
         <v>100</v>
       </c>
-      <c r="K130" t="n">
+      <c r="L130" t="n">
+        <v>26</v>
+      </c>
+      <c r="M130" t="n">
         <v>55.31914893617022</v>
       </c>
     </row>
@@ -7357,9 +8141,15 @@
         </is>
       </c>
       <c r="J131" t="n">
+        <v>3</v>
+      </c>
+      <c r="K131" t="n">
         <v>60</v>
       </c>
-      <c r="K131" t="n">
+      <c r="L131" t="n">
+        <v>29</v>
+      </c>
+      <c r="M131" t="n">
         <v>61.70212765957447</v>
       </c>
     </row>
@@ -7410,9 +8200,15 @@
         </is>
       </c>
       <c r="J132" t="n">
+        <v>5</v>
+      </c>
+      <c r="K132" t="n">
         <v>100</v>
       </c>
-      <c r="K132" t="n">
+      <c r="L132" t="n">
+        <v>21</v>
+      </c>
+      <c r="M132" t="n">
         <v>44.68085106382978</v>
       </c>
     </row>
@@ -7463,9 +8259,15 @@
         </is>
       </c>
       <c r="J133" t="n">
+        <v>3</v>
+      </c>
+      <c r="K133" t="n">
         <v>60</v>
       </c>
-      <c r="K133" t="n">
+      <c r="L133" t="n">
+        <v>30</v>
+      </c>
+      <c r="M133" t="n">
         <v>63.82978723404256</v>
       </c>
     </row>
@@ -7516,9 +8318,15 @@
         </is>
       </c>
       <c r="J134" t="n">
+        <v>4</v>
+      </c>
+      <c r="K134" t="n">
         <v>80</v>
       </c>
-      <c r="K134" t="n">
+      <c r="L134" t="n">
+        <v>34</v>
+      </c>
+      <c r="M134" t="n">
         <v>72.3404255319149</v>
       </c>
     </row>
@@ -7569,9 +8377,15 @@
         </is>
       </c>
       <c r="J135" t="n">
+        <v>4</v>
+      </c>
+      <c r="K135" t="n">
         <v>80</v>
       </c>
-      <c r="K135" t="n">
+      <c r="L135" t="n">
+        <v>41</v>
+      </c>
+      <c r="M135" t="n">
         <v>87.2340425531915</v>
       </c>
     </row>
@@ -7622,9 +8436,15 @@
         </is>
       </c>
       <c r="J136" t="n">
+        <v>2</v>
+      </c>
+      <c r="K136" t="n">
         <v>40</v>
       </c>
-      <c r="K136" t="n">
+      <c r="L136" t="n">
+        <v>29</v>
+      </c>
+      <c r="M136" t="n">
         <v>61.70212765957447</v>
       </c>
     </row>
@@ -7675,9 +8495,15 @@
         </is>
       </c>
       <c r="J137" t="n">
+        <v>4</v>
+      </c>
+      <c r="K137" t="n">
         <v>80</v>
       </c>
-      <c r="K137" t="n">
+      <c r="L137" t="n">
+        <v>45</v>
+      </c>
+      <c r="M137" t="n">
         <v>95.74468085106383</v>
       </c>
     </row>
@@ -7728,9 +8554,15 @@
         </is>
       </c>
       <c r="J138" t="n">
+        <v>5</v>
+      </c>
+      <c r="K138" t="n">
         <v>100</v>
       </c>
-      <c r="K138" t="n">
+      <c r="L138" t="n">
+        <v>44</v>
+      </c>
+      <c r="M138" t="n">
         <v>93.61702127659575</v>
       </c>
     </row>
@@ -7781,9 +8613,15 @@
         </is>
       </c>
       <c r="J139" t="n">
+        <v>5</v>
+      </c>
+      <c r="K139" t="n">
         <v>100</v>
       </c>
-      <c r="K139" t="n">
+      <c r="L139" t="n">
+        <v>41</v>
+      </c>
+      <c r="M139" t="n">
         <v>87.2340425531915</v>
       </c>
     </row>
@@ -7834,9 +8672,15 @@
         </is>
       </c>
       <c r="J140" t="n">
+        <v>5</v>
+      </c>
+      <c r="K140" t="n">
         <v>100</v>
       </c>
-      <c r="K140" t="n">
+      <c r="L140" t="n">
+        <v>36</v>
+      </c>
+      <c r="M140" t="n">
         <v>76.59574468085107</v>
       </c>
     </row>
@@ -7887,9 +8731,15 @@
         </is>
       </c>
       <c r="J141" t="n">
+        <v>4</v>
+      </c>
+      <c r="K141" t="n">
         <v>80</v>
       </c>
-      <c r="K141" t="n">
+      <c r="L141" t="n">
+        <v>32</v>
+      </c>
+      <c r="M141" t="n">
         <v>68.08510638297872</v>
       </c>
     </row>
@@ -7940,9 +8790,15 @@
         </is>
       </c>
       <c r="J142" t="n">
+        <v>5</v>
+      </c>
+      <c r="K142" t="n">
         <v>100</v>
       </c>
-      <c r="K142" t="n">
+      <c r="L142" t="n">
+        <v>35</v>
+      </c>
+      <c r="M142" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -7993,9 +8849,15 @@
         </is>
       </c>
       <c r="J143" t="n">
+        <v>2</v>
+      </c>
+      <c r="K143" t="n">
         <v>40</v>
       </c>
-      <c r="K143" t="n">
+      <c r="L143" t="n">
+        <v>26</v>
+      </c>
+      <c r="M143" t="n">
         <v>55.31914893617022</v>
       </c>
     </row>
@@ -8046,9 +8908,15 @@
         </is>
       </c>
       <c r="J144" t="n">
+        <v>5</v>
+      </c>
+      <c r="K144" t="n">
         <v>100</v>
       </c>
-      <c r="K144" t="n">
+      <c r="L144" t="n">
+        <v>34</v>
+      </c>
+      <c r="M144" t="n">
         <v>72.3404255319149</v>
       </c>
     </row>
@@ -8102,6 +8970,12 @@
         <v>0</v>
       </c>
       <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>34</v>
+      </c>
+      <c r="M145" t="n">
         <v>72.3404255319149</v>
       </c>
     </row>
@@ -8152,9 +9026,15 @@
         </is>
       </c>
       <c r="J146" t="n">
+        <v>4</v>
+      </c>
+      <c r="K146" t="n">
         <v>80</v>
       </c>
-      <c r="K146" t="n">
+      <c r="L146" t="n">
+        <v>37</v>
+      </c>
+      <c r="M146" t="n">
         <v>78.72340425531915</v>
       </c>
     </row>
@@ -8205,9 +9085,15 @@
         </is>
       </c>
       <c r="J147" t="n">
+        <v>2</v>
+      </c>
+      <c r="K147" t="n">
         <v>40</v>
       </c>
-      <c r="K147" t="n">
+      <c r="L147" t="n">
+        <v>22</v>
+      </c>
+      <c r="M147" t="n">
         <v>46.80851063829788</v>
       </c>
     </row>
@@ -8258,9 +9144,15 @@
         </is>
       </c>
       <c r="J148" t="n">
+        <v>5</v>
+      </c>
+      <c r="K148" t="n">
         <v>100</v>
       </c>
-      <c r="K148" t="n">
+      <c r="L148" t="n">
+        <v>32</v>
+      </c>
+      <c r="M148" t="n">
         <v>68.08510638297872</v>
       </c>
     </row>
@@ -8311,9 +9203,15 @@
         </is>
       </c>
       <c r="J149" t="n">
+        <v>4</v>
+      </c>
+      <c r="K149" t="n">
         <v>80</v>
       </c>
-      <c r="K149" t="n">
+      <c r="L149" t="n">
+        <v>33</v>
+      </c>
+      <c r="M149" t="n">
         <v>70.21276595744681</v>
       </c>
     </row>
@@ -8364,9 +9262,15 @@
         </is>
       </c>
       <c r="J150" t="n">
+        <v>3</v>
+      </c>
+      <c r="K150" t="n">
         <v>60</v>
       </c>
-      <c r="K150" t="n">
+      <c r="L150" t="n">
+        <v>47</v>
+      </c>
+      <c r="M150" t="n">
         <v>100</v>
       </c>
     </row>
@@ -8417,9 +9321,15 @@
         </is>
       </c>
       <c r="J151" t="n">
+        <v>2</v>
+      </c>
+      <c r="K151" t="n">
         <v>40</v>
       </c>
-      <c r="K151" t="n">
+      <c r="L151" t="n">
+        <v>25</v>
+      </c>
+      <c r="M151" t="n">
         <v>53.19148936170212</v>
       </c>
     </row>
@@ -8470,9 +9380,15 @@
         </is>
       </c>
       <c r="J152" t="n">
+        <v>4</v>
+      </c>
+      <c r="K152" t="n">
         <v>80</v>
       </c>
-      <c r="K152" t="n">
+      <c r="L152" t="n">
+        <v>29</v>
+      </c>
+      <c r="M152" t="n">
         <v>61.70212765957447</v>
       </c>
     </row>
@@ -8523,9 +9439,15 @@
         </is>
       </c>
       <c r="J153" t="n">
+        <v>4</v>
+      </c>
+      <c r="K153" t="n">
         <v>80</v>
       </c>
-      <c r="K153" t="n">
+      <c r="L153" t="n">
+        <v>23</v>
+      </c>
+      <c r="M153" t="n">
         <v>48.93617021276596</v>
       </c>
     </row>
@@ -8576,9 +9498,15 @@
         </is>
       </c>
       <c r="J154" t="n">
+        <v>4</v>
+      </c>
+      <c r="K154" t="n">
         <v>80</v>
       </c>
-      <c r="K154" t="n">
+      <c r="L154" t="n">
+        <v>35</v>
+      </c>
+      <c r="M154" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -8629,9 +9557,15 @@
         </is>
       </c>
       <c r="J155" t="n">
+        <v>2</v>
+      </c>
+      <c r="K155" t="n">
         <v>40</v>
       </c>
-      <c r="K155" t="n">
+      <c r="L155" t="n">
+        <v>28</v>
+      </c>
+      <c r="M155" t="n">
         <v>59.57446808510638</v>
       </c>
     </row>
@@ -8682,9 +9616,15 @@
         </is>
       </c>
       <c r="J156" t="n">
+        <v>3</v>
+      </c>
+      <c r="K156" t="n">
         <v>60</v>
       </c>
-      <c r="K156" t="n">
+      <c r="L156" t="n">
+        <v>28</v>
+      </c>
+      <c r="M156" t="n">
         <v>59.57446808510638</v>
       </c>
     </row>
@@ -8735,9 +9675,15 @@
         </is>
       </c>
       <c r="J157" t="n">
+        <v>3</v>
+      </c>
+      <c r="K157" t="n">
         <v>60</v>
       </c>
-      <c r="K157" t="n">
+      <c r="L157" t="n">
+        <v>33</v>
+      </c>
+      <c r="M157" t="n">
         <v>70.21276595744681</v>
       </c>
     </row>
@@ -8788,9 +9734,15 @@
         </is>
       </c>
       <c r="J158" t="n">
+        <v>4</v>
+      </c>
+      <c r="K158" t="n">
         <v>80</v>
       </c>
-      <c r="K158" t="n">
+      <c r="L158" t="n">
+        <v>33</v>
+      </c>
+      <c r="M158" t="n">
         <v>70.21276595744681</v>
       </c>
     </row>
@@ -8841,9 +9793,15 @@
         </is>
       </c>
       <c r="J159" t="n">
+        <v>3</v>
+      </c>
+      <c r="K159" t="n">
         <v>60</v>
       </c>
-      <c r="K159" t="n">
+      <c r="L159" t="n">
+        <v>20</v>
+      </c>
+      <c r="M159" t="n">
         <v>42.5531914893617</v>
       </c>
     </row>
@@ -8894,9 +9852,15 @@
         </is>
       </c>
       <c r="J160" t="n">
+        <v>2</v>
+      </c>
+      <c r="K160" t="n">
         <v>40</v>
       </c>
-      <c r="K160" t="n">
+      <c r="L160" t="n">
+        <v>22</v>
+      </c>
+      <c r="M160" t="n">
         <v>46.80851063829788</v>
       </c>
     </row>
@@ -8947,9 +9911,15 @@
         </is>
       </c>
       <c r="J161" t="n">
+        <v>4</v>
+      </c>
+      <c r="K161" t="n">
         <v>80</v>
       </c>
-      <c r="K161" t="n">
+      <c r="L161" t="n">
+        <v>25</v>
+      </c>
+      <c r="M161" t="n">
         <v>53.19148936170212</v>
       </c>
     </row>
@@ -9000,9 +9970,15 @@
         </is>
       </c>
       <c r="J162" t="n">
+        <v>4</v>
+      </c>
+      <c r="K162" t="n">
         <v>80</v>
       </c>
-      <c r="K162" t="n">
+      <c r="L162" t="n">
+        <v>23</v>
+      </c>
+      <c r="M162" t="n">
         <v>48.93617021276596</v>
       </c>
     </row>
@@ -9053,9 +10029,15 @@
         </is>
       </c>
       <c r="J163" t="n">
+        <v>2</v>
+      </c>
+      <c r="K163" t="n">
         <v>40</v>
       </c>
-      <c r="K163" t="n">
+      <c r="L163" t="n">
+        <v>41</v>
+      </c>
+      <c r="M163" t="n">
         <v>87.2340425531915</v>
       </c>
     </row>
@@ -9106,9 +10088,15 @@
         </is>
       </c>
       <c r="J164" t="n">
+        <v>4</v>
+      </c>
+      <c r="K164" t="n">
         <v>80</v>
       </c>
-      <c r="K164" t="n">
+      <c r="L164" t="n">
+        <v>23</v>
+      </c>
+      <c r="M164" t="n">
         <v>48.93617021276596</v>
       </c>
     </row>
@@ -9159,9 +10147,15 @@
         </is>
       </c>
       <c r="J165" t="n">
+        <v>2</v>
+      </c>
+      <c r="K165" t="n">
         <v>40</v>
       </c>
-      <c r="K165" t="n">
+      <c r="L165" t="n">
+        <v>47</v>
+      </c>
+      <c r="M165" t="n">
         <v>100</v>
       </c>
     </row>
@@ -9212,9 +10206,15 @@
         </is>
       </c>
       <c r="J166" t="n">
+        <v>2</v>
+      </c>
+      <c r="K166" t="n">
         <v>40</v>
       </c>
-      <c r="K166" t="n">
+      <c r="L166" t="n">
+        <v>27</v>
+      </c>
+      <c r="M166" t="n">
         <v>57.44680851063831</v>
       </c>
     </row>
@@ -9265,9 +10265,15 @@
         </is>
       </c>
       <c r="J167" t="n">
+        <v>1</v>
+      </c>
+      <c r="K167" t="n">
         <v>20</v>
       </c>
-      <c r="K167" t="n">
+      <c r="L167" t="n">
+        <v>37</v>
+      </c>
+      <c r="M167" t="n">
         <v>78.72340425531915</v>
       </c>
     </row>
@@ -9318,9 +10324,15 @@
         </is>
       </c>
       <c r="J168" t="n">
+        <v>3</v>
+      </c>
+      <c r="K168" t="n">
         <v>60</v>
       </c>
-      <c r="K168" t="n">
+      <c r="L168" t="n">
+        <v>25</v>
+      </c>
+      <c r="M168" t="n">
         <v>53.19148936170212</v>
       </c>
     </row>
@@ -9374,6 +10386,12 @@
         <v>0</v>
       </c>
       <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>27</v>
+      </c>
+      <c r="M169" t="n">
         <v>57.44680851063831</v>
       </c>
     </row>
@@ -9424,9 +10442,15 @@
         </is>
       </c>
       <c r="J170" t="n">
+        <v>4</v>
+      </c>
+      <c r="K170" t="n">
         <v>80</v>
       </c>
-      <c r="K170" t="n">
+      <c r="L170" t="n">
+        <v>29</v>
+      </c>
+      <c r="M170" t="n">
         <v>61.70212765957447</v>
       </c>
     </row>
@@ -9477,9 +10501,15 @@
         </is>
       </c>
       <c r="J171" t="n">
+        <v>3</v>
+      </c>
+      <c r="K171" t="n">
         <v>60</v>
       </c>
-      <c r="K171" t="n">
+      <c r="L171" t="n">
+        <v>33</v>
+      </c>
+      <c r="M171" t="n">
         <v>70.21276595744681</v>
       </c>
     </row>
@@ -9530,9 +10560,15 @@
         </is>
       </c>
       <c r="J172" t="n">
+        <v>1</v>
+      </c>
+      <c r="K172" t="n">
         <v>20</v>
       </c>
-      <c r="K172" t="n">
+      <c r="L172" t="n">
+        <v>36</v>
+      </c>
+      <c r="M172" t="n">
         <v>76.59574468085107</v>
       </c>
     </row>
@@ -9583,9 +10619,15 @@
         </is>
       </c>
       <c r="J173" t="n">
+        <v>3</v>
+      </c>
+      <c r="K173" t="n">
         <v>60</v>
       </c>
-      <c r="K173" t="n">
+      <c r="L173" t="n">
+        <v>30</v>
+      </c>
+      <c r="M173" t="n">
         <v>63.82978723404256</v>
       </c>
     </row>
@@ -9636,9 +10678,15 @@
         </is>
       </c>
       <c r="J174" t="n">
+        <v>4</v>
+      </c>
+      <c r="K174" t="n">
         <v>80</v>
       </c>
-      <c r="K174" t="n">
+      <c r="L174" t="n">
+        <v>29</v>
+      </c>
+      <c r="M174" t="n">
         <v>61.70212765957447</v>
       </c>
     </row>
@@ -9689,9 +10737,15 @@
         </is>
       </c>
       <c r="J175" t="n">
+        <v>4</v>
+      </c>
+      <c r="K175" t="n">
         <v>80</v>
       </c>
-      <c r="K175" t="n">
+      <c r="L175" t="n">
+        <v>31</v>
+      </c>
+      <c r="M175" t="n">
         <v>65.95744680851064</v>
       </c>
     </row>
@@ -9742,9 +10796,15 @@
         </is>
       </c>
       <c r="J176" t="n">
+        <v>3</v>
+      </c>
+      <c r="K176" t="n">
         <v>60</v>
       </c>
-      <c r="K176" t="n">
+      <c r="L176" t="n">
+        <v>24</v>
+      </c>
+      <c r="M176" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -9795,9 +10855,15 @@
         </is>
       </c>
       <c r="J177" t="n">
+        <v>2</v>
+      </c>
+      <c r="K177" t="n">
         <v>40</v>
       </c>
-      <c r="K177" t="n">
+      <c r="L177" t="n">
+        <v>41</v>
+      </c>
+      <c r="M177" t="n">
         <v>87.2340425531915</v>
       </c>
     </row>
@@ -9848,9 +10914,15 @@
         </is>
       </c>
       <c r="J178" t="n">
+        <v>2</v>
+      </c>
+      <c r="K178" t="n">
         <v>40</v>
       </c>
-      <c r="K178" t="n">
+      <c r="L178" t="n">
+        <v>26</v>
+      </c>
+      <c r="M178" t="n">
         <v>55.31914893617022</v>
       </c>
     </row>
@@ -9901,9 +10973,15 @@
         </is>
       </c>
       <c r="J179" t="n">
+        <v>4</v>
+      </c>
+      <c r="K179" t="n">
         <v>80</v>
       </c>
-      <c r="K179" t="n">
+      <c r="L179" t="n">
+        <v>24</v>
+      </c>
+      <c r="M179" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -9954,9 +11032,15 @@
         </is>
       </c>
       <c r="J180" t="n">
+        <v>4</v>
+      </c>
+      <c r="K180" t="n">
         <v>80</v>
       </c>
-      <c r="K180" t="n">
+      <c r="L180" t="n">
+        <v>33</v>
+      </c>
+      <c r="M180" t="n">
         <v>70.21276595744681</v>
       </c>
     </row>
@@ -10007,9 +11091,15 @@
         </is>
       </c>
       <c r="J181" t="n">
+        <v>4</v>
+      </c>
+      <c r="K181" t="n">
         <v>80</v>
       </c>
-      <c r="K181" t="n">
+      <c r="L181" t="n">
+        <v>30</v>
+      </c>
+      <c r="M181" t="n">
         <v>63.82978723404256</v>
       </c>
     </row>
@@ -10060,9 +11150,15 @@
         </is>
       </c>
       <c r="J182" t="n">
+        <v>3</v>
+      </c>
+      <c r="K182" t="n">
         <v>60</v>
       </c>
-      <c r="K182" t="n">
+      <c r="L182" t="n">
+        <v>42</v>
+      </c>
+      <c r="M182" t="n">
         <v>89.36170212765957</v>
       </c>
     </row>
@@ -10113,9 +11209,15 @@
         </is>
       </c>
       <c r="J183" t="n">
+        <v>2</v>
+      </c>
+      <c r="K183" t="n">
         <v>40</v>
       </c>
-      <c r="K183" t="n">
+      <c r="L183" t="n">
+        <v>14</v>
+      </c>
+      <c r="M183" t="n">
         <v>29.78723404255319</v>
       </c>
     </row>
@@ -10166,9 +11268,15 @@
         </is>
       </c>
       <c r="J184" t="n">
+        <v>2</v>
+      </c>
+      <c r="K184" t="n">
         <v>40</v>
       </c>
-      <c r="K184" t="n">
+      <c r="L184" t="n">
+        <v>21</v>
+      </c>
+      <c r="M184" t="n">
         <v>44.68085106382978</v>
       </c>
     </row>
@@ -10219,9 +11327,15 @@
         </is>
       </c>
       <c r="J185" t="n">
+        <v>4</v>
+      </c>
+      <c r="K185" t="n">
         <v>80</v>
       </c>
-      <c r="K185" t="n">
+      <c r="L185" t="n">
+        <v>23</v>
+      </c>
+      <c r="M185" t="n">
         <v>48.93617021276596</v>
       </c>
     </row>
@@ -10272,9 +11386,15 @@
         </is>
       </c>
       <c r="J186" t="n">
+        <v>1</v>
+      </c>
+      <c r="K186" t="n">
         <v>20</v>
       </c>
-      <c r="K186" t="n">
+      <c r="L186" t="n">
+        <v>27</v>
+      </c>
+      <c r="M186" t="n">
         <v>57.44680851063831</v>
       </c>
     </row>
@@ -10325,9 +11445,15 @@
         </is>
       </c>
       <c r="J187" t="n">
+        <v>1</v>
+      </c>
+      <c r="K187" t="n">
         <v>20</v>
       </c>
-      <c r="K187" t="n">
+      <c r="L187" t="n">
+        <v>27</v>
+      </c>
+      <c r="M187" t="n">
         <v>57.44680851063831</v>
       </c>
     </row>
@@ -10378,9 +11504,15 @@
         </is>
       </c>
       <c r="J188" t="n">
+        <v>2</v>
+      </c>
+      <c r="K188" t="n">
         <v>40</v>
       </c>
-      <c r="K188" t="n">
+      <c r="L188" t="n">
+        <v>19</v>
+      </c>
+      <c r="M188" t="n">
         <v>40.42553191489361</v>
       </c>
     </row>
@@ -10431,9 +11563,15 @@
         </is>
       </c>
       <c r="J189" t="n">
+        <v>2</v>
+      </c>
+      <c r="K189" t="n">
         <v>40</v>
       </c>
-      <c r="K189" t="n">
+      <c r="L189" t="n">
+        <v>22</v>
+      </c>
+      <c r="M189" t="n">
         <v>46.80851063829788</v>
       </c>
     </row>
@@ -10484,9 +11622,15 @@
         </is>
       </c>
       <c r="J190" t="n">
+        <v>3</v>
+      </c>
+      <c r="K190" t="n">
         <v>60</v>
       </c>
-      <c r="K190" t="n">
+      <c r="L190" t="n">
+        <v>22</v>
+      </c>
+      <c r="M190" t="n">
         <v>46.80851063829788</v>
       </c>
     </row>
@@ -10537,9 +11681,15 @@
         </is>
       </c>
       <c r="J191" t="n">
+        <v>1</v>
+      </c>
+      <c r="K191" t="n">
         <v>20</v>
       </c>
-      <c r="K191" t="n">
+      <c r="L191" t="n">
+        <v>16</v>
+      </c>
+      <c r="M191" t="n">
         <v>34.04255319148936</v>
       </c>
     </row>
@@ -10590,9 +11740,15 @@
         </is>
       </c>
       <c r="J192" t="n">
+        <v>2</v>
+      </c>
+      <c r="K192" t="n">
         <v>40</v>
       </c>
-      <c r="K192" t="n">
+      <c r="L192" t="n">
+        <v>23</v>
+      </c>
+      <c r="M192" t="n">
         <v>48.93617021276596</v>
       </c>
     </row>
@@ -10643,9 +11799,15 @@
         </is>
       </c>
       <c r="J193" t="n">
+        <v>2</v>
+      </c>
+      <c r="K193" t="n">
         <v>40</v>
       </c>
-      <c r="K193" t="n">
+      <c r="L193" t="n">
+        <v>24</v>
+      </c>
+      <c r="M193" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -10696,9 +11858,15 @@
         </is>
       </c>
       <c r="J194" t="n">
+        <v>2</v>
+      </c>
+      <c r="K194" t="n">
         <v>40</v>
       </c>
-      <c r="K194" t="n">
+      <c r="L194" t="n">
+        <v>32</v>
+      </c>
+      <c r="M194" t="n">
         <v>68.08510638297872</v>
       </c>
     </row>
@@ -10749,9 +11917,15 @@
         </is>
       </c>
       <c r="J195" t="n">
+        <v>2</v>
+      </c>
+      <c r="K195" t="n">
         <v>40</v>
       </c>
-      <c r="K195" t="n">
+      <c r="L195" t="n">
+        <v>22</v>
+      </c>
+      <c r="M195" t="n">
         <v>46.80851063829788</v>
       </c>
     </row>
@@ -10802,9 +11976,15 @@
         </is>
       </c>
       <c r="J196" t="n">
+        <v>3</v>
+      </c>
+      <c r="K196" t="n">
         <v>60</v>
       </c>
-      <c r="K196" t="n">
+      <c r="L196" t="n">
+        <v>23</v>
+      </c>
+      <c r="M196" t="n">
         <v>48.93617021276596</v>
       </c>
     </row>
@@ -10855,9 +12035,15 @@
         </is>
       </c>
       <c r="J197" t="n">
+        <v>3</v>
+      </c>
+      <c r="K197" t="n">
         <v>60</v>
       </c>
-      <c r="K197" t="n">
+      <c r="L197" t="n">
+        <v>42</v>
+      </c>
+      <c r="M197" t="n">
         <v>89.36170212765957</v>
       </c>
     </row>
@@ -10908,9 +12094,15 @@
         </is>
       </c>
       <c r="J198" t="n">
+        <v>2</v>
+      </c>
+      <c r="K198" t="n">
         <v>40</v>
       </c>
-      <c r="K198" t="n">
+      <c r="L198" t="n">
+        <v>35</v>
+      </c>
+      <c r="M198" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -10961,9 +12153,15 @@
         </is>
       </c>
       <c r="J199" t="n">
+        <v>4</v>
+      </c>
+      <c r="K199" t="n">
         <v>80</v>
       </c>
-      <c r="K199" t="n">
+      <c r="L199" t="n">
+        <v>23</v>
+      </c>
+      <c r="M199" t="n">
         <v>48.93617021276596</v>
       </c>
     </row>
@@ -11014,9 +12212,15 @@
         </is>
       </c>
       <c r="J200" t="n">
+        <v>2</v>
+      </c>
+      <c r="K200" t="n">
         <v>40</v>
       </c>
-      <c r="K200" t="n">
+      <c r="L200" t="n">
+        <v>25</v>
+      </c>
+      <c r="M200" t="n">
         <v>53.19148936170212</v>
       </c>
     </row>
@@ -11067,9 +12271,15 @@
         </is>
       </c>
       <c r="J201" t="n">
+        <v>3</v>
+      </c>
+      <c r="K201" t="n">
         <v>60</v>
       </c>
-      <c r="K201" t="n">
+      <c r="L201" t="n">
+        <v>27</v>
+      </c>
+      <c r="M201" t="n">
         <v>57.44680851063831</v>
       </c>
     </row>
@@ -11120,9 +12330,15 @@
         </is>
       </c>
       <c r="J202" t="n">
+        <v>2</v>
+      </c>
+      <c r="K202" t="n">
         <v>40</v>
       </c>
-      <c r="K202" t="n">
+      <c r="L202" t="n">
+        <v>29</v>
+      </c>
+      <c r="M202" t="n">
         <v>61.70212765957447</v>
       </c>
     </row>
@@ -11173,9 +12389,15 @@
         </is>
       </c>
       <c r="J203" t="n">
+        <v>3</v>
+      </c>
+      <c r="K203" t="n">
         <v>60</v>
       </c>
-      <c r="K203" t="n">
+      <c r="L203" t="n">
+        <v>32</v>
+      </c>
+      <c r="M203" t="n">
         <v>68.08510638297872</v>
       </c>
     </row>
@@ -11226,9 +12448,15 @@
         </is>
       </c>
       <c r="J204" t="n">
+        <v>4</v>
+      </c>
+      <c r="K204" t="n">
         <v>80</v>
       </c>
-      <c r="K204" t="n">
+      <c r="L204" t="n">
+        <v>21</v>
+      </c>
+      <c r="M204" t="n">
         <v>44.68085106382978</v>
       </c>
     </row>
@@ -11282,6 +12510,12 @@
         <v>0</v>
       </c>
       <c r="K205" t="n">
+        <v>0</v>
+      </c>
+      <c r="L205" t="n">
+        <v>18</v>
+      </c>
+      <c r="M205" t="n">
         <v>38.29787234042553</v>
       </c>
     </row>
@@ -11332,9 +12566,15 @@
         </is>
       </c>
       <c r="J206" t="n">
+        <v>1</v>
+      </c>
+      <c r="K206" t="n">
         <v>20</v>
       </c>
-      <c r="K206" t="n">
+      <c r="L206" t="n">
+        <v>29</v>
+      </c>
+      <c r="M206" t="n">
         <v>61.70212765957447</v>
       </c>
     </row>
@@ -11385,9 +12625,15 @@
         </is>
       </c>
       <c r="J207" t="n">
+        <v>2</v>
+      </c>
+      <c r="K207" t="n">
         <v>40</v>
       </c>
-      <c r="K207" t="n">
+      <c r="L207" t="n">
+        <v>24</v>
+      </c>
+      <c r="M207" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -11441,6 +12687,12 @@
         <v>0</v>
       </c>
       <c r="K208" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" t="n">
+        <v>27</v>
+      </c>
+      <c r="M208" t="n">
         <v>57.44680851063831</v>
       </c>
     </row>
@@ -11491,9 +12743,15 @@
         </is>
       </c>
       <c r="J209" t="n">
+        <v>1</v>
+      </c>
+      <c r="K209" t="n">
         <v>20</v>
       </c>
-      <c r="K209" t="n">
+      <c r="L209" t="n">
+        <v>23</v>
+      </c>
+      <c r="M209" t="n">
         <v>48.93617021276596</v>
       </c>
     </row>
@@ -11544,9 +12802,15 @@
         </is>
       </c>
       <c r="J210" t="n">
+        <v>2</v>
+      </c>
+      <c r="K210" t="n">
         <v>40</v>
       </c>
-      <c r="K210" t="n">
+      <c r="L210" t="n">
+        <v>26</v>
+      </c>
+      <c r="M210" t="n">
         <v>55.31914893617022</v>
       </c>
     </row>
@@ -11597,9 +12861,15 @@
         </is>
       </c>
       <c r="J211" t="n">
+        <v>1</v>
+      </c>
+      <c r="K211" t="n">
         <v>20</v>
       </c>
-      <c r="K211" t="n">
+      <c r="L211" t="n">
+        <v>23</v>
+      </c>
+      <c r="M211" t="n">
         <v>48.93617021276596</v>
       </c>
     </row>
@@ -11650,9 +12920,15 @@
         </is>
       </c>
       <c r="J212" t="n">
+        <v>2</v>
+      </c>
+      <c r="K212" t="n">
         <v>40</v>
       </c>
-      <c r="K212" t="n">
+      <c r="L212" t="n">
+        <v>36</v>
+      </c>
+      <c r="M212" t="n">
         <v>76.59574468085107</v>
       </c>
     </row>
@@ -11703,9 +12979,15 @@
         </is>
       </c>
       <c r="J213" t="n">
+        <v>2</v>
+      </c>
+      <c r="K213" t="n">
         <v>40</v>
       </c>
-      <c r="K213" t="n">
+      <c r="L213" t="n">
+        <v>24</v>
+      </c>
+      <c r="M213" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -11756,9 +13038,15 @@
         </is>
       </c>
       <c r="J214" t="n">
+        <v>2</v>
+      </c>
+      <c r="K214" t="n">
         <v>40</v>
       </c>
-      <c r="K214" t="n">
+      <c r="L214" t="n">
+        <v>24</v>
+      </c>
+      <c r="M214" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -11809,9 +13097,15 @@
         </is>
       </c>
       <c r="J215" t="n">
+        <v>1</v>
+      </c>
+      <c r="K215" t="n">
         <v>20</v>
       </c>
-      <c r="K215" t="n">
+      <c r="L215" t="n">
+        <v>20</v>
+      </c>
+      <c r="M215" t="n">
         <v>42.5531914893617</v>
       </c>
     </row>
@@ -11862,9 +13156,15 @@
         </is>
       </c>
       <c r="J216" t="n">
+        <v>2</v>
+      </c>
+      <c r="K216" t="n">
         <v>40</v>
       </c>
-      <c r="K216" t="n">
+      <c r="L216" t="n">
+        <v>37</v>
+      </c>
+      <c r="M216" t="n">
         <v>78.72340425531915</v>
       </c>
     </row>
@@ -11915,9 +13215,15 @@
         </is>
       </c>
       <c r="J217" t="n">
+        <v>2</v>
+      </c>
+      <c r="K217" t="n">
         <v>40</v>
       </c>
-      <c r="K217" t="n">
+      <c r="L217" t="n">
+        <v>38</v>
+      </c>
+      <c r="M217" t="n">
         <v>80.85106382978722</v>
       </c>
     </row>
@@ -11968,9 +13274,15 @@
         </is>
       </c>
       <c r="J218" t="n">
+        <v>2</v>
+      </c>
+      <c r="K218" t="n">
         <v>40</v>
       </c>
-      <c r="K218" t="n">
+      <c r="L218" t="n">
+        <v>22</v>
+      </c>
+      <c r="M218" t="n">
         <v>46.80851063829788</v>
       </c>
     </row>
@@ -12021,9 +13333,15 @@
         </is>
       </c>
       <c r="J219" t="n">
+        <v>2</v>
+      </c>
+      <c r="K219" t="n">
         <v>40</v>
       </c>
-      <c r="K219" t="n">
+      <c r="L219" t="n">
+        <v>15</v>
+      </c>
+      <c r="M219" t="n">
         <v>31.91489361702128</v>
       </c>
     </row>
@@ -12074,9 +13392,15 @@
         </is>
       </c>
       <c r="J220" t="n">
+        <v>4</v>
+      </c>
+      <c r="K220" t="n">
         <v>80</v>
       </c>
-      <c r="K220" t="n">
+      <c r="L220" t="n">
+        <v>45</v>
+      </c>
+      <c r="M220" t="n">
         <v>95.74468085106383</v>
       </c>
     </row>
@@ -12127,9 +13451,15 @@
         </is>
       </c>
       <c r="J221" t="n">
+        <v>2</v>
+      </c>
+      <c r="K221" t="n">
         <v>40</v>
       </c>
-      <c r="K221" t="n">
+      <c r="L221" t="n">
+        <v>32</v>
+      </c>
+      <c r="M221" t="n">
         <v>68.08510638297872</v>
       </c>
     </row>
@@ -12180,9 +13510,15 @@
         </is>
       </c>
       <c r="J222" t="n">
+        <v>1</v>
+      </c>
+      <c r="K222" t="n">
         <v>20</v>
       </c>
-      <c r="K222" t="n">
+      <c r="L222" t="n">
+        <v>35</v>
+      </c>
+      <c r="M222" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -12236,6 +13572,12 @@
         <v>0</v>
       </c>
       <c r="K223" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" t="n">
+        <v>24</v>
+      </c>
+      <c r="M223" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -12286,9 +13628,15 @@
         </is>
       </c>
       <c r="J224" t="n">
+        <v>4</v>
+      </c>
+      <c r="K224" t="n">
         <v>80</v>
       </c>
-      <c r="K224" t="n">
+      <c r="L224" t="n">
+        <v>35</v>
+      </c>
+      <c r="M224" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -12339,9 +13687,15 @@
         </is>
       </c>
       <c r="J225" t="n">
+        <v>4</v>
+      </c>
+      <c r="K225" t="n">
         <v>80</v>
       </c>
-      <c r="K225" t="n">
+      <c r="L225" t="n">
+        <v>33</v>
+      </c>
+      <c r="M225" t="n">
         <v>70.21276595744681</v>
       </c>
     </row>
@@ -12392,9 +13746,15 @@
         </is>
       </c>
       <c r="J226" t="n">
+        <v>4</v>
+      </c>
+      <c r="K226" t="n">
         <v>80</v>
       </c>
-      <c r="K226" t="n">
+      <c r="L226" t="n">
+        <v>23</v>
+      </c>
+      <c r="M226" t="n">
         <v>48.93617021276596</v>
       </c>
     </row>
@@ -12445,9 +13805,15 @@
         </is>
       </c>
       <c r="J227" t="n">
+        <v>4</v>
+      </c>
+      <c r="K227" t="n">
         <v>80</v>
       </c>
-      <c r="K227" t="n">
+      <c r="L227" t="n">
+        <v>33</v>
+      </c>
+      <c r="M227" t="n">
         <v>70.21276595744681</v>
       </c>
     </row>
@@ -12498,9 +13864,15 @@
         </is>
       </c>
       <c r="J228" t="n">
+        <v>5</v>
+      </c>
+      <c r="K228" t="n">
         <v>100</v>
       </c>
-      <c r="K228" t="n">
+      <c r="L228" t="n">
+        <v>38</v>
+      </c>
+      <c r="M228" t="n">
         <v>80.85106382978722</v>
       </c>
     </row>
@@ -12551,9 +13923,15 @@
         </is>
       </c>
       <c r="J229" t="n">
+        <v>5</v>
+      </c>
+      <c r="K229" t="n">
         <v>100</v>
       </c>
-      <c r="K229" t="n">
+      <c r="L229" t="n">
+        <v>39</v>
+      </c>
+      <c r="M229" t="n">
         <v>82.97872340425532</v>
       </c>
     </row>
@@ -12604,9 +13982,15 @@
         </is>
       </c>
       <c r="J230" t="n">
+        <v>3</v>
+      </c>
+      <c r="K230" t="n">
         <v>60</v>
       </c>
-      <c r="K230" t="n">
+      <c r="L230" t="n">
+        <v>26</v>
+      </c>
+      <c r="M230" t="n">
         <v>55.31914893617022</v>
       </c>
     </row>
@@ -12657,9 +14041,15 @@
         </is>
       </c>
       <c r="J231" t="n">
+        <v>3</v>
+      </c>
+      <c r="K231" t="n">
         <v>60</v>
       </c>
-      <c r="K231" t="n">
+      <c r="L231" t="n">
+        <v>24</v>
+      </c>
+      <c r="M231" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -12710,9 +14100,15 @@
         </is>
       </c>
       <c r="J232" t="n">
+        <v>1</v>
+      </c>
+      <c r="K232" t="n">
         <v>20</v>
       </c>
-      <c r="K232" t="n">
+      <c r="L232" t="n">
+        <v>24</v>
+      </c>
+      <c r="M232" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -12763,9 +14159,15 @@
         </is>
       </c>
       <c r="J233" t="n">
+        <v>3</v>
+      </c>
+      <c r="K233" t="n">
         <v>60</v>
       </c>
-      <c r="K233" t="n">
+      <c r="L233" t="n">
+        <v>33</v>
+      </c>
+      <c r="M233" t="n">
         <v>70.21276595744681</v>
       </c>
     </row>
@@ -12816,9 +14218,15 @@
         </is>
       </c>
       <c r="J234" t="n">
+        <v>5</v>
+      </c>
+      <c r="K234" t="n">
         <v>100</v>
       </c>
-      <c r="K234" t="n">
+      <c r="L234" t="n">
+        <v>35</v>
+      </c>
+      <c r="M234" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -12869,9 +14277,15 @@
         </is>
       </c>
       <c r="J235" t="n">
+        <v>5</v>
+      </c>
+      <c r="K235" t="n">
         <v>100</v>
       </c>
-      <c r="K235" t="n">
+      <c r="L235" t="n">
+        <v>42</v>
+      </c>
+      <c r="M235" t="n">
         <v>89.36170212765957</v>
       </c>
     </row>
@@ -12922,9 +14336,15 @@
         </is>
       </c>
       <c r="J236" t="n">
+        <v>4</v>
+      </c>
+      <c r="K236" t="n">
         <v>80</v>
       </c>
-      <c r="K236" t="n">
+      <c r="L236" t="n">
+        <v>37</v>
+      </c>
+      <c r="M236" t="n">
         <v>78.72340425531915</v>
       </c>
     </row>
@@ -12975,9 +14395,15 @@
         </is>
       </c>
       <c r="J237" t="n">
+        <v>3</v>
+      </c>
+      <c r="K237" t="n">
         <v>60</v>
       </c>
-      <c r="K237" t="n">
+      <c r="L237" t="n">
+        <v>15</v>
+      </c>
+      <c r="M237" t="n">
         <v>31.91489361702128</v>
       </c>
     </row>
@@ -13028,9 +14454,15 @@
         </is>
       </c>
       <c r="J238" t="n">
+        <v>2</v>
+      </c>
+      <c r="K238" t="n">
         <v>40</v>
       </c>
-      <c r="K238" t="n">
+      <c r="L238" t="n">
+        <v>22</v>
+      </c>
+      <c r="M238" t="n">
         <v>46.80851063829788</v>
       </c>
     </row>
@@ -13081,9 +14513,15 @@
         </is>
       </c>
       <c r="J239" t="n">
+        <v>5</v>
+      </c>
+      <c r="K239" t="n">
         <v>100</v>
       </c>
-      <c r="K239" t="n">
+      <c r="L239" t="n">
+        <v>44</v>
+      </c>
+      <c r="M239" t="n">
         <v>93.61702127659575</v>
       </c>
     </row>
@@ -13134,9 +14572,15 @@
         </is>
       </c>
       <c r="J240" t="n">
+        <v>4</v>
+      </c>
+      <c r="K240" t="n">
         <v>80</v>
       </c>
-      <c r="K240" t="n">
+      <c r="L240" t="n">
+        <v>23</v>
+      </c>
+      <c r="M240" t="n">
         <v>48.93617021276596</v>
       </c>
     </row>
@@ -13187,9 +14631,15 @@
         </is>
       </c>
       <c r="J241" t="n">
+        <v>5</v>
+      </c>
+      <c r="K241" t="n">
         <v>100</v>
       </c>
-      <c r="K241" t="n">
+      <c r="L241" t="n">
+        <v>20</v>
+      </c>
+      <c r="M241" t="n">
         <v>42.5531914893617</v>
       </c>
     </row>
@@ -13240,9 +14690,15 @@
         </is>
       </c>
       <c r="J242" t="n">
+        <v>5</v>
+      </c>
+      <c r="K242" t="n">
         <v>100</v>
       </c>
-      <c r="K242" t="n">
+      <c r="L242" t="n">
+        <v>36</v>
+      </c>
+      <c r="M242" t="n">
         <v>76.59574468085107</v>
       </c>
     </row>
@@ -13293,9 +14749,15 @@
         </is>
       </c>
       <c r="J243" t="n">
+        <v>3</v>
+      </c>
+      <c r="K243" t="n">
         <v>60</v>
       </c>
-      <c r="K243" t="n">
+      <c r="L243" t="n">
+        <v>42</v>
+      </c>
+      <c r="M243" t="n">
         <v>89.36170212765957</v>
       </c>
     </row>
@@ -13346,9 +14808,15 @@
         </is>
       </c>
       <c r="J244" t="n">
+        <v>5</v>
+      </c>
+      <c r="K244" t="n">
         <v>100</v>
       </c>
-      <c r="K244" t="n">
+      <c r="L244" t="n">
+        <v>30</v>
+      </c>
+      <c r="M244" t="n">
         <v>63.82978723404256</v>
       </c>
     </row>
@@ -13399,9 +14867,15 @@
         </is>
       </c>
       <c r="J245" t="n">
+        <v>5</v>
+      </c>
+      <c r="K245" t="n">
         <v>100</v>
       </c>
-      <c r="K245" t="n">
+      <c r="L245" t="n">
+        <v>29</v>
+      </c>
+      <c r="M245" t="n">
         <v>61.70212765957447</v>
       </c>
     </row>
@@ -13452,9 +14926,15 @@
         </is>
       </c>
       <c r="J246" t="n">
+        <v>4</v>
+      </c>
+      <c r="K246" t="n">
         <v>80</v>
       </c>
-      <c r="K246" t="n">
+      <c r="L246" t="n">
+        <v>22</v>
+      </c>
+      <c r="M246" t="n">
         <v>46.80851063829788</v>
       </c>
     </row>
@@ -13505,9 +14985,15 @@
         </is>
       </c>
       <c r="J247" t="n">
+        <v>3</v>
+      </c>
+      <c r="K247" t="n">
         <v>60</v>
       </c>
-      <c r="K247" t="n">
+      <c r="L247" t="n">
+        <v>37</v>
+      </c>
+      <c r="M247" t="n">
         <v>78.72340425531915</v>
       </c>
     </row>
@@ -13558,9 +15044,15 @@
         </is>
       </c>
       <c r="J248" t="n">
+        <v>3</v>
+      </c>
+      <c r="K248" t="n">
         <v>60</v>
       </c>
-      <c r="K248" t="n">
+      <c r="L248" t="n">
+        <v>18</v>
+      </c>
+      <c r="M248" t="n">
         <v>38.29787234042553</v>
       </c>
     </row>
@@ -13611,9 +15103,15 @@
         </is>
       </c>
       <c r="J249" t="n">
+        <v>5</v>
+      </c>
+      <c r="K249" t="n">
         <v>100</v>
       </c>
-      <c r="K249" t="n">
+      <c r="L249" t="n">
+        <v>38</v>
+      </c>
+      <c r="M249" t="n">
         <v>80.85106382978722</v>
       </c>
     </row>
@@ -13664,9 +15162,15 @@
         </is>
       </c>
       <c r="J250" t="n">
+        <v>4</v>
+      </c>
+      <c r="K250" t="n">
         <v>80</v>
       </c>
-      <c r="K250" t="n">
+      <c r="L250" t="n">
+        <v>26</v>
+      </c>
+      <c r="M250" t="n">
         <v>55.31914893617022</v>
       </c>
     </row>
@@ -13717,9 +15221,15 @@
         </is>
       </c>
       <c r="J251" t="n">
+        <v>3</v>
+      </c>
+      <c r="K251" t="n">
         <v>60</v>
       </c>
-      <c r="K251" t="n">
+      <c r="L251" t="n">
+        <v>40</v>
+      </c>
+      <c r="M251" t="n">
         <v>85.1063829787234</v>
       </c>
     </row>
@@ -13770,9 +15280,15 @@
         </is>
       </c>
       <c r="J252" t="n">
+        <v>5</v>
+      </c>
+      <c r="K252" t="n">
         <v>100</v>
       </c>
-      <c r="K252" t="n">
+      <c r="L252" t="n">
+        <v>36</v>
+      </c>
+      <c r="M252" t="n">
         <v>76.59574468085107</v>
       </c>
     </row>
@@ -13823,9 +15339,15 @@
         </is>
       </c>
       <c r="J253" t="n">
+        <v>3</v>
+      </c>
+      <c r="K253" t="n">
         <v>60</v>
       </c>
-      <c r="K253" t="n">
+      <c r="L253" t="n">
+        <v>25</v>
+      </c>
+      <c r="M253" t="n">
         <v>53.19148936170212</v>
       </c>
     </row>
@@ -13876,9 +15398,15 @@
         </is>
       </c>
       <c r="J254" t="n">
+        <v>5</v>
+      </c>
+      <c r="K254" t="n">
         <v>100</v>
       </c>
-      <c r="K254" t="n">
+      <c r="L254" t="n">
+        <v>29</v>
+      </c>
+      <c r="M254" t="n">
         <v>61.70212765957447</v>
       </c>
     </row>
@@ -13929,9 +15457,15 @@
         </is>
       </c>
       <c r="J255" t="n">
+        <v>4</v>
+      </c>
+      <c r="K255" t="n">
         <v>80</v>
       </c>
-      <c r="K255" t="n">
+      <c r="L255" t="n">
+        <v>41</v>
+      </c>
+      <c r="M255" t="n">
         <v>87.2340425531915</v>
       </c>
     </row>
@@ -13982,9 +15516,15 @@
         </is>
       </c>
       <c r="J256" t="n">
+        <v>4</v>
+      </c>
+      <c r="K256" t="n">
         <v>80</v>
       </c>
-      <c r="K256" t="n">
+      <c r="L256" t="n">
+        <v>31</v>
+      </c>
+      <c r="M256" t="n">
         <v>65.95744680851064</v>
       </c>
     </row>
@@ -14035,9 +15575,15 @@
         </is>
       </c>
       <c r="J257" t="n">
+        <v>5</v>
+      </c>
+      <c r="K257" t="n">
         <v>100</v>
       </c>
-      <c r="K257" t="n">
+      <c r="L257" t="n">
+        <v>45</v>
+      </c>
+      <c r="M257" t="n">
         <v>95.74468085106383</v>
       </c>
     </row>
@@ -14088,9 +15634,15 @@
         </is>
       </c>
       <c r="J258" t="n">
+        <v>5</v>
+      </c>
+      <c r="K258" t="n">
         <v>100</v>
       </c>
-      <c r="K258" t="n">
+      <c r="L258" t="n">
+        <v>34</v>
+      </c>
+      <c r="M258" t="n">
         <v>72.3404255319149</v>
       </c>
     </row>
@@ -14141,9 +15693,15 @@
         </is>
       </c>
       <c r="J259" t="n">
+        <v>5</v>
+      </c>
+      <c r="K259" t="n">
         <v>100</v>
       </c>
-      <c r="K259" t="n">
+      <c r="L259" t="n">
+        <v>27</v>
+      </c>
+      <c r="M259" t="n">
         <v>57.44680851063831</v>
       </c>
     </row>
@@ -14194,9 +15752,15 @@
         </is>
       </c>
       <c r="J260" t="n">
+        <v>3</v>
+      </c>
+      <c r="K260" t="n">
         <v>60</v>
       </c>
-      <c r="K260" t="n">
+      <c r="L260" t="n">
+        <v>24</v>
+      </c>
+      <c r="M260" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -14247,9 +15811,15 @@
         </is>
       </c>
       <c r="J261" t="n">
+        <v>5</v>
+      </c>
+      <c r="K261" t="n">
         <v>100</v>
       </c>
-      <c r="K261" t="n">
+      <c r="L261" t="n">
+        <v>44</v>
+      </c>
+      <c r="M261" t="n">
         <v>93.61702127659575</v>
       </c>
     </row>
@@ -14300,9 +15870,15 @@
         </is>
       </c>
       <c r="J262" t="n">
+        <v>4</v>
+      </c>
+      <c r="K262" t="n">
         <v>80</v>
       </c>
-      <c r="K262" t="n">
+      <c r="L262" t="n">
+        <v>30</v>
+      </c>
+      <c r="M262" t="n">
         <v>63.82978723404256</v>
       </c>
     </row>
@@ -14353,9 +15929,15 @@
         </is>
       </c>
       <c r="J263" t="n">
+        <v>2</v>
+      </c>
+      <c r="K263" t="n">
         <v>40</v>
       </c>
-      <c r="K263" t="n">
+      <c r="L263" t="n">
+        <v>17</v>
+      </c>
+      <c r="M263" t="n">
         <v>36.17021276595745</v>
       </c>
     </row>
@@ -14406,9 +15988,15 @@
         </is>
       </c>
       <c r="J264" t="n">
+        <v>4</v>
+      </c>
+      <c r="K264" t="n">
         <v>80</v>
       </c>
-      <c r="K264" t="n">
+      <c r="L264" t="n">
+        <v>35</v>
+      </c>
+      <c r="M264" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -14459,9 +16047,15 @@
         </is>
       </c>
       <c r="J265" t="n">
+        <v>2</v>
+      </c>
+      <c r="K265" t="n">
         <v>40</v>
       </c>
-      <c r="K265" t="n">
+      <c r="L265" t="n">
+        <v>28</v>
+      </c>
+      <c r="M265" t="n">
         <v>59.57446808510638</v>
       </c>
     </row>
@@ -14512,9 +16106,15 @@
         </is>
       </c>
       <c r="J266" t="n">
+        <v>2</v>
+      </c>
+      <c r="K266" t="n">
         <v>40</v>
       </c>
-      <c r="K266" t="n">
+      <c r="L266" t="n">
+        <v>18</v>
+      </c>
+      <c r="M266" t="n">
         <v>38.29787234042553</v>
       </c>
     </row>
@@ -14565,9 +16165,15 @@
         </is>
       </c>
       <c r="J267" t="n">
+        <v>4</v>
+      </c>
+      <c r="K267" t="n">
         <v>80</v>
       </c>
-      <c r="K267" t="n">
+      <c r="L267" t="n">
+        <v>23</v>
+      </c>
+      <c r="M267" t="n">
         <v>48.93617021276596</v>
       </c>
     </row>
@@ -14618,9 +16224,15 @@
         </is>
       </c>
       <c r="J268" t="n">
+        <v>5</v>
+      </c>
+      <c r="K268" t="n">
         <v>100</v>
       </c>
-      <c r="K268" t="n">
+      <c r="L268" t="n">
+        <v>34</v>
+      </c>
+      <c r="M268" t="n">
         <v>72.3404255319149</v>
       </c>
     </row>
@@ -14671,9 +16283,15 @@
         </is>
       </c>
       <c r="J269" t="n">
+        <v>5</v>
+      </c>
+      <c r="K269" t="n">
         <v>100</v>
       </c>
-      <c r="K269" t="n">
+      <c r="L269" t="n">
+        <v>35</v>
+      </c>
+      <c r="M269" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -14724,9 +16342,15 @@
         </is>
       </c>
       <c r="J270" t="n">
+        <v>5</v>
+      </c>
+      <c r="K270" t="n">
         <v>100</v>
       </c>
-      <c r="K270" t="n">
+      <c r="L270" t="n">
+        <v>33</v>
+      </c>
+      <c r="M270" t="n">
         <v>70.21276595744681</v>
       </c>
     </row>
@@ -14777,9 +16401,15 @@
         </is>
       </c>
       <c r="J271" t="n">
+        <v>4</v>
+      </c>
+      <c r="K271" t="n">
         <v>80</v>
       </c>
-      <c r="K271" t="n">
+      <c r="L271" t="n">
+        <v>36</v>
+      </c>
+      <c r="M271" t="n">
         <v>76.59574468085107</v>
       </c>
     </row>
@@ -14830,9 +16460,15 @@
         </is>
       </c>
       <c r="J272" t="n">
+        <v>4</v>
+      </c>
+      <c r="K272" t="n">
         <v>80</v>
       </c>
-      <c r="K272" t="n">
+      <c r="L272" t="n">
+        <v>44</v>
+      </c>
+      <c r="M272" t="n">
         <v>93.61702127659575</v>
       </c>
     </row>
@@ -14883,9 +16519,15 @@
         </is>
       </c>
       <c r="J273" t="n">
+        <v>5</v>
+      </c>
+      <c r="K273" t="n">
         <v>100</v>
       </c>
-      <c r="K273" t="n">
+      <c r="L273" t="n">
+        <v>31</v>
+      </c>
+      <c r="M273" t="n">
         <v>65.95744680851064</v>
       </c>
     </row>
@@ -14936,9 +16578,15 @@
         </is>
       </c>
       <c r="J274" t="n">
+        <v>4</v>
+      </c>
+      <c r="K274" t="n">
         <v>80</v>
       </c>
-      <c r="K274" t="n">
+      <c r="L274" t="n">
+        <v>36</v>
+      </c>
+      <c r="M274" t="n">
         <v>76.59574468085107</v>
       </c>
     </row>
@@ -14989,9 +16637,15 @@
         </is>
       </c>
       <c r="J275" t="n">
+        <v>5</v>
+      </c>
+      <c r="K275" t="n">
         <v>100</v>
       </c>
-      <c r="K275" t="n">
+      <c r="L275" t="n">
+        <v>30</v>
+      </c>
+      <c r="M275" t="n">
         <v>63.82978723404256</v>
       </c>
     </row>
@@ -15042,9 +16696,15 @@
         </is>
       </c>
       <c r="J276" t="n">
+        <v>5</v>
+      </c>
+      <c r="K276" t="n">
         <v>100</v>
       </c>
-      <c r="K276" t="n">
+      <c r="L276" t="n">
+        <v>33</v>
+      </c>
+      <c r="M276" t="n">
         <v>70.21276595744681</v>
       </c>
     </row>
@@ -15095,9 +16755,15 @@
         </is>
       </c>
       <c r="J277" t="n">
+        <v>4</v>
+      </c>
+      <c r="K277" t="n">
         <v>80</v>
       </c>
-      <c r="K277" t="n">
+      <c r="L277" t="n">
+        <v>31</v>
+      </c>
+      <c r="M277" t="n">
         <v>65.95744680851064</v>
       </c>
     </row>
@@ -15148,9 +16814,15 @@
         </is>
       </c>
       <c r="J278" t="n">
+        <v>4</v>
+      </c>
+      <c r="K278" t="n">
         <v>80</v>
       </c>
-      <c r="K278" t="n">
+      <c r="L278" t="n">
+        <v>29</v>
+      </c>
+      <c r="M278" t="n">
         <v>61.70212765957447</v>
       </c>
     </row>
@@ -15201,9 +16873,15 @@
         </is>
       </c>
       <c r="J279" t="n">
+        <v>4</v>
+      </c>
+      <c r="K279" t="n">
         <v>80</v>
       </c>
-      <c r="K279" t="n">
+      <c r="L279" t="n">
+        <v>39</v>
+      </c>
+      <c r="M279" t="n">
         <v>82.97872340425532</v>
       </c>
     </row>
@@ -15254,9 +16932,15 @@
         </is>
       </c>
       <c r="J280" t="n">
+        <v>3</v>
+      </c>
+      <c r="K280" t="n">
         <v>60</v>
       </c>
-      <c r="K280" t="n">
+      <c r="L280" t="n">
+        <v>33</v>
+      </c>
+      <c r="M280" t="n">
         <v>70.21276595744681</v>
       </c>
     </row>
@@ -15307,9 +16991,15 @@
         </is>
       </c>
       <c r="J281" t="n">
+        <v>5</v>
+      </c>
+      <c r="K281" t="n">
         <v>100</v>
       </c>
-      <c r="K281" t="n">
+      <c r="L281" t="n">
+        <v>33</v>
+      </c>
+      <c r="M281" t="n">
         <v>70.21276595744681</v>
       </c>
     </row>
@@ -15360,9 +17050,15 @@
         </is>
       </c>
       <c r="J282" t="n">
+        <v>4</v>
+      </c>
+      <c r="K282" t="n">
         <v>80</v>
       </c>
-      <c r="K282" t="n">
+      <c r="L282" t="n">
+        <v>32</v>
+      </c>
+      <c r="M282" t="n">
         <v>68.08510638297872</v>
       </c>
     </row>
@@ -15413,9 +17109,15 @@
         </is>
       </c>
       <c r="J283" t="n">
+        <v>3</v>
+      </c>
+      <c r="K283" t="n">
         <v>60</v>
       </c>
-      <c r="K283" t="n">
+      <c r="L283" t="n">
+        <v>26</v>
+      </c>
+      <c r="M283" t="n">
         <v>55.31914893617022</v>
       </c>
     </row>
@@ -15466,9 +17168,15 @@
         </is>
       </c>
       <c r="J284" t="n">
+        <v>3</v>
+      </c>
+      <c r="K284" t="n">
         <v>60</v>
       </c>
-      <c r="K284" t="n">
+      <c r="L284" t="n">
+        <v>38</v>
+      </c>
+      <c r="M284" t="n">
         <v>80.85106382978722</v>
       </c>
     </row>
@@ -15519,9 +17227,15 @@
         </is>
       </c>
       <c r="J285" t="n">
+        <v>4</v>
+      </c>
+      <c r="K285" t="n">
         <v>80</v>
       </c>
-      <c r="K285" t="n">
+      <c r="L285" t="n">
+        <v>15</v>
+      </c>
+      <c r="M285" t="n">
         <v>31.91489361702128</v>
       </c>
     </row>
@@ -15572,9 +17286,15 @@
         </is>
       </c>
       <c r="J286" t="n">
+        <v>4</v>
+      </c>
+      <c r="K286" t="n">
         <v>80</v>
       </c>
-      <c r="K286" t="n">
+      <c r="L286" t="n">
+        <v>35</v>
+      </c>
+      <c r="M286" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -15625,9 +17345,15 @@
         </is>
       </c>
       <c r="J287" t="n">
+        <v>3</v>
+      </c>
+      <c r="K287" t="n">
         <v>60</v>
       </c>
-      <c r="K287" t="n">
+      <c r="L287" t="n">
+        <v>44</v>
+      </c>
+      <c r="M287" t="n">
         <v>93.61702127659575</v>
       </c>
     </row>
@@ -15678,9 +17404,15 @@
         </is>
       </c>
       <c r="J288" t="n">
+        <v>5</v>
+      </c>
+      <c r="K288" t="n">
         <v>100</v>
       </c>
-      <c r="K288" t="n">
+      <c r="L288" t="n">
+        <v>31</v>
+      </c>
+      <c r="M288" t="n">
         <v>65.95744680851064</v>
       </c>
     </row>
@@ -15731,9 +17463,15 @@
         </is>
       </c>
       <c r="J289" t="n">
+        <v>2</v>
+      </c>
+      <c r="K289" t="n">
         <v>40</v>
       </c>
-      <c r="K289" t="n">
+      <c r="L289" t="n">
+        <v>32</v>
+      </c>
+      <c r="M289" t="n">
         <v>68.08510638297872</v>
       </c>
     </row>
@@ -15784,9 +17522,15 @@
         </is>
       </c>
       <c r="J290" t="n">
+        <v>3</v>
+      </c>
+      <c r="K290" t="n">
         <v>60</v>
       </c>
-      <c r="K290" t="n">
+      <c r="L290" t="n">
+        <v>33</v>
+      </c>
+      <c r="M290" t="n">
         <v>70.21276595744681</v>
       </c>
     </row>
@@ -15837,9 +17581,15 @@
         </is>
       </c>
       <c r="J291" t="n">
+        <v>5</v>
+      </c>
+      <c r="K291" t="n">
         <v>100</v>
       </c>
-      <c r="K291" t="n">
+      <c r="L291" t="n">
+        <v>27</v>
+      </c>
+      <c r="M291" t="n">
         <v>57.44680851063831</v>
       </c>
     </row>
@@ -15890,9 +17640,15 @@
         </is>
       </c>
       <c r="J292" t="n">
+        <v>4</v>
+      </c>
+      <c r="K292" t="n">
         <v>80</v>
       </c>
-      <c r="K292" t="n">
+      <c r="L292" t="n">
+        <v>20</v>
+      </c>
+      <c r="M292" t="n">
         <v>42.5531914893617</v>
       </c>
     </row>
@@ -15943,9 +17699,15 @@
         </is>
       </c>
       <c r="J293" t="n">
+        <v>3</v>
+      </c>
+      <c r="K293" t="n">
         <v>60</v>
       </c>
-      <c r="K293" t="n">
+      <c r="L293" t="n">
+        <v>24</v>
+      </c>
+      <c r="M293" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -15996,9 +17758,15 @@
         </is>
       </c>
       <c r="J294" t="n">
+        <v>5</v>
+      </c>
+      <c r="K294" t="n">
         <v>100</v>
       </c>
-      <c r="K294" t="n">
+      <c r="L294" t="n">
+        <v>20</v>
+      </c>
+      <c r="M294" t="n">
         <v>42.5531914893617</v>
       </c>
     </row>
@@ -16049,9 +17817,15 @@
         </is>
       </c>
       <c r="J295" t="n">
+        <v>3</v>
+      </c>
+      <c r="K295" t="n">
         <v>60</v>
       </c>
-      <c r="K295" t="n">
+      <c r="L295" t="n">
+        <v>24</v>
+      </c>
+      <c r="M295" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -16102,9 +17876,15 @@
         </is>
       </c>
       <c r="J296" t="n">
+        <v>3</v>
+      </c>
+      <c r="K296" t="n">
         <v>60</v>
       </c>
-      <c r="K296" t="n">
+      <c r="L296" t="n">
+        <v>30</v>
+      </c>
+      <c r="M296" t="n">
         <v>63.82978723404256</v>
       </c>
     </row>
@@ -16155,9 +17935,15 @@
         </is>
       </c>
       <c r="J297" t="n">
+        <v>3</v>
+      </c>
+      <c r="K297" t="n">
         <v>60</v>
       </c>
-      <c r="K297" t="n">
+      <c r="L297" t="n">
+        <v>30</v>
+      </c>
+      <c r="M297" t="n">
         <v>63.82978723404256</v>
       </c>
     </row>
@@ -16208,9 +17994,15 @@
         </is>
       </c>
       <c r="J298" t="n">
+        <v>4</v>
+      </c>
+      <c r="K298" t="n">
         <v>80</v>
       </c>
-      <c r="K298" t="n">
+      <c r="L298" t="n">
+        <v>29</v>
+      </c>
+      <c r="M298" t="n">
         <v>61.70212765957447</v>
       </c>
     </row>
@@ -16261,9 +18053,15 @@
         </is>
       </c>
       <c r="J299" t="n">
+        <v>3</v>
+      </c>
+      <c r="K299" t="n">
         <v>60</v>
       </c>
-      <c r="K299" t="n">
+      <c r="L299" t="n">
+        <v>36</v>
+      </c>
+      <c r="M299" t="n">
         <v>76.59574468085107</v>
       </c>
     </row>
@@ -16314,9 +18112,15 @@
         </is>
       </c>
       <c r="J300" t="n">
+        <v>3</v>
+      </c>
+      <c r="K300" t="n">
         <v>60</v>
       </c>
-      <c r="K300" t="n">
+      <c r="L300" t="n">
+        <v>25</v>
+      </c>
+      <c r="M300" t="n">
         <v>53.19148936170212</v>
       </c>
     </row>
@@ -16367,9 +18171,15 @@
         </is>
       </c>
       <c r="J301" t="n">
+        <v>4</v>
+      </c>
+      <c r="K301" t="n">
         <v>80</v>
       </c>
-      <c r="K301" t="n">
+      <c r="L301" t="n">
+        <v>41</v>
+      </c>
+      <c r="M301" t="n">
         <v>87.2340425531915</v>
       </c>
     </row>
@@ -16420,9 +18230,15 @@
         </is>
       </c>
       <c r="J302" t="n">
+        <v>3</v>
+      </c>
+      <c r="K302" t="n">
         <v>60</v>
       </c>
-      <c r="K302" t="n">
+      <c r="L302" t="n">
+        <v>28</v>
+      </c>
+      <c r="M302" t="n">
         <v>59.57446808510638</v>
       </c>
     </row>
@@ -16473,9 +18289,15 @@
         </is>
       </c>
       <c r="J303" t="n">
+        <v>5</v>
+      </c>
+      <c r="K303" t="n">
         <v>100</v>
       </c>
-      <c r="K303" t="n">
+      <c r="L303" t="n">
+        <v>29</v>
+      </c>
+      <c r="M303" t="n">
         <v>61.70212765957447</v>
       </c>
     </row>
@@ -16526,9 +18348,15 @@
         </is>
       </c>
       <c r="J304" t="n">
+        <v>2</v>
+      </c>
+      <c r="K304" t="n">
         <v>40</v>
       </c>
-      <c r="K304" t="n">
+      <c r="L304" t="n">
+        <v>22</v>
+      </c>
+      <c r="M304" t="n">
         <v>46.80851063829788</v>
       </c>
     </row>
@@ -16579,9 +18407,15 @@
         </is>
       </c>
       <c r="J305" t="n">
+        <v>4</v>
+      </c>
+      <c r="K305" t="n">
         <v>80</v>
       </c>
-      <c r="K305" t="n">
+      <c r="L305" t="n">
+        <v>31</v>
+      </c>
+      <c r="M305" t="n">
         <v>65.95744680851064</v>
       </c>
     </row>
@@ -16632,9 +18466,15 @@
         </is>
       </c>
       <c r="J306" t="n">
+        <v>3</v>
+      </c>
+      <c r="K306" t="n">
         <v>60</v>
       </c>
-      <c r="K306" t="n">
+      <c r="L306" t="n">
+        <v>26</v>
+      </c>
+      <c r="M306" t="n">
         <v>55.31914893617022</v>
       </c>
     </row>
@@ -16685,9 +18525,15 @@
         </is>
       </c>
       <c r="J307" t="n">
+        <v>3</v>
+      </c>
+      <c r="K307" t="n">
         <v>60</v>
       </c>
-      <c r="K307" t="n">
+      <c r="L307" t="n">
+        <v>38</v>
+      </c>
+      <c r="M307" t="n">
         <v>80.85106382978722</v>
       </c>
     </row>
@@ -16738,9 +18584,15 @@
         </is>
       </c>
       <c r="J308" t="n">
+        <v>4</v>
+      </c>
+      <c r="K308" t="n">
         <v>80</v>
       </c>
-      <c r="K308" t="n">
+      <c r="L308" t="n">
+        <v>19</v>
+      </c>
+      <c r="M308" t="n">
         <v>40.42553191489361</v>
       </c>
     </row>
@@ -16791,9 +18643,15 @@
         </is>
       </c>
       <c r="J309" t="n">
+        <v>5</v>
+      </c>
+      <c r="K309" t="n">
         <v>100</v>
       </c>
-      <c r="K309" t="n">
+      <c r="L309" t="n">
+        <v>44</v>
+      </c>
+      <c r="M309" t="n">
         <v>93.61702127659575</v>
       </c>
     </row>
@@ -16844,9 +18702,15 @@
         </is>
       </c>
       <c r="J310" t="n">
+        <v>3</v>
+      </c>
+      <c r="K310" t="n">
         <v>60</v>
       </c>
-      <c r="K310" t="n">
+      <c r="L310" t="n">
+        <v>38</v>
+      </c>
+      <c r="M310" t="n">
         <v>80.85106382978722</v>
       </c>
     </row>
@@ -16897,9 +18761,15 @@
         </is>
       </c>
       <c r="J311" t="n">
+        <v>4</v>
+      </c>
+      <c r="K311" t="n">
         <v>80</v>
       </c>
-      <c r="K311" t="n">
+      <c r="L311" t="n">
+        <v>26</v>
+      </c>
+      <c r="M311" t="n">
         <v>55.31914893617022</v>
       </c>
     </row>
@@ -16950,9 +18820,15 @@
         </is>
       </c>
       <c r="J312" t="n">
+        <v>5</v>
+      </c>
+      <c r="K312" t="n">
         <v>100</v>
       </c>
-      <c r="K312" t="n">
+      <c r="L312" t="n">
+        <v>45</v>
+      </c>
+      <c r="M312" t="n">
         <v>95.74468085106383</v>
       </c>
     </row>
@@ -17003,9 +18879,15 @@
         </is>
       </c>
       <c r="J313" t="n">
+        <v>3</v>
+      </c>
+      <c r="K313" t="n">
         <v>60</v>
       </c>
-      <c r="K313" t="n">
+      <c r="L313" t="n">
+        <v>22</v>
+      </c>
+      <c r="M313" t="n">
         <v>46.80851063829788</v>
       </c>
     </row>
@@ -17056,9 +18938,15 @@
         </is>
       </c>
       <c r="J314" t="n">
+        <v>3</v>
+      </c>
+      <c r="K314" t="n">
         <v>60</v>
       </c>
-      <c r="K314" t="n">
+      <c r="L314" t="n">
+        <v>43</v>
+      </c>
+      <c r="M314" t="n">
         <v>91.48936170212765</v>
       </c>
     </row>
@@ -17109,9 +18997,15 @@
         </is>
       </c>
       <c r="J315" t="n">
+        <v>2</v>
+      </c>
+      <c r="K315" t="n">
         <v>40</v>
       </c>
-      <c r="K315" t="n">
+      <c r="L315" t="n">
+        <v>21</v>
+      </c>
+      <c r="M315" t="n">
         <v>44.68085106382978</v>
       </c>
     </row>
@@ -17162,9 +19056,15 @@
         </is>
       </c>
       <c r="J316" t="n">
+        <v>5</v>
+      </c>
+      <c r="K316" t="n">
         <v>100</v>
       </c>
-      <c r="K316" t="n">
+      <c r="L316" t="n">
+        <v>28</v>
+      </c>
+      <c r="M316" t="n">
         <v>59.57446808510638</v>
       </c>
     </row>
@@ -17215,9 +19115,15 @@
         </is>
       </c>
       <c r="J317" t="n">
+        <v>2</v>
+      </c>
+      <c r="K317" t="n">
         <v>40</v>
       </c>
-      <c r="K317" t="n">
+      <c r="L317" t="n">
+        <v>17</v>
+      </c>
+      <c r="M317" t="n">
         <v>36.17021276595745</v>
       </c>
     </row>
@@ -17268,9 +19174,15 @@
         </is>
       </c>
       <c r="J318" t="n">
+        <v>5</v>
+      </c>
+      <c r="K318" t="n">
         <v>100</v>
       </c>
-      <c r="K318" t="n">
+      <c r="L318" t="n">
+        <v>28</v>
+      </c>
+      <c r="M318" t="n">
         <v>59.57446808510638</v>
       </c>
     </row>
@@ -17321,9 +19233,15 @@
         </is>
       </c>
       <c r="J319" t="n">
+        <v>3</v>
+      </c>
+      <c r="K319" t="n">
         <v>60</v>
       </c>
-      <c r="K319" t="n">
+      <c r="L319" t="n">
+        <v>27</v>
+      </c>
+      <c r="M319" t="n">
         <v>57.44680851063831</v>
       </c>
     </row>
@@ -17374,9 +19292,15 @@
         </is>
       </c>
       <c r="J320" t="n">
+        <v>4</v>
+      </c>
+      <c r="K320" t="n">
         <v>80</v>
       </c>
-      <c r="K320" t="n">
+      <c r="L320" t="n">
+        <v>20</v>
+      </c>
+      <c r="M320" t="n">
         <v>42.5531914893617</v>
       </c>
     </row>
@@ -17427,9 +19351,15 @@
         </is>
       </c>
       <c r="J321" t="n">
+        <v>4</v>
+      </c>
+      <c r="K321" t="n">
         <v>80</v>
       </c>
-      <c r="K321" t="n">
+      <c r="L321" t="n">
+        <v>41</v>
+      </c>
+      <c r="M321" t="n">
         <v>87.2340425531915</v>
       </c>
     </row>
@@ -17480,9 +19410,15 @@
         </is>
       </c>
       <c r="J322" t="n">
+        <v>3</v>
+      </c>
+      <c r="K322" t="n">
         <v>60</v>
       </c>
-      <c r="K322" t="n">
+      <c r="L322" t="n">
+        <v>26</v>
+      </c>
+      <c r="M322" t="n">
         <v>55.31914893617022</v>
       </c>
     </row>
@@ -17533,9 +19469,15 @@
         </is>
       </c>
       <c r="J323" t="n">
+        <v>5</v>
+      </c>
+      <c r="K323" t="n">
         <v>100</v>
       </c>
-      <c r="K323" t="n">
+      <c r="L323" t="n">
+        <v>34</v>
+      </c>
+      <c r="M323" t="n">
         <v>72.3404255319149</v>
       </c>
     </row>
@@ -17586,9 +19528,15 @@
         </is>
       </c>
       <c r="J324" t="n">
+        <v>4</v>
+      </c>
+      <c r="K324" t="n">
         <v>80</v>
       </c>
-      <c r="K324" t="n">
+      <c r="L324" t="n">
+        <v>36</v>
+      </c>
+      <c r="M324" t="n">
         <v>76.59574468085107</v>
       </c>
     </row>
@@ -17639,9 +19587,15 @@
         </is>
       </c>
       <c r="J325" t="n">
+        <v>4</v>
+      </c>
+      <c r="K325" t="n">
         <v>80</v>
       </c>
-      <c r="K325" t="n">
+      <c r="L325" t="n">
+        <v>38</v>
+      </c>
+      <c r="M325" t="n">
         <v>80.85106382978722</v>
       </c>
     </row>
@@ -17692,9 +19646,15 @@
         </is>
       </c>
       <c r="J326" t="n">
+        <v>4</v>
+      </c>
+      <c r="K326" t="n">
         <v>80</v>
       </c>
-      <c r="K326" t="n">
+      <c r="L326" t="n">
+        <v>43</v>
+      </c>
+      <c r="M326" t="n">
         <v>91.48936170212765</v>
       </c>
     </row>
@@ -17745,9 +19705,15 @@
         </is>
       </c>
       <c r="J327" t="n">
+        <v>3</v>
+      </c>
+      <c r="K327" t="n">
         <v>60</v>
       </c>
-      <c r="K327" t="n">
+      <c r="L327" t="n">
+        <v>26</v>
+      </c>
+      <c r="M327" t="n">
         <v>55.31914893617022</v>
       </c>
     </row>
@@ -17798,9 +19764,15 @@
         </is>
       </c>
       <c r="J328" t="n">
+        <v>4</v>
+      </c>
+      <c r="K328" t="n">
         <v>80</v>
       </c>
-      <c r="K328" t="n">
+      <c r="L328" t="n">
+        <v>26</v>
+      </c>
+      <c r="M328" t="n">
         <v>55.31914893617022</v>
       </c>
     </row>
@@ -17851,9 +19823,15 @@
         </is>
       </c>
       <c r="J329" t="n">
+        <v>5</v>
+      </c>
+      <c r="K329" t="n">
         <v>100</v>
       </c>
-      <c r="K329" t="n">
+      <c r="L329" t="n">
+        <v>43</v>
+      </c>
+      <c r="M329" t="n">
         <v>91.48936170212765</v>
       </c>
     </row>
@@ -17904,9 +19882,15 @@
         </is>
       </c>
       <c r="J330" t="n">
+        <v>4</v>
+      </c>
+      <c r="K330" t="n">
         <v>80</v>
       </c>
-      <c r="K330" t="n">
+      <c r="L330" t="n">
+        <v>21</v>
+      </c>
+      <c r="M330" t="n">
         <v>44.68085106382978</v>
       </c>
     </row>
@@ -17957,9 +19941,15 @@
         </is>
       </c>
       <c r="J331" t="n">
+        <v>5</v>
+      </c>
+      <c r="K331" t="n">
         <v>100</v>
       </c>
-      <c r="K331" t="n">
+      <c r="L331" t="n">
+        <v>32</v>
+      </c>
+      <c r="M331" t="n">
         <v>68.08510638297872</v>
       </c>
     </row>
@@ -18010,9 +20000,15 @@
         </is>
       </c>
       <c r="J332" t="n">
+        <v>2</v>
+      </c>
+      <c r="K332" t="n">
         <v>40</v>
       </c>
-      <c r="K332" t="n">
+      <c r="L332" t="n">
+        <v>25</v>
+      </c>
+      <c r="M332" t="n">
         <v>53.19148936170212</v>
       </c>
     </row>
@@ -18063,9 +20059,15 @@
         </is>
       </c>
       <c r="J333" t="n">
+        <v>3</v>
+      </c>
+      <c r="K333" t="n">
         <v>60</v>
       </c>
-      <c r="K333" t="n">
+      <c r="L333" t="n">
+        <v>23</v>
+      </c>
+      <c r="M333" t="n">
         <v>48.93617021276596</v>
       </c>
     </row>
@@ -18116,9 +20118,15 @@
         </is>
       </c>
       <c r="J334" t="n">
+        <v>3</v>
+      </c>
+      <c r="K334" t="n">
         <v>60</v>
       </c>
-      <c r="K334" t="n">
+      <c r="L334" t="n">
+        <v>25</v>
+      </c>
+      <c r="M334" t="n">
         <v>53.19148936170212</v>
       </c>
     </row>
@@ -18169,9 +20177,15 @@
         </is>
       </c>
       <c r="J335" t="n">
+        <v>2</v>
+      </c>
+      <c r="K335" t="n">
         <v>40</v>
       </c>
-      <c r="K335" t="n">
+      <c r="L335" t="n">
+        <v>33</v>
+      </c>
+      <c r="M335" t="n">
         <v>70.21276595744681</v>
       </c>
     </row>
@@ -18222,9 +20236,15 @@
         </is>
       </c>
       <c r="J336" t="n">
+        <v>4</v>
+      </c>
+      <c r="K336" t="n">
         <v>80</v>
       </c>
-      <c r="K336" t="n">
+      <c r="L336" t="n">
+        <v>24</v>
+      </c>
+      <c r="M336" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -18275,9 +20295,15 @@
         </is>
       </c>
       <c r="J337" t="n">
+        <v>4</v>
+      </c>
+      <c r="K337" t="n">
         <v>80</v>
       </c>
-      <c r="K337" t="n">
+      <c r="L337" t="n">
+        <v>20</v>
+      </c>
+      <c r="M337" t="n">
         <v>42.5531914893617</v>
       </c>
     </row>
@@ -18328,9 +20354,15 @@
         </is>
       </c>
       <c r="J338" t="n">
+        <v>4</v>
+      </c>
+      <c r="K338" t="n">
         <v>80</v>
       </c>
-      <c r="K338" t="n">
+      <c r="L338" t="n">
+        <v>40</v>
+      </c>
+      <c r="M338" t="n">
         <v>85.1063829787234</v>
       </c>
     </row>
@@ -18381,9 +20413,15 @@
         </is>
       </c>
       <c r="J339" t="n">
+        <v>4</v>
+      </c>
+      <c r="K339" t="n">
         <v>80</v>
       </c>
-      <c r="K339" t="n">
+      <c r="L339" t="n">
+        <v>21</v>
+      </c>
+      <c r="M339" t="n">
         <v>44.68085106382978</v>
       </c>
     </row>
@@ -18434,9 +20472,15 @@
         </is>
       </c>
       <c r="J340" t="n">
+        <v>5</v>
+      </c>
+      <c r="K340" t="n">
         <v>100</v>
       </c>
-      <c r="K340" t="n">
+      <c r="L340" t="n">
+        <v>31</v>
+      </c>
+      <c r="M340" t="n">
         <v>65.95744680851064</v>
       </c>
     </row>
@@ -18487,9 +20531,15 @@
         </is>
       </c>
       <c r="J341" t="n">
+        <v>5</v>
+      </c>
+      <c r="K341" t="n">
         <v>100</v>
       </c>
-      <c r="K341" t="n">
+      <c r="L341" t="n">
+        <v>28</v>
+      </c>
+      <c r="M341" t="n">
         <v>59.57446808510638</v>
       </c>
     </row>
@@ -18540,9 +20590,15 @@
         </is>
       </c>
       <c r="J342" t="n">
+        <v>2</v>
+      </c>
+      <c r="K342" t="n">
         <v>40</v>
       </c>
-      <c r="K342" t="n">
+      <c r="L342" t="n">
+        <v>14</v>
+      </c>
+      <c r="M342" t="n">
         <v>29.78723404255319</v>
       </c>
     </row>
@@ -18593,9 +20649,15 @@
         </is>
       </c>
       <c r="J343" t="n">
+        <v>4</v>
+      </c>
+      <c r="K343" t="n">
         <v>80</v>
       </c>
-      <c r="K343" t="n">
+      <c r="L343" t="n">
+        <v>26</v>
+      </c>
+      <c r="M343" t="n">
         <v>55.31914893617022</v>
       </c>
     </row>
@@ -18646,9 +20708,15 @@
         </is>
       </c>
       <c r="J344" t="n">
+        <v>5</v>
+      </c>
+      <c r="K344" t="n">
         <v>100</v>
       </c>
-      <c r="K344" t="n">
+      <c r="L344" t="n">
+        <v>20</v>
+      </c>
+      <c r="M344" t="n">
         <v>42.5531914893617</v>
       </c>
     </row>
@@ -18699,9 +20767,15 @@
         </is>
       </c>
       <c r="J345" t="n">
+        <v>4</v>
+      </c>
+      <c r="K345" t="n">
         <v>80</v>
       </c>
-      <c r="K345" t="n">
+      <c r="L345" t="n">
+        <v>37</v>
+      </c>
+      <c r="M345" t="n">
         <v>78.72340425531915</v>
       </c>
     </row>
@@ -18752,9 +20826,15 @@
         </is>
       </c>
       <c r="J346" t="n">
+        <v>4</v>
+      </c>
+      <c r="K346" t="n">
         <v>80</v>
       </c>
-      <c r="K346" t="n">
+      <c r="L346" t="n">
+        <v>37</v>
+      </c>
+      <c r="M346" t="n">
         <v>78.72340425531915</v>
       </c>
     </row>
@@ -18805,9 +20885,15 @@
         </is>
       </c>
       <c r="J347" t="n">
+        <v>4</v>
+      </c>
+      <c r="K347" t="n">
         <v>80</v>
       </c>
-      <c r="K347" t="n">
+      <c r="L347" t="n">
+        <v>36</v>
+      </c>
+      <c r="M347" t="n">
         <v>76.59574468085107</v>
       </c>
     </row>
@@ -18858,9 +20944,15 @@
         </is>
       </c>
       <c r="J348" t="n">
+        <v>3</v>
+      </c>
+      <c r="K348" t="n">
         <v>60</v>
       </c>
-      <c r="K348" t="n">
+      <c r="L348" t="n">
+        <v>20</v>
+      </c>
+      <c r="M348" t="n">
         <v>42.5531914893617</v>
       </c>
     </row>
@@ -18911,9 +21003,15 @@
         </is>
       </c>
       <c r="J349" t="n">
+        <v>3</v>
+      </c>
+      <c r="K349" t="n">
         <v>60</v>
       </c>
-      <c r="K349" t="n">
+      <c r="L349" t="n">
+        <v>23</v>
+      </c>
+      <c r="M349" t="n">
         <v>48.93617021276596</v>
       </c>
     </row>
@@ -18964,9 +21062,15 @@
         </is>
       </c>
       <c r="J350" t="n">
+        <v>2</v>
+      </c>
+      <c r="K350" t="n">
         <v>40</v>
       </c>
-      <c r="K350" t="n">
+      <c r="L350" t="n">
+        <v>37</v>
+      </c>
+      <c r="M350" t="n">
         <v>78.72340425531915</v>
       </c>
     </row>
@@ -19017,9 +21121,15 @@
         </is>
       </c>
       <c r="J351" t="n">
+        <v>5</v>
+      </c>
+      <c r="K351" t="n">
         <v>100</v>
       </c>
-      <c r="K351" t="n">
+      <c r="L351" t="n">
+        <v>30</v>
+      </c>
+      <c r="M351" t="n">
         <v>63.82978723404256</v>
       </c>
     </row>
@@ -19070,9 +21180,15 @@
         </is>
       </c>
       <c r="J352" t="n">
+        <v>4</v>
+      </c>
+      <c r="K352" t="n">
         <v>80</v>
       </c>
-      <c r="K352" t="n">
+      <c r="L352" t="n">
+        <v>21</v>
+      </c>
+      <c r="M352" t="n">
         <v>44.68085106382978</v>
       </c>
     </row>
@@ -19123,9 +21239,15 @@
         </is>
       </c>
       <c r="J353" t="n">
+        <v>3</v>
+      </c>
+      <c r="K353" t="n">
         <v>60</v>
       </c>
-      <c r="K353" t="n">
+      <c r="L353" t="n">
+        <v>25</v>
+      </c>
+      <c r="M353" t="n">
         <v>53.19148936170212</v>
       </c>
     </row>
@@ -19176,9 +21298,15 @@
         </is>
       </c>
       <c r="J354" t="n">
+        <v>1</v>
+      </c>
+      <c r="K354" t="n">
         <v>20</v>
       </c>
-      <c r="K354" t="n">
+      <c r="L354" t="n">
+        <v>25</v>
+      </c>
+      <c r="M354" t="n">
         <v>53.19148936170212</v>
       </c>
     </row>
@@ -19229,9 +21357,15 @@
         </is>
       </c>
       <c r="J355" t="n">
+        <v>5</v>
+      </c>
+      <c r="K355" t="n">
         <v>100</v>
       </c>
-      <c r="K355" t="n">
+      <c r="L355" t="n">
+        <v>26</v>
+      </c>
+      <c r="M355" t="n">
         <v>55.31914893617022</v>
       </c>
     </row>
@@ -19282,9 +21416,15 @@
         </is>
       </c>
       <c r="J356" t="n">
+        <v>3</v>
+      </c>
+      <c r="K356" t="n">
         <v>60</v>
       </c>
-      <c r="K356" t="n">
+      <c r="L356" t="n">
+        <v>37</v>
+      </c>
+      <c r="M356" t="n">
         <v>78.72340425531915</v>
       </c>
     </row>
@@ -19335,9 +21475,15 @@
         </is>
       </c>
       <c r="J357" t="n">
+        <v>5</v>
+      </c>
+      <c r="K357" t="n">
         <v>100</v>
       </c>
-      <c r="K357" t="n">
+      <c r="L357" t="n">
+        <v>45</v>
+      </c>
+      <c r="M357" t="n">
         <v>95.74468085106383</v>
       </c>
     </row>
@@ -19388,9 +21534,15 @@
         </is>
       </c>
       <c r="J358" t="n">
+        <v>3</v>
+      </c>
+      <c r="K358" t="n">
         <v>60</v>
       </c>
-      <c r="K358" t="n">
+      <c r="L358" t="n">
+        <v>27</v>
+      </c>
+      <c r="M358" t="n">
         <v>57.44680851063831</v>
       </c>
     </row>
@@ -19441,9 +21593,15 @@
         </is>
       </c>
       <c r="J359" t="n">
+        <v>2</v>
+      </c>
+      <c r="K359" t="n">
         <v>40</v>
       </c>
-      <c r="K359" t="n">
+      <c r="L359" t="n">
+        <v>22</v>
+      </c>
+      <c r="M359" t="n">
         <v>46.80851063829788</v>
       </c>
     </row>
@@ -19494,9 +21652,15 @@
         </is>
       </c>
       <c r="J360" t="n">
+        <v>4</v>
+      </c>
+      <c r="K360" t="n">
         <v>80</v>
       </c>
-      <c r="K360" t="n">
+      <c r="L360" t="n">
+        <v>26</v>
+      </c>
+      <c r="M360" t="n">
         <v>55.31914893617022</v>
       </c>
     </row>
@@ -19547,9 +21711,15 @@
         </is>
       </c>
       <c r="J361" t="n">
+        <v>3</v>
+      </c>
+      <c r="K361" t="n">
         <v>60</v>
       </c>
-      <c r="K361" t="n">
+      <c r="L361" t="n">
+        <v>31</v>
+      </c>
+      <c r="M361" t="n">
         <v>65.95744680851064</v>
       </c>
     </row>
@@ -19600,9 +21770,15 @@
         </is>
       </c>
       <c r="J362" t="n">
+        <v>5</v>
+      </c>
+      <c r="K362" t="n">
         <v>100</v>
       </c>
-      <c r="K362" t="n">
+      <c r="L362" t="n">
+        <v>33</v>
+      </c>
+      <c r="M362" t="n">
         <v>70.21276595744681</v>
       </c>
     </row>
@@ -19653,9 +21829,15 @@
         </is>
       </c>
       <c r="J363" t="n">
+        <v>2</v>
+      </c>
+      <c r="K363" t="n">
         <v>40</v>
       </c>
-      <c r="K363" t="n">
+      <c r="L363" t="n">
+        <v>35</v>
+      </c>
+      <c r="M363" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -19706,9 +21888,15 @@
         </is>
       </c>
       <c r="J364" t="n">
+        <v>3</v>
+      </c>
+      <c r="K364" t="n">
         <v>60</v>
       </c>
-      <c r="K364" t="n">
+      <c r="L364" t="n">
+        <v>24</v>
+      </c>
+      <c r="M364" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -19759,9 +21947,15 @@
         </is>
       </c>
       <c r="J365" t="n">
+        <v>5</v>
+      </c>
+      <c r="K365" t="n">
         <v>100</v>
       </c>
-      <c r="K365" t="n">
+      <c r="L365" t="n">
+        <v>34</v>
+      </c>
+      <c r="M365" t="n">
         <v>72.3404255319149</v>
       </c>
     </row>
@@ -19812,9 +22006,15 @@
         </is>
       </c>
       <c r="J366" t="n">
+        <v>5</v>
+      </c>
+      <c r="K366" t="n">
         <v>100</v>
       </c>
-      <c r="K366" t="n">
+      <c r="L366" t="n">
+        <v>21</v>
+      </c>
+      <c r="M366" t="n">
         <v>44.68085106382978</v>
       </c>
     </row>
@@ -19865,9 +22065,15 @@
         </is>
       </c>
       <c r="J367" t="n">
+        <v>4</v>
+      </c>
+      <c r="K367" t="n">
         <v>80</v>
       </c>
-      <c r="K367" t="n">
+      <c r="L367" t="n">
+        <v>29</v>
+      </c>
+      <c r="M367" t="n">
         <v>61.70212765957447</v>
       </c>
     </row>
@@ -19918,9 +22124,15 @@
         </is>
       </c>
       <c r="J368" t="n">
+        <v>4</v>
+      </c>
+      <c r="K368" t="n">
         <v>80</v>
       </c>
-      <c r="K368" t="n">
+      <c r="L368" t="n">
+        <v>25</v>
+      </c>
+      <c r="M368" t="n">
         <v>53.19148936170212</v>
       </c>
     </row>
@@ -19971,9 +22183,15 @@
         </is>
       </c>
       <c r="J369" t="n">
+        <v>3</v>
+      </c>
+      <c r="K369" t="n">
         <v>60</v>
       </c>
-      <c r="K369" t="n">
+      <c r="L369" t="n">
+        <v>37</v>
+      </c>
+      <c r="M369" t="n">
         <v>78.72340425531915</v>
       </c>
     </row>
@@ -20024,9 +22242,15 @@
         </is>
       </c>
       <c r="J370" t="n">
+        <v>3</v>
+      </c>
+      <c r="K370" t="n">
         <v>60</v>
       </c>
-      <c r="K370" t="n">
+      <c r="L370" t="n">
+        <v>26</v>
+      </c>
+      <c r="M370" t="n">
         <v>55.31914893617022</v>
       </c>
     </row>
@@ -20077,9 +22301,15 @@
         </is>
       </c>
       <c r="J371" t="n">
+        <v>5</v>
+      </c>
+      <c r="K371" t="n">
         <v>100</v>
       </c>
-      <c r="K371" t="n">
+      <c r="L371" t="n">
+        <v>45</v>
+      </c>
+      <c r="M371" t="n">
         <v>95.74468085106383</v>
       </c>
     </row>
@@ -20130,9 +22360,15 @@
         </is>
       </c>
       <c r="J372" t="n">
+        <v>4</v>
+      </c>
+      <c r="K372" t="n">
         <v>80</v>
       </c>
-      <c r="K372" t="n">
+      <c r="L372" t="n">
+        <v>35</v>
+      </c>
+      <c r="M372" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -20183,9 +22419,15 @@
         </is>
       </c>
       <c r="J373" t="n">
+        <v>4</v>
+      </c>
+      <c r="K373" t="n">
         <v>80</v>
       </c>
-      <c r="K373" t="n">
+      <c r="L373" t="n">
+        <v>24</v>
+      </c>
+      <c r="M373" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -20236,9 +22478,15 @@
         </is>
       </c>
       <c r="J374" t="n">
+        <v>2</v>
+      </c>
+      <c r="K374" t="n">
         <v>40</v>
       </c>
-      <c r="K374" t="n">
+      <c r="L374" t="n">
+        <v>30</v>
+      </c>
+      <c r="M374" t="n">
         <v>63.82978723404256</v>
       </c>
     </row>
@@ -20289,9 +22537,15 @@
         </is>
       </c>
       <c r="J375" t="n">
+        <v>2</v>
+      </c>
+      <c r="K375" t="n">
         <v>40</v>
       </c>
-      <c r="K375" t="n">
+      <c r="L375" t="n">
+        <v>41</v>
+      </c>
+      <c r="M375" t="n">
         <v>87.2340425531915</v>
       </c>
     </row>
@@ -20342,9 +22596,15 @@
         </is>
       </c>
       <c r="J376" t="n">
+        <v>2</v>
+      </c>
+      <c r="K376" t="n">
         <v>40</v>
       </c>
-      <c r="K376" t="n">
+      <c r="L376" t="n">
+        <v>17</v>
+      </c>
+      <c r="M376" t="n">
         <v>36.17021276595745</v>
       </c>
     </row>
@@ -20395,9 +22655,15 @@
         </is>
       </c>
       <c r="J377" t="n">
+        <v>4</v>
+      </c>
+      <c r="K377" t="n">
         <v>80</v>
       </c>
-      <c r="K377" t="n">
+      <c r="L377" t="n">
+        <v>34</v>
+      </c>
+      <c r="M377" t="n">
         <v>72.3404255319149</v>
       </c>
     </row>
@@ -20448,9 +22714,15 @@
         </is>
       </c>
       <c r="J378" t="n">
+        <v>2</v>
+      </c>
+      <c r="K378" t="n">
         <v>40</v>
       </c>
-      <c r="K378" t="n">
+      <c r="L378" t="n">
+        <v>13</v>
+      </c>
+      <c r="M378" t="n">
         <v>27.65957446808511</v>
       </c>
     </row>
@@ -20501,9 +22773,15 @@
         </is>
       </c>
       <c r="J379" t="n">
+        <v>3</v>
+      </c>
+      <c r="K379" t="n">
         <v>60</v>
       </c>
-      <c r="K379" t="n">
+      <c r="L379" t="n">
+        <v>18</v>
+      </c>
+      <c r="M379" t="n">
         <v>38.29787234042553</v>
       </c>
     </row>
@@ -20554,9 +22832,15 @@
         </is>
       </c>
       <c r="J380" t="n">
+        <v>4</v>
+      </c>
+      <c r="K380" t="n">
         <v>80</v>
       </c>
-      <c r="K380" t="n">
+      <c r="L380" t="n">
+        <v>40</v>
+      </c>
+      <c r="M380" t="n">
         <v>85.1063829787234</v>
       </c>
     </row>
@@ -20607,9 +22891,15 @@
         </is>
       </c>
       <c r="J381" t="n">
+        <v>3</v>
+      </c>
+      <c r="K381" t="n">
         <v>60</v>
       </c>
-      <c r="K381" t="n">
+      <c r="L381" t="n">
+        <v>21</v>
+      </c>
+      <c r="M381" t="n">
         <v>44.68085106382978</v>
       </c>
     </row>
@@ -20660,9 +22950,15 @@
         </is>
       </c>
       <c r="J382" t="n">
+        <v>3</v>
+      </c>
+      <c r="K382" t="n">
         <v>60</v>
       </c>
-      <c r="K382" t="n">
+      <c r="L382" t="n">
+        <v>37</v>
+      </c>
+      <c r="M382" t="n">
         <v>78.72340425531915</v>
       </c>
     </row>
@@ -20713,9 +23009,15 @@
         </is>
       </c>
       <c r="J383" t="n">
+        <v>4</v>
+      </c>
+      <c r="K383" t="n">
         <v>80</v>
       </c>
-      <c r="K383" t="n">
+      <c r="L383" t="n">
+        <v>32</v>
+      </c>
+      <c r="M383" t="n">
         <v>68.08510638297872</v>
       </c>
     </row>
@@ -20766,9 +23068,15 @@
         </is>
       </c>
       <c r="J384" t="n">
+        <v>5</v>
+      </c>
+      <c r="K384" t="n">
         <v>100</v>
       </c>
-      <c r="K384" t="n">
+      <c r="L384" t="n">
+        <v>35</v>
+      </c>
+      <c r="M384" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -20819,9 +23127,15 @@
         </is>
       </c>
       <c r="J385" t="n">
+        <v>4</v>
+      </c>
+      <c r="K385" t="n">
         <v>80</v>
       </c>
-      <c r="K385" t="n">
+      <c r="L385" t="n">
+        <v>37</v>
+      </c>
+      <c r="M385" t="n">
         <v>78.72340425531915</v>
       </c>
     </row>
@@ -20872,9 +23186,15 @@
         </is>
       </c>
       <c r="J386" t="n">
+        <v>2</v>
+      </c>
+      <c r="K386" t="n">
         <v>40</v>
       </c>
-      <c r="K386" t="n">
+      <c r="L386" t="n">
+        <v>23</v>
+      </c>
+      <c r="M386" t="n">
         <v>48.93617021276596</v>
       </c>
     </row>
@@ -20925,9 +23245,15 @@
         </is>
       </c>
       <c r="J387" t="n">
+        <v>5</v>
+      </c>
+      <c r="K387" t="n">
         <v>100</v>
       </c>
-      <c r="K387" t="n">
+      <c r="L387" t="n">
+        <v>32</v>
+      </c>
+      <c r="M387" t="n">
         <v>68.08510638297872</v>
       </c>
     </row>
@@ -20978,9 +23304,15 @@
         </is>
       </c>
       <c r="J388" t="n">
+        <v>2</v>
+      </c>
+      <c r="K388" t="n">
         <v>40</v>
       </c>
-      <c r="K388" t="n">
+      <c r="L388" t="n">
+        <v>19</v>
+      </c>
+      <c r="M388" t="n">
         <v>40.42553191489361</v>
       </c>
     </row>
@@ -21031,9 +23363,15 @@
         </is>
       </c>
       <c r="J389" t="n">
+        <v>3</v>
+      </c>
+      <c r="K389" t="n">
         <v>60</v>
       </c>
-      <c r="K389" t="n">
+      <c r="L389" t="n">
+        <v>25</v>
+      </c>
+      <c r="M389" t="n">
         <v>53.19148936170212</v>
       </c>
     </row>
@@ -21084,9 +23422,15 @@
         </is>
       </c>
       <c r="J390" t="n">
+        <v>5</v>
+      </c>
+      <c r="K390" t="n">
         <v>100</v>
       </c>
-      <c r="K390" t="n">
+      <c r="L390" t="n">
+        <v>37</v>
+      </c>
+      <c r="M390" t="n">
         <v>78.72340425531915</v>
       </c>
     </row>
@@ -21137,9 +23481,15 @@
         </is>
       </c>
       <c r="J391" t="n">
+        <v>5</v>
+      </c>
+      <c r="K391" t="n">
         <v>100</v>
       </c>
-      <c r="K391" t="n">
+      <c r="L391" t="n">
+        <v>46</v>
+      </c>
+      <c r="M391" t="n">
         <v>97.87234042553192</v>
       </c>
     </row>
@@ -21190,9 +23540,15 @@
         </is>
       </c>
       <c r="J392" t="n">
+        <v>3</v>
+      </c>
+      <c r="K392" t="n">
         <v>60</v>
       </c>
-      <c r="K392" t="n">
+      <c r="L392" t="n">
+        <v>22</v>
+      </c>
+      <c r="M392" t="n">
         <v>46.80851063829788</v>
       </c>
     </row>
@@ -21243,9 +23599,15 @@
         </is>
       </c>
       <c r="J393" t="n">
+        <v>1</v>
+      </c>
+      <c r="K393" t="n">
         <v>20</v>
       </c>
-      <c r="K393" t="n">
+      <c r="L393" t="n">
+        <v>27</v>
+      </c>
+      <c r="M393" t="n">
         <v>57.44680851063831</v>
       </c>
     </row>
@@ -21296,9 +23658,15 @@
         </is>
       </c>
       <c r="J394" t="n">
+        <v>4</v>
+      </c>
+      <c r="K394" t="n">
         <v>80</v>
       </c>
-      <c r="K394" t="n">
+      <c r="L394" t="n">
+        <v>37</v>
+      </c>
+      <c r="M394" t="n">
         <v>78.72340425531915</v>
       </c>
     </row>
@@ -21349,9 +23717,15 @@
         </is>
       </c>
       <c r="J395" t="n">
+        <v>2</v>
+      </c>
+      <c r="K395" t="n">
         <v>40</v>
       </c>
-      <c r="K395" t="n">
+      <c r="L395" t="n">
+        <v>29</v>
+      </c>
+      <c r="M395" t="n">
         <v>61.70212765957447</v>
       </c>
     </row>
@@ -21402,9 +23776,15 @@
         </is>
       </c>
       <c r="J396" t="n">
+        <v>4</v>
+      </c>
+      <c r="K396" t="n">
         <v>80</v>
       </c>
-      <c r="K396" t="n">
+      <c r="L396" t="n">
+        <v>43</v>
+      </c>
+      <c r="M396" t="n">
         <v>91.48936170212765</v>
       </c>
     </row>
@@ -21455,9 +23835,15 @@
         </is>
       </c>
       <c r="J397" t="n">
+        <v>2</v>
+      </c>
+      <c r="K397" t="n">
         <v>40</v>
       </c>
-      <c r="K397" t="n">
+      <c r="L397" t="n">
+        <v>23</v>
+      </c>
+      <c r="M397" t="n">
         <v>48.93617021276596</v>
       </c>
     </row>
@@ -21508,9 +23894,15 @@
         </is>
       </c>
       <c r="J398" t="n">
+        <v>3</v>
+      </c>
+      <c r="K398" t="n">
         <v>60</v>
       </c>
-      <c r="K398" t="n">
+      <c r="L398" t="n">
+        <v>32</v>
+      </c>
+      <c r="M398" t="n">
         <v>68.08510638297872</v>
       </c>
     </row>
@@ -21561,9 +23953,15 @@
         </is>
       </c>
       <c r="J399" t="n">
+        <v>5</v>
+      </c>
+      <c r="K399" t="n">
         <v>100</v>
       </c>
-      <c r="K399" t="n">
+      <c r="L399" t="n">
+        <v>40</v>
+      </c>
+      <c r="M399" t="n">
         <v>85.1063829787234</v>
       </c>
     </row>
@@ -21614,9 +24012,15 @@
         </is>
       </c>
       <c r="J400" t="n">
+        <v>2</v>
+      </c>
+      <c r="K400" t="n">
         <v>40</v>
       </c>
-      <c r="K400" t="n">
+      <c r="L400" t="n">
+        <v>27</v>
+      </c>
+      <c r="M400" t="n">
         <v>57.44680851063831</v>
       </c>
     </row>
@@ -21667,9 +24071,15 @@
         </is>
       </c>
       <c r="J401" t="n">
+        <v>4</v>
+      </c>
+      <c r="K401" t="n">
         <v>80</v>
       </c>
-      <c r="K401" t="n">
+      <c r="L401" t="n">
+        <v>46</v>
+      </c>
+      <c r="M401" t="n">
         <v>97.87234042553192</v>
       </c>
     </row>
@@ -21720,9 +24130,15 @@
         </is>
       </c>
       <c r="J402" t="n">
+        <v>3</v>
+      </c>
+      <c r="K402" t="n">
         <v>60</v>
       </c>
-      <c r="K402" t="n">
+      <c r="L402" t="n">
+        <v>20</v>
+      </c>
+      <c r="M402" t="n">
         <v>42.5531914893617</v>
       </c>
     </row>
@@ -21773,9 +24189,15 @@
         </is>
       </c>
       <c r="J403" t="n">
+        <v>3</v>
+      </c>
+      <c r="K403" t="n">
         <v>60</v>
       </c>
-      <c r="K403" t="n">
+      <c r="L403" t="n">
+        <v>29</v>
+      </c>
+      <c r="M403" t="n">
         <v>61.70212765957447</v>
       </c>
     </row>
@@ -21826,9 +24248,15 @@
         </is>
       </c>
       <c r="J404" t="n">
+        <v>5</v>
+      </c>
+      <c r="K404" t="n">
         <v>100</v>
       </c>
-      <c r="K404" t="n">
+      <c r="L404" t="n">
+        <v>44</v>
+      </c>
+      <c r="M404" t="n">
         <v>93.61702127659575</v>
       </c>
     </row>
@@ -21879,9 +24307,15 @@
         </is>
       </c>
       <c r="J405" t="n">
+        <v>2</v>
+      </c>
+      <c r="K405" t="n">
         <v>40</v>
       </c>
-      <c r="K405" t="n">
+      <c r="L405" t="n">
+        <v>37</v>
+      </c>
+      <c r="M405" t="n">
         <v>78.72340425531915</v>
       </c>
     </row>
@@ -21932,9 +24366,15 @@
         </is>
       </c>
       <c r="J406" t="n">
+        <v>2</v>
+      </c>
+      <c r="K406" t="n">
         <v>40</v>
       </c>
-      <c r="K406" t="n">
+      <c r="L406" t="n">
+        <v>20</v>
+      </c>
+      <c r="M406" t="n">
         <v>42.5531914893617</v>
       </c>
     </row>
@@ -21985,9 +24425,15 @@
         </is>
       </c>
       <c r="J407" t="n">
+        <v>4</v>
+      </c>
+      <c r="K407" t="n">
         <v>80</v>
       </c>
-      <c r="K407" t="n">
+      <c r="L407" t="n">
+        <v>23</v>
+      </c>
+      <c r="M407" t="n">
         <v>48.93617021276596</v>
       </c>
     </row>
@@ -22038,9 +24484,15 @@
         </is>
       </c>
       <c r="J408" t="n">
+        <v>3</v>
+      </c>
+      <c r="K408" t="n">
         <v>60</v>
       </c>
-      <c r="K408" t="n">
+      <c r="L408" t="n">
+        <v>31</v>
+      </c>
+      <c r="M408" t="n">
         <v>65.95744680851064</v>
       </c>
     </row>
@@ -22091,9 +24543,15 @@
         </is>
       </c>
       <c r="J409" t="n">
+        <v>5</v>
+      </c>
+      <c r="K409" t="n">
         <v>100</v>
       </c>
-      <c r="K409" t="n">
+      <c r="L409" t="n">
+        <v>45</v>
+      </c>
+      <c r="M409" t="n">
         <v>95.74468085106383</v>
       </c>
     </row>
@@ -22144,9 +24602,15 @@
         </is>
       </c>
       <c r="J410" t="n">
+        <v>4</v>
+      </c>
+      <c r="K410" t="n">
         <v>80</v>
       </c>
-      <c r="K410" t="n">
+      <c r="L410" t="n">
+        <v>42</v>
+      </c>
+      <c r="M410" t="n">
         <v>89.36170212765957</v>
       </c>
     </row>
@@ -22197,9 +24661,15 @@
         </is>
       </c>
       <c r="J411" t="n">
+        <v>3</v>
+      </c>
+      <c r="K411" t="n">
         <v>60</v>
       </c>
-      <c r="K411" t="n">
+      <c r="L411" t="n">
+        <v>21</v>
+      </c>
+      <c r="M411" t="n">
         <v>44.68085106382978</v>
       </c>
     </row>
@@ -22250,9 +24720,15 @@
         </is>
       </c>
       <c r="J412" t="n">
+        <v>3</v>
+      </c>
+      <c r="K412" t="n">
         <v>60</v>
       </c>
-      <c r="K412" t="n">
+      <c r="L412" t="n">
+        <v>13</v>
+      </c>
+      <c r="M412" t="n">
         <v>27.65957446808511</v>
       </c>
     </row>
@@ -22303,9 +24779,15 @@
         </is>
       </c>
       <c r="J413" t="n">
+        <v>5</v>
+      </c>
+      <c r="K413" t="n">
         <v>100</v>
       </c>
-      <c r="K413" t="n">
+      <c r="L413" t="n">
+        <v>37</v>
+      </c>
+      <c r="M413" t="n">
         <v>78.72340425531915</v>
       </c>
     </row>
@@ -22356,9 +24838,15 @@
         </is>
       </c>
       <c r="J414" t="n">
+        <v>3</v>
+      </c>
+      <c r="K414" t="n">
         <v>60</v>
       </c>
-      <c r="K414" t="n">
+      <c r="L414" t="n">
+        <v>20</v>
+      </c>
+      <c r="M414" t="n">
         <v>42.5531914893617</v>
       </c>
     </row>
@@ -22409,9 +24897,15 @@
         </is>
       </c>
       <c r="J415" t="n">
+        <v>2</v>
+      </c>
+      <c r="K415" t="n">
         <v>40</v>
       </c>
-      <c r="K415" t="n">
+      <c r="L415" t="n">
+        <v>20</v>
+      </c>
+      <c r="M415" t="n">
         <v>42.5531914893617</v>
       </c>
     </row>
@@ -22462,9 +24956,15 @@
         </is>
       </c>
       <c r="J416" t="n">
+        <v>3</v>
+      </c>
+      <c r="K416" t="n">
         <v>60</v>
       </c>
-      <c r="K416" t="n">
+      <c r="L416" t="n">
+        <v>41</v>
+      </c>
+      <c r="M416" t="n">
         <v>87.2340425531915</v>
       </c>
     </row>
@@ -22515,9 +25015,15 @@
         </is>
       </c>
       <c r="J417" t="n">
+        <v>3</v>
+      </c>
+      <c r="K417" t="n">
         <v>60</v>
       </c>
-      <c r="K417" t="n">
+      <c r="L417" t="n">
+        <v>23</v>
+      </c>
+      <c r="M417" t="n">
         <v>48.93617021276596</v>
       </c>
     </row>
@@ -22568,9 +25074,15 @@
         </is>
       </c>
       <c r="J418" t="n">
+        <v>5</v>
+      </c>
+      <c r="K418" t="n">
         <v>100</v>
       </c>
-      <c r="K418" t="n">
+      <c r="L418" t="n">
+        <v>35</v>
+      </c>
+      <c r="M418" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -22621,9 +25133,15 @@
         </is>
       </c>
       <c r="J419" t="n">
+        <v>2</v>
+      </c>
+      <c r="K419" t="n">
         <v>40</v>
       </c>
-      <c r="K419" t="n">
+      <c r="L419" t="n">
+        <v>27</v>
+      </c>
+      <c r="M419" t="n">
         <v>57.44680851063831</v>
       </c>
     </row>
@@ -22674,9 +25192,15 @@
         </is>
       </c>
       <c r="J420" t="n">
+        <v>5</v>
+      </c>
+      <c r="K420" t="n">
         <v>100</v>
       </c>
-      <c r="K420" t="n">
+      <c r="L420" t="n">
+        <v>36</v>
+      </c>
+      <c r="M420" t="n">
         <v>76.59574468085107</v>
       </c>
     </row>
@@ -22727,9 +25251,15 @@
         </is>
       </c>
       <c r="J421" t="n">
+        <v>5</v>
+      </c>
+      <c r="K421" t="n">
         <v>100</v>
       </c>
-      <c r="K421" t="n">
+      <c r="L421" t="n">
+        <v>44</v>
+      </c>
+      <c r="M421" t="n">
         <v>93.61702127659575</v>
       </c>
     </row>
@@ -22780,9 +25310,15 @@
         </is>
       </c>
       <c r="J422" t="n">
+        <v>2</v>
+      </c>
+      <c r="K422" t="n">
         <v>40</v>
       </c>
-      <c r="K422" t="n">
+      <c r="L422" t="n">
+        <v>29</v>
+      </c>
+      <c r="M422" t="n">
         <v>61.70212765957447</v>
       </c>
     </row>
@@ -22833,9 +25369,15 @@
         </is>
       </c>
       <c r="J423" t="n">
+        <v>1</v>
+      </c>
+      <c r="K423" t="n">
         <v>20</v>
       </c>
-      <c r="K423" t="n">
+      <c r="L423" t="n">
+        <v>19</v>
+      </c>
+      <c r="M423" t="n">
         <v>40.42553191489361</v>
       </c>
     </row>
@@ -22886,9 +25428,15 @@
         </is>
       </c>
       <c r="J424" t="n">
+        <v>5</v>
+      </c>
+      <c r="K424" t="n">
         <v>100</v>
       </c>
-      <c r="K424" t="n">
+      <c r="L424" t="n">
+        <v>38</v>
+      </c>
+      <c r="M424" t="n">
         <v>80.85106382978722</v>
       </c>
     </row>
@@ -22939,9 +25487,15 @@
         </is>
       </c>
       <c r="J425" t="n">
+        <v>5</v>
+      </c>
+      <c r="K425" t="n">
         <v>100</v>
       </c>
-      <c r="K425" t="n">
+      <c r="L425" t="n">
+        <v>28</v>
+      </c>
+      <c r="M425" t="n">
         <v>59.57446808510638</v>
       </c>
     </row>
@@ -22992,9 +25546,15 @@
         </is>
       </c>
       <c r="J426" t="n">
+        <v>4</v>
+      </c>
+      <c r="K426" t="n">
         <v>80</v>
       </c>
-      <c r="K426" t="n">
+      <c r="L426" t="n">
+        <v>34</v>
+      </c>
+      <c r="M426" t="n">
         <v>72.3404255319149</v>
       </c>
     </row>
@@ -23045,9 +25605,15 @@
         </is>
       </c>
       <c r="J427" t="n">
+        <v>3</v>
+      </c>
+      <c r="K427" t="n">
         <v>60</v>
       </c>
-      <c r="K427" t="n">
+      <c r="L427" t="n">
+        <v>39</v>
+      </c>
+      <c r="M427" t="n">
         <v>82.97872340425532</v>
       </c>
     </row>
@@ -23098,9 +25664,15 @@
         </is>
       </c>
       <c r="J428" t="n">
+        <v>3</v>
+      </c>
+      <c r="K428" t="n">
         <v>60</v>
       </c>
-      <c r="K428" t="n">
+      <c r="L428" t="n">
+        <v>25</v>
+      </c>
+      <c r="M428" t="n">
         <v>53.19148936170212</v>
       </c>
     </row>
@@ -23154,6 +25726,12 @@
         <v>0</v>
       </c>
       <c r="K429" t="n">
+        <v>0</v>
+      </c>
+      <c r="L429" t="n">
+        <v>29</v>
+      </c>
+      <c r="M429" t="n">
         <v>61.70212765957447</v>
       </c>
     </row>
@@ -23204,9 +25782,15 @@
         </is>
       </c>
       <c r="J430" t="n">
+        <v>5</v>
+      </c>
+      <c r="K430" t="n">
         <v>100</v>
       </c>
-      <c r="K430" t="n">
+      <c r="L430" t="n">
+        <v>38</v>
+      </c>
+      <c r="M430" t="n">
         <v>80.85106382978722</v>
       </c>
     </row>
@@ -23257,9 +25841,15 @@
         </is>
       </c>
       <c r="J431" t="n">
+        <v>2</v>
+      </c>
+      <c r="K431" t="n">
         <v>40</v>
       </c>
-      <c r="K431" t="n">
+      <c r="L431" t="n">
+        <v>21</v>
+      </c>
+      <c r="M431" t="n">
         <v>44.68085106382978</v>
       </c>
     </row>
@@ -23310,9 +25900,15 @@
         </is>
       </c>
       <c r="J432" t="n">
+        <v>3</v>
+      </c>
+      <c r="K432" t="n">
         <v>60</v>
       </c>
-      <c r="K432" t="n">
+      <c r="L432" t="n">
+        <v>29</v>
+      </c>
+      <c r="M432" t="n">
         <v>61.70212765957447</v>
       </c>
     </row>
@@ -23363,9 +25959,15 @@
         </is>
       </c>
       <c r="J433" t="n">
+        <v>2</v>
+      </c>
+      <c r="K433" t="n">
         <v>40</v>
       </c>
-      <c r="K433" t="n">
+      <c r="L433" t="n">
+        <v>16</v>
+      </c>
+      <c r="M433" t="n">
         <v>34.04255319148936</v>
       </c>
     </row>
@@ -23416,9 +26018,15 @@
         </is>
       </c>
       <c r="J434" t="n">
+        <v>2</v>
+      </c>
+      <c r="K434" t="n">
         <v>40</v>
       </c>
-      <c r="K434" t="n">
+      <c r="L434" t="n">
+        <v>40</v>
+      </c>
+      <c r="M434" t="n">
         <v>85.1063829787234</v>
       </c>
     </row>
@@ -23469,9 +26077,15 @@
         </is>
       </c>
       <c r="J435" t="n">
+        <v>5</v>
+      </c>
+      <c r="K435" t="n">
         <v>100</v>
       </c>
-      <c r="K435" t="n">
+      <c r="L435" t="n">
+        <v>29</v>
+      </c>
+      <c r="M435" t="n">
         <v>61.70212765957447</v>
       </c>
     </row>
@@ -23522,9 +26136,15 @@
         </is>
       </c>
       <c r="J436" t="n">
+        <v>3</v>
+      </c>
+      <c r="K436" t="n">
         <v>60</v>
       </c>
-      <c r="K436" t="n">
+      <c r="L436" t="n">
+        <v>39</v>
+      </c>
+      <c r="M436" t="n">
         <v>82.97872340425532</v>
       </c>
     </row>
@@ -23575,9 +26195,15 @@
         </is>
       </c>
       <c r="J437" t="n">
+        <v>3</v>
+      </c>
+      <c r="K437" t="n">
         <v>60</v>
       </c>
-      <c r="K437" t="n">
+      <c r="L437" t="n">
+        <v>31</v>
+      </c>
+      <c r="M437" t="n">
         <v>65.95744680851064</v>
       </c>
     </row>
@@ -23628,9 +26254,15 @@
         </is>
       </c>
       <c r="J438" t="n">
+        <v>2</v>
+      </c>
+      <c r="K438" t="n">
         <v>40</v>
       </c>
-      <c r="K438" t="n">
+      <c r="L438" t="n">
+        <v>35</v>
+      </c>
+      <c r="M438" t="n">
         <v>74.46808510638297</v>
       </c>
     </row>
@@ -23681,9 +26313,15 @@
         </is>
       </c>
       <c r="J439" t="n">
+        <v>4</v>
+      </c>
+      <c r="K439" t="n">
         <v>80</v>
       </c>
-      <c r="K439" t="n">
+      <c r="L439" t="n">
+        <v>24</v>
+      </c>
+      <c r="M439" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -23734,9 +26372,15 @@
         </is>
       </c>
       <c r="J440" t="n">
+        <v>2</v>
+      </c>
+      <c r="K440" t="n">
         <v>40</v>
       </c>
-      <c r="K440" t="n">
+      <c r="L440" t="n">
+        <v>24</v>
+      </c>
+      <c r="M440" t="n">
         <v>51.06382978723404</v>
       </c>
     </row>
@@ -23787,9 +26431,15 @@
         </is>
       </c>
       <c r="J441" t="n">
+        <v>3</v>
+      </c>
+      <c r="K441" t="n">
         <v>60</v>
       </c>
-      <c r="K441" t="n">
+      <c r="L441" t="n">
+        <v>19</v>
+      </c>
+      <c r="M441" t="n">
         <v>40.42553191489361</v>
       </c>
     </row>
@@ -23840,9 +26490,15 @@
         </is>
       </c>
       <c r="J442" t="n">
+        <v>4</v>
+      </c>
+      <c r="K442" t="n">
         <v>80</v>
       </c>
-      <c r="K442" t="n">
+      <c r="L442" t="n">
+        <v>27</v>
+      </c>
+      <c r="M442" t="n">
         <v>57.44680851063831</v>
       </c>
     </row>
@@ -23893,9 +26549,15 @@
         </is>
       </c>
       <c r="J443" t="n">
+        <v>3</v>
+      </c>
+      <c r="K443" t="n">
         <v>60</v>
       </c>
-      <c r="K443" t="n">
+      <c r="L443" t="n">
+        <v>38</v>
+      </c>
+      <c r="M443" t="n">
         <v>80.85106382978722</v>
       </c>
     </row>
@@ -23946,9 +26608,15 @@
         </is>
       </c>
       <c r="J444" t="n">
+        <v>4</v>
+      </c>
+      <c r="K444" t="n">
         <v>80</v>
       </c>
-      <c r="K444" t="n">
+      <c r="L444" t="n">
+        <v>28</v>
+      </c>
+      <c r="M444" t="n">
         <v>59.57446808510638</v>
       </c>
     </row>
